--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2ED708-E05D-44AF-A1F1-DB7F6136140B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E921ED5-0C75-4C61-A177-FF878B42D9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -297,6 +297,8 @@
       <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 09-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 10-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 11-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 14-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -312,7 +314,9 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -343,25 +347,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>223525</v>
+            <v>244920</v>
           </cell>
           <cell r="H3">
-            <v>218722</v>
+            <v>240117</v>
           </cell>
           <cell r="I3">
-            <v>27340.25</v>
+            <v>26679.666666666668</v>
           </cell>
           <cell r="J3">
-            <v>601485.5</v>
+            <v>586952.66666666674</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.33208734034476767</v>
+            <v>0.36387353270211603</v>
           </cell>
           <cell r="M3">
-            <v>-449566</v>
+            <v>-428171</v>
           </cell>
         </row>
         <row r="4">
@@ -372,10 +376,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>9064</v>
+            <v>10060</v>
           </cell>
           <cell r="D4">
-            <v>1133</v>
+            <v>1117.7777777777778</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -404,10 +408,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>677</v>
+            <v>699</v>
           </cell>
           <cell r="D5">
-            <v>84.625</v>
+            <v>77.666666666666671</v>
           </cell>
           <cell r="G5">
             <v>4803</v>
@@ -416,16 +420,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46276</v>
+            <v>46279</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="L5">
-            <v>14</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="6">
@@ -436,10 +440,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>3432</v>
+            <v>3800</v>
           </cell>
           <cell r="D6">
-            <v>429</v>
+            <v>422.22222222222223</v>
           </cell>
         </row>
         <row r="7">
@@ -450,10 +454,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>840</v>
+            <v>875</v>
           </cell>
           <cell r="D7">
-            <v>105</v>
+            <v>97.222222222222229</v>
           </cell>
         </row>
         <row r="8">
@@ -464,10 +468,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>112</v>
+            <v>119</v>
           </cell>
           <cell r="D8">
-            <v>14</v>
+            <v>13.222222222222221</v>
           </cell>
         </row>
         <row r="9">
@@ -478,10 +482,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>10701</v>
+            <v>11835</v>
           </cell>
           <cell r="D9">
-            <v>1337.625</v>
+            <v>1315</v>
           </cell>
         </row>
         <row r="10">
@@ -492,10 +496,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>1082</v>
+            <v>1188</v>
           </cell>
           <cell r="D10">
-            <v>135.25</v>
+            <v>132</v>
           </cell>
         </row>
         <row r="11">
@@ -506,10 +510,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>2258</v>
+            <v>2450</v>
           </cell>
           <cell r="D11">
-            <v>282.25</v>
+            <v>272.22222222222223</v>
           </cell>
         </row>
         <row r="12">
@@ -520,10 +524,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>5774</v>
+            <v>6188</v>
           </cell>
           <cell r="D12">
-            <v>721.75</v>
+            <v>687.55555555555554</v>
           </cell>
         </row>
         <row r="13">
@@ -534,10 +538,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>2607</v>
+            <v>2885</v>
           </cell>
           <cell r="D13">
-            <v>325.875</v>
+            <v>320.55555555555554</v>
           </cell>
         </row>
         <row r="14">
@@ -548,10 +552,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>26908</v>
+            <v>29472</v>
           </cell>
           <cell r="D14">
-            <v>3363.5</v>
+            <v>3274.6666666666665</v>
           </cell>
         </row>
         <row r="15">
@@ -562,10 +566,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>16353</v>
+            <v>18119</v>
           </cell>
           <cell r="D15">
-            <v>2044.125</v>
+            <v>2013.2222222222222</v>
           </cell>
         </row>
         <row r="16">
@@ -576,10 +580,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>17448</v>
+            <v>19042</v>
           </cell>
           <cell r="D16">
-            <v>2181</v>
+            <v>2115.7777777777778</v>
           </cell>
         </row>
         <row r="17">
@@ -590,10 +594,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>20714</v>
+            <v>22752</v>
           </cell>
           <cell r="D17">
-            <v>2589.25</v>
+            <v>2528</v>
           </cell>
         </row>
         <row r="18">
@@ -604,10 +608,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>5529</v>
+            <v>6107</v>
           </cell>
           <cell r="D18">
-            <v>691.125</v>
+            <v>678.55555555555554</v>
           </cell>
         </row>
         <row r="19">
@@ -618,10 +622,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>6699</v>
+            <v>7290</v>
           </cell>
           <cell r="D19">
-            <v>837.375</v>
+            <v>810</v>
           </cell>
         </row>
         <row r="20">
@@ -632,10 +636,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>6582</v>
+            <v>7201</v>
           </cell>
           <cell r="D20">
-            <v>822.75</v>
+            <v>800.11111111111109</v>
           </cell>
         </row>
         <row r="21">
@@ -646,10 +650,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>2049</v>
+            <v>2275</v>
           </cell>
           <cell r="D21">
-            <v>256.125</v>
+            <v>252.77777777777777</v>
           </cell>
         </row>
         <row r="22">
@@ -660,10 +664,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>961</v>
+            <v>1072</v>
           </cell>
           <cell r="D22">
-            <v>120.125</v>
+            <v>119.11111111111111</v>
           </cell>
         </row>
         <row r="23">
@@ -674,10 +678,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>4233</v>
+            <v>4508</v>
           </cell>
           <cell r="D23">
-            <v>529.125</v>
+            <v>500.88888888888891</v>
           </cell>
         </row>
         <row r="24">
@@ -688,10 +692,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>6800</v>
+            <v>7394</v>
           </cell>
           <cell r="D24">
-            <v>850</v>
+            <v>821.55555555555554</v>
           </cell>
         </row>
         <row r="25">
@@ -705,7 +709,7 @@
             <v>620</v>
           </cell>
           <cell r="D25">
-            <v>77.5</v>
+            <v>68.888888888888886</v>
           </cell>
         </row>
         <row r="26">
@@ -716,10 +720,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>5247</v>
+            <v>5936</v>
           </cell>
           <cell r="D26">
-            <v>655.875</v>
+            <v>659.55555555555554</v>
           </cell>
         </row>
         <row r="27">
@@ -730,10 +734,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>7711</v>
+            <v>8619</v>
           </cell>
           <cell r="D27">
-            <v>963.875</v>
+            <v>957.66666666666663</v>
           </cell>
         </row>
         <row r="28">
@@ -744,10 +748,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>4104</v>
+            <v>4587</v>
           </cell>
           <cell r="D28">
-            <v>513</v>
+            <v>509.66666666666669</v>
           </cell>
         </row>
         <row r="29">
@@ -758,10 +762,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>2795</v>
+            <v>3399</v>
           </cell>
           <cell r="D29">
-            <v>349.375</v>
+            <v>377.66666666666669</v>
           </cell>
         </row>
         <row r="30">
@@ -772,10 +776,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>1717</v>
+            <v>1919</v>
           </cell>
           <cell r="D30">
-            <v>214.625</v>
+            <v>213.22222222222223</v>
           </cell>
         </row>
         <row r="31">
@@ -786,10 +790,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>2058</v>
+            <v>2232</v>
           </cell>
           <cell r="D31">
-            <v>257.25</v>
+            <v>248</v>
           </cell>
         </row>
         <row r="32">
@@ -800,10 +804,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>1025</v>
+            <v>1112</v>
           </cell>
           <cell r="D32">
-            <v>128.125</v>
+            <v>123.55555555555556</v>
           </cell>
         </row>
         <row r="33">
@@ -814,10 +818,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>1050</v>
+            <v>1148</v>
           </cell>
           <cell r="D33">
-            <v>131.25</v>
+            <v>127.55555555555556</v>
           </cell>
         </row>
         <row r="34">
@@ -828,10 +832,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>6142</v>
+            <v>6731</v>
           </cell>
           <cell r="D34">
-            <v>767.75</v>
+            <v>747.88888888888891</v>
           </cell>
         </row>
         <row r="35">
@@ -842,10 +846,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>4726</v>
+            <v>5173</v>
           </cell>
           <cell r="D35">
-            <v>590.75</v>
+            <v>574.77777777777783</v>
           </cell>
         </row>
         <row r="36">
@@ -856,10 +860,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>6389</v>
+            <v>6824</v>
           </cell>
           <cell r="D36">
-            <v>798.625</v>
+            <v>758.22222222222217</v>
           </cell>
         </row>
         <row r="37">
@@ -870,10 +874,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>3896</v>
+            <v>4256</v>
           </cell>
           <cell r="D37">
-            <v>487</v>
+            <v>472.88888888888891</v>
           </cell>
         </row>
         <row r="38">
@@ -884,10 +888,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>32</v>
+            <v>46</v>
           </cell>
           <cell r="D38">
-            <v>4</v>
+            <v>5.1111111111111107</v>
           </cell>
         </row>
         <row r="39">
@@ -901,7 +905,7 @@
             <v>6</v>
           </cell>
           <cell r="D39">
-            <v>0.75</v>
+            <v>0.66666666666666663</v>
           </cell>
         </row>
         <row r="40">
@@ -912,10 +916,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>1140</v>
+            <v>1295</v>
           </cell>
           <cell r="D40">
-            <v>142.5</v>
+            <v>143.88888888888889</v>
           </cell>
         </row>
         <row r="41">
@@ -926,10 +930,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>4182</v>
+            <v>4583</v>
           </cell>
           <cell r="D41">
-            <v>522.75</v>
+            <v>509.22222222222223</v>
           </cell>
         </row>
         <row r="42">
@@ -940,10 +944,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>3404</v>
+            <v>3741</v>
           </cell>
           <cell r="D42">
-            <v>425.5</v>
+            <v>415.66666666666669</v>
           </cell>
         </row>
         <row r="43">
@@ -954,10 +958,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>1477</v>
+            <v>1599</v>
           </cell>
           <cell r="D43">
-            <v>184.625</v>
+            <v>177.66666666666666</v>
           </cell>
         </row>
         <row r="44">
@@ -968,10 +972,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>3785</v>
+            <v>4152</v>
           </cell>
           <cell r="D44">
-            <v>473.125</v>
+            <v>461.33333333333331</v>
           </cell>
         </row>
         <row r="45">
@@ -982,10 +986,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>2519</v>
+            <v>2662</v>
           </cell>
           <cell r="D45">
-            <v>314.875</v>
+            <v>295.77777777777777</v>
           </cell>
         </row>
         <row r="46">
@@ -996,10 +1000,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>1785</v>
+            <v>1894</v>
           </cell>
           <cell r="D46">
-            <v>223.125</v>
+            <v>210.44444444444446</v>
           </cell>
         </row>
         <row r="47">
@@ -1010,10 +1014,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>241</v>
+            <v>284</v>
           </cell>
           <cell r="D47">
-            <v>30.125</v>
+            <v>31.555555555555557</v>
           </cell>
         </row>
         <row r="48">
@@ -1024,10 +1028,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>902</v>
+            <v>973</v>
           </cell>
           <cell r="D48">
-            <v>112.75</v>
+            <v>108.11111111111111</v>
           </cell>
         </row>
         <row r="49">
@@ -1038,10 +1042,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>382</v>
+            <v>410</v>
           </cell>
           <cell r="D49">
-            <v>47.75</v>
+            <v>45.555555555555557</v>
           </cell>
         </row>
         <row r="50">
@@ -1052,14 +1056,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>564</v>
+            <v>585</v>
           </cell>
           <cell r="D50">
-            <v>70.5</v>
+            <v>65</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1406,11 +1410,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>9064</v>
+        <v>10060</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1133</v>
+        <v>1117.7777777777778</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,11 +1428,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>677</v>
+        <v>699</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>84.625</v>
+        <v>77.666666666666671</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1442,11 +1446,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>3432</v>
+        <v>3800</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>429</v>
+        <v>422.22222222222223</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1460,11 +1464,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>840</v>
+        <v>875</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>105</v>
+        <v>97.222222222222229</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,11 +1482,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>14</v>
+        <v>13.222222222222221</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1496,11 +1500,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>10701</v>
+        <v>11835</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1337.625</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1514,11 +1518,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1082</v>
+        <v>1188</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>135.25</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1532,11 +1536,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>2258</v>
+        <v>2450</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>282.25</v>
+        <v>272.22222222222223</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1550,11 +1554,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>5774</v>
+        <v>6188</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>721.75</v>
+        <v>687.55555555555554</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1568,11 +1572,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>2607</v>
+        <v>2885</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>325.875</v>
+        <v>320.55555555555554</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1586,11 +1590,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>26908</v>
+        <v>29472</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3363.5</v>
+        <v>3274.6666666666665</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,11 +1608,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>16353</v>
+        <v>18119</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2044.125</v>
+        <v>2013.2222222222222</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1622,11 +1626,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>17448</v>
+        <v>19042</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2181</v>
+        <v>2115.7777777777778</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1640,11 +1644,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>20714</v>
+        <v>22752</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2589.25</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1658,11 +1662,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>5529</v>
+        <v>6107</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>691.125</v>
+        <v>678.55555555555554</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1676,11 +1680,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>6699</v>
+        <v>7290</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>837.375</v>
+        <v>810</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1694,11 +1698,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>6582</v>
+        <v>7201</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>822.75</v>
+        <v>800.11111111111109</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1712,11 +1716,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>2049</v>
+        <v>2275</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>256.125</v>
+        <v>252.77777777777777</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,11 +1734,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>961</v>
+        <v>1072</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>120.125</v>
+        <v>119.11111111111111</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1748,11 +1752,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>4233</v>
+        <v>4508</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>529.125</v>
+        <v>500.88888888888891</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1766,11 +1770,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>6800</v>
+        <v>7394</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>850</v>
+        <v>821.55555555555554</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1788,7 +1792,7 @@
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>77.5</v>
+        <v>68.888888888888886</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1802,11 +1806,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>5247</v>
+        <v>5936</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>655.875</v>
+        <v>659.55555555555554</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1820,11 +1824,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>7711</v>
+        <v>8619</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>963.875</v>
+        <v>957.66666666666663</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1838,11 +1842,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>4104</v>
+        <v>4587</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>513</v>
+        <v>509.66666666666669</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1856,11 +1860,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>2795</v>
+        <v>3399</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>349.375</v>
+        <v>377.66666666666669</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1874,11 +1878,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1717</v>
+        <v>1919</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>214.625</v>
+        <v>213.22222222222223</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1892,11 +1896,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>2058</v>
+        <v>2232</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>257.25</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1910,11 +1914,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1025</v>
+        <v>1112</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>128.125</v>
+        <v>123.55555555555556</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1928,11 +1932,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1050</v>
+        <v>1148</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>131.25</v>
+        <v>127.55555555555556</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,11 +1950,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>6142</v>
+        <v>6731</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>767.75</v>
+        <v>747.88888888888891</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1964,11 +1968,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>4726</v>
+        <v>5173</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>590.75</v>
+        <v>574.77777777777783</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1982,11 +1986,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>6389</v>
+        <v>6824</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>798.625</v>
+        <v>758.22222222222217</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2000,11 +2004,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>3896</v>
+        <v>4256</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>487</v>
+        <v>472.88888888888891</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2018,11 +2022,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4</v>
+        <v>5.1111111111111107</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2040,7 +2044,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2054,11 +2058,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1140</v>
+        <v>1295</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>142.5</v>
+        <v>143.88888888888889</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2072,11 +2076,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>4182</v>
+        <v>4583</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>522.75</v>
+        <v>509.22222222222223</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2090,11 +2094,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>3404</v>
+        <v>3741</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>425.5</v>
+        <v>415.66666666666669</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2108,11 +2112,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1477</v>
+        <v>1599</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>184.625</v>
+        <v>177.66666666666666</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2126,11 +2130,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>3785</v>
+        <v>4152</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>473.125</v>
+        <v>461.33333333333331</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2144,11 +2148,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>2519</v>
+        <v>2662</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>314.875</v>
+        <v>295.77777777777777</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2162,11 +2166,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>1785</v>
+        <v>1894</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>223.125</v>
+        <v>210.44444444444446</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2180,11 +2184,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>30.125</v>
+        <v>31.555555555555557</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2198,11 +2202,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>902</v>
+        <v>973</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>112.75</v>
+        <v>108.11111111111111</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2216,11 +2220,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>47.75</v>
+        <v>45.555555555555557</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2234,11 +2238,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>70.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2303,19 +2307,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>223525</v>
+        <v>244920</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>218722</v>
+        <v>240117</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>27340.25</v>
+        <v>26679.666666666668</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>601485.5</v>
+        <v>586952.66666666674</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2323,11 +2327,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.33208734034476767</v>
+        <v>0.36387353270211603</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-449566</v>
+        <v>-428171</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2368,7 +2372,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2376,11 +2380,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E921ED5-0C75-4C61-A177-FF878B42D9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94795063-C67F-440E-AE32-3DD8800CA378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -347,25 +347,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>244920</v>
+            <v>282655</v>
           </cell>
           <cell r="H3">
-            <v>240117</v>
+            <v>277852</v>
           </cell>
           <cell r="I3">
-            <v>26679.666666666668</v>
+            <v>27785.200000000001</v>
           </cell>
           <cell r="J3">
-            <v>586952.66666666674</v>
+            <v>611274.4</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.36387353270211603</v>
+            <v>0.41993578877150339</v>
           </cell>
           <cell r="M3">
-            <v>-428171</v>
+            <v>-390436</v>
           </cell>
         </row>
         <row r="4">
@@ -376,10 +376,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>10060</v>
+            <v>12153</v>
           </cell>
           <cell r="D4">
-            <v>1117.7777777777778</v>
+            <v>1215.3</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -408,10 +408,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>699</v>
+            <v>742</v>
           </cell>
           <cell r="D5">
-            <v>77.666666666666671</v>
+            <v>74.2</v>
           </cell>
           <cell r="G5">
             <v>4803</v>
@@ -420,16 +420,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46279</v>
+            <v>46280</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="L5">
-            <v>13</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="6">
@@ -440,10 +440,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>3800</v>
+            <v>4846</v>
           </cell>
           <cell r="D6">
-            <v>422.22222222222223</v>
+            <v>484.6</v>
           </cell>
         </row>
         <row r="7">
@@ -454,10 +454,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>875</v>
+            <v>1080</v>
           </cell>
           <cell r="D7">
-            <v>97.222222222222229</v>
+            <v>108</v>
           </cell>
         </row>
         <row r="8">
@@ -468,10 +468,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>119</v>
+            <v>151</v>
           </cell>
           <cell r="D8">
-            <v>13.222222222222221</v>
+            <v>15.1</v>
           </cell>
         </row>
         <row r="9">
@@ -482,10 +482,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>11835</v>
+            <v>14773</v>
           </cell>
           <cell r="D9">
-            <v>1315</v>
+            <v>1477.3</v>
           </cell>
         </row>
         <row r="10">
@@ -496,10 +496,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>1188</v>
+            <v>1369</v>
           </cell>
           <cell r="D10">
-            <v>132</v>
+            <v>136.9</v>
           </cell>
         </row>
         <row r="11">
@@ -510,10 +510,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>2450</v>
+            <v>2687</v>
           </cell>
           <cell r="D11">
-            <v>272.22222222222223</v>
+            <v>268.7</v>
           </cell>
         </row>
         <row r="12">
@@ -524,10 +524,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>6188</v>
+            <v>6876</v>
           </cell>
           <cell r="D12">
-            <v>687.55555555555554</v>
+            <v>687.6</v>
           </cell>
         </row>
         <row r="13">
@@ -538,10 +538,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>2885</v>
+            <v>3200</v>
           </cell>
           <cell r="D13">
-            <v>320.55555555555554</v>
+            <v>320</v>
           </cell>
         </row>
         <row r="14">
@@ -552,10 +552,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>29472</v>
+            <v>34761</v>
           </cell>
           <cell r="D14">
-            <v>3274.6666666666665</v>
+            <v>3476.1</v>
           </cell>
         </row>
         <row r="15">
@@ -566,10 +566,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>18119</v>
+            <v>21304</v>
           </cell>
           <cell r="D15">
-            <v>2013.2222222222222</v>
+            <v>2130.4</v>
           </cell>
         </row>
         <row r="16">
@@ -580,10 +580,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>19042</v>
+            <v>21893</v>
           </cell>
           <cell r="D16">
-            <v>2115.7777777777778</v>
+            <v>2189.3000000000002</v>
           </cell>
         </row>
         <row r="17">
@@ -594,10 +594,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>22752</v>
+            <v>26554</v>
           </cell>
           <cell r="D17">
-            <v>2528</v>
+            <v>2655.4</v>
           </cell>
         </row>
         <row r="18">
@@ -608,10 +608,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>6107</v>
+            <v>6692</v>
           </cell>
           <cell r="D18">
-            <v>678.55555555555554</v>
+            <v>669.2</v>
           </cell>
         </row>
         <row r="19">
@@ -622,10 +622,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>7290</v>
+            <v>8064</v>
           </cell>
           <cell r="D19">
-            <v>810</v>
+            <v>806.4</v>
           </cell>
         </row>
         <row r="20">
@@ -636,10 +636,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>7201</v>
+            <v>7950</v>
           </cell>
           <cell r="D20">
-            <v>800.11111111111109</v>
+            <v>795</v>
           </cell>
         </row>
         <row r="21">
@@ -650,10 +650,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>2275</v>
+            <v>2498</v>
           </cell>
           <cell r="D21">
-            <v>252.77777777777777</v>
+            <v>249.8</v>
           </cell>
         </row>
         <row r="22">
@@ -664,10 +664,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>1072</v>
+            <v>1210</v>
           </cell>
           <cell r="D22">
-            <v>119.11111111111111</v>
+            <v>121</v>
           </cell>
         </row>
         <row r="23">
@@ -678,10 +678,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>4508</v>
+            <v>4918</v>
           </cell>
           <cell r="D23">
-            <v>500.88888888888891</v>
+            <v>491.8</v>
           </cell>
         </row>
         <row r="24">
@@ -692,10 +692,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>7394</v>
+            <v>8077</v>
           </cell>
           <cell r="D24">
-            <v>821.55555555555554</v>
+            <v>807.7</v>
           </cell>
         </row>
         <row r="25">
@@ -709,7 +709,7 @@
             <v>620</v>
           </cell>
           <cell r="D25">
-            <v>68.888888888888886</v>
+            <v>62</v>
           </cell>
         </row>
         <row r="26">
@@ -720,10 +720,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>5936</v>
+            <v>7053</v>
           </cell>
           <cell r="D26">
-            <v>659.55555555555554</v>
+            <v>705.3</v>
           </cell>
         </row>
         <row r="27">
@@ -734,10 +734,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>8619</v>
+            <v>11068</v>
           </cell>
           <cell r="D27">
-            <v>957.66666666666663</v>
+            <v>1106.8</v>
           </cell>
         </row>
         <row r="28">
@@ -748,10 +748,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>4587</v>
+            <v>5171</v>
           </cell>
           <cell r="D28">
-            <v>509.66666666666669</v>
+            <v>517.1</v>
           </cell>
         </row>
         <row r="29">
@@ -762,10 +762,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>3399</v>
+            <v>3866</v>
           </cell>
           <cell r="D29">
-            <v>377.66666666666669</v>
+            <v>386.6</v>
           </cell>
         </row>
         <row r="30">
@@ -776,10 +776,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>1919</v>
+            <v>2361</v>
           </cell>
           <cell r="D30">
-            <v>213.22222222222223</v>
+            <v>236.1</v>
           </cell>
         </row>
         <row r="31">
@@ -790,10 +790,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>2232</v>
+            <v>2839</v>
           </cell>
           <cell r="D31">
-            <v>248</v>
+            <v>283.89999999999998</v>
           </cell>
         </row>
         <row r="32">
@@ -804,10 +804,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>1112</v>
+            <v>1274</v>
           </cell>
           <cell r="D32">
-            <v>123.55555555555556</v>
+            <v>127.4</v>
           </cell>
         </row>
         <row r="33">
@@ -818,10 +818,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>1148</v>
+            <v>1299</v>
           </cell>
           <cell r="D33">
-            <v>127.55555555555556</v>
+            <v>129.9</v>
           </cell>
         </row>
         <row r="34">
@@ -832,10 +832,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>6731</v>
+            <v>7493</v>
           </cell>
           <cell r="D34">
-            <v>747.88888888888891</v>
+            <v>749.3</v>
           </cell>
         </row>
         <row r="35">
@@ -846,10 +846,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>5173</v>
+            <v>5789</v>
           </cell>
           <cell r="D35">
-            <v>574.77777777777783</v>
+            <v>578.9</v>
           </cell>
         </row>
         <row r="36">
@@ -860,10 +860,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>6824</v>
+            <v>7718</v>
           </cell>
           <cell r="D36">
-            <v>758.22222222222217</v>
+            <v>771.8</v>
           </cell>
         </row>
         <row r="37">
@@ -874,10 +874,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>4256</v>
+            <v>4936</v>
           </cell>
           <cell r="D37">
-            <v>472.88888888888891</v>
+            <v>493.6</v>
           </cell>
         </row>
         <row r="38">
@@ -888,10 +888,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>46</v>
+            <v>48</v>
           </cell>
           <cell r="D38">
-            <v>5.1111111111111107</v>
+            <v>4.8</v>
           </cell>
         </row>
         <row r="39">
@@ -902,10 +902,10 @@
             <v>Cremigurt Griego Dulce 4 Kg</v>
           </cell>
           <cell r="C39">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="D39">
-            <v>0.66666666666666663</v>
+            <v>0.7</v>
           </cell>
         </row>
         <row r="40">
@@ -916,10 +916,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>1295</v>
+            <v>1476</v>
           </cell>
           <cell r="D40">
-            <v>143.88888888888889</v>
+            <v>147.6</v>
           </cell>
         </row>
         <row r="41">
@@ -930,10 +930,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>4583</v>
+            <v>5127</v>
           </cell>
           <cell r="D41">
-            <v>509.22222222222223</v>
+            <v>512.70000000000005</v>
           </cell>
         </row>
         <row r="42">
@@ -944,10 +944,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>3741</v>
+            <v>4097</v>
           </cell>
           <cell r="D42">
-            <v>415.66666666666669</v>
+            <v>409.7</v>
           </cell>
         </row>
         <row r="43">
@@ -958,10 +958,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>1599</v>
+            <v>1819</v>
           </cell>
           <cell r="D43">
-            <v>177.66666666666666</v>
+            <v>181.9</v>
           </cell>
         </row>
         <row r="44">
@@ -972,10 +972,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>4152</v>
+            <v>4554</v>
           </cell>
           <cell r="D44">
-            <v>461.33333333333331</v>
+            <v>455.4</v>
           </cell>
         </row>
         <row r="45">
@@ -986,10 +986,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>2662</v>
+            <v>2879</v>
           </cell>
           <cell r="D45">
-            <v>295.77777777777777</v>
+            <v>287.89999999999998</v>
           </cell>
         </row>
         <row r="46">
@@ -1000,10 +1000,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>1894</v>
+            <v>2117</v>
           </cell>
           <cell r="D46">
-            <v>210.44444444444446</v>
+            <v>211.7</v>
           </cell>
         </row>
         <row r="47">
@@ -1014,10 +1014,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>284</v>
+            <v>312</v>
           </cell>
           <cell r="D47">
-            <v>31.555555555555557</v>
+            <v>31.2</v>
           </cell>
         </row>
         <row r="48">
@@ -1028,10 +1028,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>973</v>
+            <v>1070</v>
           </cell>
           <cell r="D48">
-            <v>108.11111111111111</v>
+            <v>107</v>
           </cell>
         </row>
         <row r="49">
@@ -1042,10 +1042,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>410</v>
+            <v>443</v>
           </cell>
           <cell r="D49">
-            <v>45.555555555555557</v>
+            <v>44.3</v>
           </cell>
         </row>
         <row r="50">
@@ -1056,10 +1056,10 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>585</v>
+            <v>618</v>
           </cell>
           <cell r="D50">
-            <v>65</v>
+            <v>61.8</v>
           </cell>
         </row>
       </sheetData>
@@ -1410,11 +1410,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>10060</v>
+        <v>12153</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1117.7777777777778</v>
+        <v>1215.3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>699</v>
+        <v>742</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>77.666666666666671</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1446,11 +1446,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>3800</v>
+        <v>4846</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>422.22222222222223</v>
+        <v>484.6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,11 +1464,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>875</v>
+        <v>1080</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>97.222222222222229</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1482,11 +1482,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>13.222222222222221</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1500,11 +1500,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>11835</v>
+        <v>14773</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1315</v>
+        <v>1477.3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1188</v>
+        <v>1369</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>132</v>
+        <v>136.9</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,11 +1536,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>2450</v>
+        <v>2687</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>272.22222222222223</v>
+        <v>268.7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1554,11 +1554,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>6188</v>
+        <v>6876</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>687.55555555555554</v>
+        <v>687.6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1572,11 +1572,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>2885</v>
+        <v>3200</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>320.55555555555554</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,11 +1590,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>29472</v>
+        <v>34761</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3274.6666666666665</v>
+        <v>3476.1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>18119</v>
+        <v>21304</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2013.2222222222222</v>
+        <v>2130.4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>19042</v>
+        <v>21893</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2115.7777777777778</v>
+        <v>2189.3000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1644,11 +1644,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>22752</v>
+        <v>26554</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2528</v>
+        <v>2655.4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,11 +1662,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>6107</v>
+        <v>6692</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>678.55555555555554</v>
+        <v>669.2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1680,11 +1680,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>7290</v>
+        <v>8064</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>810</v>
+        <v>806.4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>7201</v>
+        <v>7950</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>800.11111111111109</v>
+        <v>795</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,11 +1716,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>2275</v>
+        <v>2498</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>252.77777777777777</v>
+        <v>249.8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1734,11 +1734,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1072</v>
+        <v>1210</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>119.11111111111111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1752,11 +1752,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>4508</v>
+        <v>4918</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>500.88888888888891</v>
+        <v>491.8</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1770,11 +1770,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>7394</v>
+        <v>8077</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>821.55555555555554</v>
+        <v>807.7</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>68.888888888888886</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1806,11 +1806,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>5936</v>
+        <v>7053</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>659.55555555555554</v>
+        <v>705.3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1824,11 +1824,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>8619</v>
+        <v>11068</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>957.66666666666663</v>
+        <v>1106.8</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1842,11 +1842,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>4587</v>
+        <v>5171</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>509.66666666666669</v>
+        <v>517.1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1860,11 +1860,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>3399</v>
+        <v>3866</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>377.66666666666669</v>
+        <v>386.6</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1878,11 +1878,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1919</v>
+        <v>2361</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>213.22222222222223</v>
+        <v>236.1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1896,11 +1896,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>2232</v>
+        <v>2839</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>248</v>
+        <v>283.89999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1914,11 +1914,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1112</v>
+        <v>1274</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>123.55555555555556</v>
+        <v>127.4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1148</v>
+        <v>1299</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>127.55555555555556</v>
+        <v>129.9</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1950,11 +1950,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>6731</v>
+        <v>7493</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>747.88888888888891</v>
+        <v>749.3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>5173</v>
+        <v>5789</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>574.77777777777783</v>
+        <v>578.9</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1986,11 +1986,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>6824</v>
+        <v>7718</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>758.22222222222217</v>
+        <v>771.8</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2004,11 +2004,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>4256</v>
+        <v>4936</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>472.88888888888891</v>
+        <v>493.6</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2022,11 +2022,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>5.1111111111111107</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2040,11 +2040,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.66666666666666663</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1295</v>
+        <v>1476</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>143.88888888888889</v>
+        <v>147.6</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2076,11 +2076,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>4583</v>
+        <v>5127</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>509.22222222222223</v>
+        <v>512.70000000000005</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2094,11 +2094,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>3741</v>
+        <v>4097</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>415.66666666666669</v>
+        <v>409.7</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2112,11 +2112,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1599</v>
+        <v>1819</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>177.66666666666666</v>
+        <v>181.9</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2130,11 +2130,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>4152</v>
+        <v>4554</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>461.33333333333331</v>
+        <v>455.4</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>2662</v>
+        <v>2879</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>295.77777777777777</v>
+        <v>287.89999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2166,11 +2166,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>1894</v>
+        <v>2117</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>210.44444444444446</v>
+        <v>211.7</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2184,11 +2184,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>31.555555555555557</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2202,11 +2202,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>973</v>
+        <v>1070</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>108.11111111111111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2220,11 +2220,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>410</v>
+        <v>443</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>45.555555555555557</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2238,11 +2238,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>585</v>
+        <v>618</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>65</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2307,19 +2307,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>244920</v>
+        <v>282655</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>240117</v>
+        <v>277852</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26679.666666666668</v>
+        <v>27785.200000000001</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>586952.66666666674</v>
+        <v>611274.4</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2327,11 +2327,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.36387353270211603</v>
+        <v>0.41993578877150339</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-428171</v>
+        <v>-390436</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2380,11 +2380,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94795063-C67F-440E-AE32-3DD8800CA378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6373D99A-355E-473D-A0B0-0845F29E6EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -299,6 +299,8 @@
       <sheetName val="INVENTARIO NACIONAL 10-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 11-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 15-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 16-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -316,7 +318,9 @@
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -347,25 +351,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>282655</v>
+            <v>320287</v>
           </cell>
           <cell r="H3">
-            <v>277852</v>
+            <v>315484</v>
           </cell>
           <cell r="I3">
-            <v>27785.200000000001</v>
+            <v>28680.363636363636</v>
           </cell>
           <cell r="J3">
-            <v>611274.4</v>
+            <v>630968</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.41993578877150339</v>
+            <v>0.47584501946987851</v>
           </cell>
           <cell r="M3">
-            <v>-390436</v>
+            <v>-352804</v>
           </cell>
         </row>
         <row r="4">
@@ -376,10 +380,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>12153</v>
+            <v>13833</v>
           </cell>
           <cell r="D4">
-            <v>1215.3</v>
+            <v>1257.5454545454545</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -408,10 +412,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>742</v>
+            <v>777</v>
           </cell>
           <cell r="D5">
-            <v>74.2</v>
+            <v>70.63636363636364</v>
           </cell>
           <cell r="G5">
             <v>4803</v>
@@ -420,16 +424,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46280</v>
+            <v>46281</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>10</v>
+            <v>11</v>
           </cell>
           <cell r="L5">
-            <v>12</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="6">
@@ -440,10 +444,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>4846</v>
+            <v>5628</v>
           </cell>
           <cell r="D6">
-            <v>484.6</v>
+            <v>511.63636363636363</v>
           </cell>
         </row>
         <row r="7">
@@ -454,10 +458,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1080</v>
+            <v>1352</v>
           </cell>
           <cell r="D7">
-            <v>108</v>
+            <v>122.90909090909091</v>
           </cell>
         </row>
         <row r="8">
@@ -468,10 +472,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>151</v>
+            <v>169</v>
           </cell>
           <cell r="D8">
-            <v>15.1</v>
+            <v>15.363636363636363</v>
           </cell>
         </row>
         <row r="9">
@@ -482,10 +486,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>14773</v>
+            <v>16066</v>
           </cell>
           <cell r="D9">
-            <v>1477.3</v>
+            <v>1460.5454545454545</v>
           </cell>
         </row>
         <row r="10">
@@ -496,10 +500,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>1369</v>
+            <v>1608</v>
           </cell>
           <cell r="D10">
-            <v>136.9</v>
+            <v>146.18181818181819</v>
           </cell>
         </row>
         <row r="11">
@@ -510,10 +514,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>2687</v>
+            <v>3066</v>
           </cell>
           <cell r="D11">
-            <v>268.7</v>
+            <v>278.72727272727275</v>
           </cell>
         </row>
         <row r="12">
@@ -524,10 +528,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>6876</v>
+            <v>8050</v>
           </cell>
           <cell r="D12">
-            <v>687.6</v>
+            <v>731.81818181818187</v>
           </cell>
         </row>
         <row r="13">
@@ -538,10 +542,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>3200</v>
+            <v>3908</v>
           </cell>
           <cell r="D13">
-            <v>320</v>
+            <v>355.27272727272725</v>
           </cell>
         </row>
         <row r="14">
@@ -552,10 +556,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>34761</v>
+            <v>38956</v>
           </cell>
           <cell r="D14">
-            <v>3476.1</v>
+            <v>3541.4545454545455</v>
           </cell>
         </row>
         <row r="15">
@@ -566,10 +570,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>21304</v>
+            <v>23927</v>
           </cell>
           <cell r="D15">
-            <v>2130.4</v>
+            <v>2175.181818181818</v>
           </cell>
         </row>
         <row r="16">
@@ -580,10 +584,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>21893</v>
+            <v>24425</v>
           </cell>
           <cell r="D16">
-            <v>2189.3000000000002</v>
+            <v>2220.4545454545455</v>
           </cell>
         </row>
         <row r="17">
@@ -594,10 +598,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>26554</v>
+            <v>29796</v>
           </cell>
           <cell r="D17">
-            <v>2655.4</v>
+            <v>2708.7272727272725</v>
           </cell>
         </row>
         <row r="18">
@@ -608,10 +612,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>6692</v>
+            <v>7754</v>
           </cell>
           <cell r="D18">
-            <v>669.2</v>
+            <v>704.90909090909088</v>
           </cell>
         </row>
         <row r="19">
@@ -622,10 +626,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>8064</v>
+            <v>9383</v>
           </cell>
           <cell r="D19">
-            <v>806.4</v>
+            <v>853</v>
           </cell>
         </row>
         <row r="20">
@@ -636,10 +640,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>7950</v>
+            <v>9525</v>
           </cell>
           <cell r="D20">
-            <v>795</v>
+            <v>865.90909090909088</v>
           </cell>
         </row>
         <row r="21">
@@ -650,10 +654,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>2498</v>
+            <v>2827</v>
           </cell>
           <cell r="D21">
-            <v>249.8</v>
+            <v>257</v>
           </cell>
         </row>
         <row r="22">
@@ -664,10 +668,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>1210</v>
+            <v>1365</v>
           </cell>
           <cell r="D22">
-            <v>121</v>
+            <v>124.09090909090909</v>
           </cell>
         </row>
         <row r="23">
@@ -678,10 +682,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>4918</v>
+            <v>5649</v>
           </cell>
           <cell r="D23">
-            <v>491.8</v>
+            <v>513.5454545454545</v>
           </cell>
         </row>
         <row r="24">
@@ -692,10 +696,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>8077</v>
+            <v>9381</v>
           </cell>
           <cell r="D24">
-            <v>807.7</v>
+            <v>852.81818181818187</v>
           </cell>
         </row>
         <row r="25">
@@ -706,10 +710,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>620</v>
+            <v>630</v>
           </cell>
           <cell r="D25">
-            <v>62</v>
+            <v>57.272727272727273</v>
           </cell>
         </row>
         <row r="26">
@@ -720,10 +724,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>7053</v>
+            <v>7910</v>
           </cell>
           <cell r="D26">
-            <v>705.3</v>
+            <v>719.09090909090912</v>
           </cell>
         </row>
         <row r="27">
@@ -734,10 +738,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>11068</v>
+            <v>12404</v>
           </cell>
           <cell r="D27">
-            <v>1106.8</v>
+            <v>1127.6363636363637</v>
           </cell>
         </row>
         <row r="28">
@@ -748,10 +752,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>5171</v>
+            <v>6246</v>
           </cell>
           <cell r="D28">
-            <v>517.1</v>
+            <v>567.81818181818187</v>
           </cell>
         </row>
         <row r="29">
@@ -762,10 +766,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>3866</v>
+            <v>4767</v>
           </cell>
           <cell r="D29">
-            <v>386.6</v>
+            <v>433.36363636363637</v>
           </cell>
         </row>
         <row r="30">
@@ -776,10 +780,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>2361</v>
+            <v>2509</v>
           </cell>
           <cell r="D30">
-            <v>236.1</v>
+            <v>228.09090909090909</v>
           </cell>
         </row>
         <row r="31">
@@ -790,10 +794,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>2839</v>
+            <v>3025</v>
           </cell>
           <cell r="D31">
-            <v>283.89999999999998</v>
+            <v>275</v>
           </cell>
         </row>
         <row r="32">
@@ -804,10 +808,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>1274</v>
+            <v>1535</v>
           </cell>
           <cell r="D32">
-            <v>127.4</v>
+            <v>139.54545454545453</v>
           </cell>
         </row>
         <row r="33">
@@ -818,10 +822,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>1299</v>
+            <v>1532</v>
           </cell>
           <cell r="D33">
-            <v>129.9</v>
+            <v>139.27272727272728</v>
           </cell>
         </row>
         <row r="34">
@@ -832,10 +836,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>7493</v>
+            <v>8377</v>
           </cell>
           <cell r="D34">
-            <v>749.3</v>
+            <v>761.5454545454545</v>
           </cell>
         </row>
         <row r="35">
@@ -846,10 +850,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>5789</v>
+            <v>6675</v>
           </cell>
           <cell r="D35">
-            <v>578.9</v>
+            <v>606.81818181818187</v>
           </cell>
         </row>
         <row r="36">
@@ -860,10 +864,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>7718</v>
+            <v>8796</v>
           </cell>
           <cell r="D36">
-            <v>771.8</v>
+            <v>799.63636363636363</v>
           </cell>
         </row>
         <row r="37">
@@ -874,10 +878,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>4936</v>
+            <v>5829</v>
           </cell>
           <cell r="D37">
-            <v>493.6</v>
+            <v>529.90909090909088</v>
           </cell>
         </row>
         <row r="38">
@@ -888,10 +892,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>48</v>
+            <v>51</v>
           </cell>
           <cell r="D38">
-            <v>4.8</v>
+            <v>4.6363636363636367</v>
           </cell>
         </row>
         <row r="39">
@@ -905,7 +909,7 @@
             <v>7</v>
           </cell>
           <cell r="D39">
-            <v>0.7</v>
+            <v>0.63636363636363635</v>
           </cell>
         </row>
         <row r="40">
@@ -916,10 +920,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>1476</v>
+            <v>1667</v>
           </cell>
           <cell r="D40">
-            <v>147.6</v>
+            <v>151.54545454545453</v>
           </cell>
         </row>
         <row r="41">
@@ -930,10 +934,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>5127</v>
+            <v>5868</v>
           </cell>
           <cell r="D41">
-            <v>512.70000000000005</v>
+            <v>533.4545454545455</v>
           </cell>
         </row>
         <row r="42">
@@ -944,10 +948,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>4097</v>
+            <v>4588</v>
           </cell>
           <cell r="D42">
-            <v>409.7</v>
+            <v>417.09090909090907</v>
           </cell>
         </row>
         <row r="43">
@@ -958,10 +962,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>1819</v>
+            <v>2088</v>
           </cell>
           <cell r="D43">
-            <v>181.9</v>
+            <v>189.81818181818181</v>
           </cell>
         </row>
         <row r="44">
@@ -972,10 +976,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>4554</v>
+            <v>5105</v>
           </cell>
           <cell r="D44">
-            <v>455.4</v>
+            <v>464.09090909090907</v>
           </cell>
         </row>
         <row r="45">
@@ -986,10 +990,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>2879</v>
+            <v>3218</v>
           </cell>
           <cell r="D45">
-            <v>287.89999999999998</v>
+            <v>292.54545454545456</v>
           </cell>
         </row>
         <row r="46">
@@ -1000,10 +1004,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>2117</v>
+            <v>2417</v>
           </cell>
           <cell r="D46">
-            <v>211.7</v>
+            <v>219.72727272727272</v>
           </cell>
         </row>
         <row r="47">
@@ -1014,10 +1018,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>312</v>
+            <v>400</v>
           </cell>
           <cell r="D47">
-            <v>31.2</v>
+            <v>36.363636363636367</v>
           </cell>
         </row>
         <row r="48">
@@ -1028,10 +1032,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>1070</v>
+            <v>1218</v>
           </cell>
           <cell r="D48">
-            <v>107</v>
+            <v>110.72727272727273</v>
           </cell>
         </row>
         <row r="49">
@@ -1042,10 +1046,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>443</v>
+            <v>504</v>
           </cell>
           <cell r="D49">
-            <v>44.3</v>
+            <v>45.81818181818182</v>
           </cell>
         </row>
         <row r="50">
@@ -1056,14 +1060,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>618</v>
+            <v>673</v>
           </cell>
           <cell r="D50">
-            <v>61.8</v>
+            <v>61.18181818181818</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="12"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1410,11 +1414,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>12153</v>
+        <v>13833</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1215.3</v>
+        <v>1257.5454545454545</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1428,11 +1432,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>742</v>
+        <v>777</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>74.2</v>
+        <v>70.63636363636364</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1446,11 +1450,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>4846</v>
+        <v>5628</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>484.6</v>
+        <v>511.63636363636363</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,11 +1468,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1080</v>
+        <v>1352</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>108</v>
+        <v>122.90909090909091</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1482,11 +1486,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>15.1</v>
+        <v>15.363636363636363</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1500,11 +1504,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>14773</v>
+        <v>16066</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1477.3</v>
+        <v>1460.5454545454545</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,11 +1522,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1369</v>
+        <v>1608</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>136.9</v>
+        <v>146.18181818181819</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,11 +1540,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>2687</v>
+        <v>3066</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>268.7</v>
+        <v>278.72727272727275</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1554,11 +1558,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>6876</v>
+        <v>8050</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>687.6</v>
+        <v>731.81818181818187</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1572,11 +1576,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>3200</v>
+        <v>3908</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>320</v>
+        <v>355.27272727272725</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,11 +1594,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>34761</v>
+        <v>38956</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3476.1</v>
+        <v>3541.4545454545455</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1608,11 +1612,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>21304</v>
+        <v>23927</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2130.4</v>
+        <v>2175.181818181818</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1626,11 +1630,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>21893</v>
+        <v>24425</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2189.3000000000002</v>
+        <v>2220.4545454545455</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1644,11 +1648,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>26554</v>
+        <v>29796</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2655.4</v>
+        <v>2708.7272727272725</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,11 +1666,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>6692</v>
+        <v>7754</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>669.2</v>
+        <v>704.90909090909088</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1680,11 +1684,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>8064</v>
+        <v>9383</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>806.4</v>
+        <v>853</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1698,11 +1702,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>7950</v>
+        <v>9525</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>795</v>
+        <v>865.90909090909088</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,11 +1720,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>2498</v>
+        <v>2827</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>249.8</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1734,11 +1738,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1210</v>
+        <v>1365</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>121</v>
+        <v>124.09090909090909</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1752,11 +1756,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>4918</v>
+        <v>5649</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>491.8</v>
+        <v>513.5454545454545</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1770,11 +1774,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>8077</v>
+        <v>9381</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>807.7</v>
+        <v>852.81818181818187</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1788,11 +1792,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>62</v>
+        <v>57.272727272727273</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1806,11 +1810,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>7053</v>
+        <v>7910</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>705.3</v>
+        <v>719.09090909090912</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1824,11 +1828,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>11068</v>
+        <v>12404</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1106.8</v>
+        <v>1127.6363636363637</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1842,11 +1846,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>5171</v>
+        <v>6246</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>517.1</v>
+        <v>567.81818181818187</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1860,11 +1864,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>3866</v>
+        <v>4767</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>386.6</v>
+        <v>433.36363636363637</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1878,11 +1882,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>2361</v>
+        <v>2509</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>236.1</v>
+        <v>228.09090909090909</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1896,11 +1900,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>2839</v>
+        <v>3025</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>283.89999999999998</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1914,11 +1918,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1274</v>
+        <v>1535</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>127.4</v>
+        <v>139.54545454545453</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,11 +1936,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1299</v>
+        <v>1532</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>129.9</v>
+        <v>139.27272727272728</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1950,11 +1954,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>7493</v>
+        <v>8377</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>749.3</v>
+        <v>761.5454545454545</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1968,11 +1972,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>5789</v>
+        <v>6675</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>578.9</v>
+        <v>606.81818181818187</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1986,11 +1990,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>7718</v>
+        <v>8796</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>771.8</v>
+        <v>799.63636363636363</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2004,11 +2008,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>4936</v>
+        <v>5829</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>493.6</v>
+        <v>529.90909090909088</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2022,11 +2026,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4.8</v>
+        <v>4.6363636363636367</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2044,7 +2048,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.7</v>
+        <v>0.63636363636363635</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2058,11 +2062,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1476</v>
+        <v>1667</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>147.6</v>
+        <v>151.54545454545453</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2076,11 +2080,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>5127</v>
+        <v>5868</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>512.70000000000005</v>
+        <v>533.4545454545455</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2094,11 +2098,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>4097</v>
+        <v>4588</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>409.7</v>
+        <v>417.09090909090907</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2112,11 +2116,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1819</v>
+        <v>2088</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>181.9</v>
+        <v>189.81818181818181</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2130,11 +2134,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>4554</v>
+        <v>5105</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>455.4</v>
+        <v>464.09090909090907</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2148,11 +2152,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>2879</v>
+        <v>3218</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>287.89999999999998</v>
+        <v>292.54545454545456</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2166,11 +2170,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>2117</v>
+        <v>2417</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>211.7</v>
+        <v>219.72727272727272</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2184,11 +2188,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>312</v>
+        <v>400</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>31.2</v>
+        <v>36.363636363636367</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2202,11 +2206,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1070</v>
+        <v>1218</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>107</v>
+        <v>110.72727272727273</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2220,11 +2224,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>443</v>
+        <v>504</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>44.3</v>
+        <v>45.81818181818182</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2238,11 +2242,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>618</v>
+        <v>673</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>61.8</v>
+        <v>61.18181818181818</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2307,19 +2311,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>282655</v>
+        <v>320287</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>277852</v>
+        <v>315484</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>27785.200000000001</v>
+        <v>28680.363636363636</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>611274.4</v>
+        <v>630968</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2327,11 +2331,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.41993578877150339</v>
+        <v>0.47584501946987851</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-390436</v>
+        <v>-352804</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2372,7 +2376,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2380,11 +2384,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6373D99A-355E-473D-A0B0-0845F29E6EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC22840D-405A-45DA-B745-1FF62EEB666D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -351,10 +351,10 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>320287</v>
+            <v>315484</v>
           </cell>
           <cell r="H3">
-            <v>315484</v>
+            <v>305645</v>
           </cell>
           <cell r="I3">
             <v>28680.363636363636</v>
@@ -366,10 +366,10 @@
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.47584501946987851</v>
+            <v>0.46870928299442421</v>
           </cell>
           <cell r="M3">
-            <v>-352804</v>
+            <v>-42123</v>
           </cell>
         </row>
         <row r="4">
@@ -418,7 +418,7 @@
             <v>70.63636363636364</v>
           </cell>
           <cell r="G5">
-            <v>4803</v>
+            <v>9839</v>
           </cell>
           <cell r="H5">
             <v>46266</v>
@@ -2311,11 +2311,11 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>320287</v>
+        <v>315484</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>315484</v>
+        <v>305645</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.47584501946987851</v>
+        <v>0.46870928299442421</v>
       </c>
       <c r="G3" s="7">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-352804</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
+        <v>-42123</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2368,7 +2368,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>4803</v>
+        <v>9839</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC22840D-405A-45DA-B745-1FF62EEB666D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004BBE0E-E2B4-4781-8720-9C0FF5C79003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -301,6 +301,7 @@
       <sheetName val="INVENTARIO NACIONAL 14-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 15-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 16-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -320,7 +321,8 @@
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
-      <sheetData sheetId="13">
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -351,25 +353,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>315484</v>
+            <v>339999</v>
           </cell>
           <cell r="H3">
-            <v>305645</v>
+            <v>330160</v>
           </cell>
           <cell r="I3">
-            <v>28680.363636363636</v>
+            <v>28333.25</v>
           </cell>
           <cell r="J3">
-            <v>630968</v>
+            <v>623331.5</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.46870928299442421</v>
+            <v>0.50513080697855117</v>
           </cell>
           <cell r="M3">
-            <v>-42123</v>
+            <v>-49759.5</v>
           </cell>
         </row>
         <row r="4">
@@ -380,10 +382,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>13833</v>
+            <v>14842</v>
           </cell>
           <cell r="D4">
-            <v>1257.5454545454545</v>
+            <v>1236.8333333333333</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -412,10 +414,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>777</v>
+            <v>801</v>
           </cell>
           <cell r="D5">
-            <v>70.63636363636364</v>
+            <v>66.75</v>
           </cell>
           <cell r="G5">
             <v>9839</v>
@@ -424,16 +426,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46281</v>
+            <v>46282</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>11</v>
+            <v>12</v>
           </cell>
           <cell r="L5">
-            <v>11</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="6">
@@ -444,10 +446,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>5628</v>
+            <v>5941</v>
           </cell>
           <cell r="D6">
-            <v>511.63636363636363</v>
+            <v>495.08333333333331</v>
           </cell>
         </row>
         <row r="7">
@@ -458,10 +460,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1352</v>
+            <v>1439</v>
           </cell>
           <cell r="D7">
-            <v>122.90909090909091</v>
+            <v>119.91666666666667</v>
           </cell>
         </row>
         <row r="8">
@@ -472,10 +474,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>169</v>
+            <v>185</v>
           </cell>
           <cell r="D8">
-            <v>15.363636363636363</v>
+            <v>15.416666666666666</v>
           </cell>
         </row>
         <row r="9">
@@ -486,10 +488,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>16066</v>
+            <v>17164</v>
           </cell>
           <cell r="D9">
-            <v>1460.5454545454545</v>
+            <v>1430.3333333333333</v>
           </cell>
         </row>
         <row r="10">
@@ -500,10 +502,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>1608</v>
+            <v>1768</v>
           </cell>
           <cell r="D10">
-            <v>146.18181818181819</v>
+            <v>147.33333333333334</v>
           </cell>
         </row>
         <row r="11">
@@ -514,10 +516,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>3066</v>
+            <v>3424</v>
           </cell>
           <cell r="D11">
-            <v>278.72727272727275</v>
+            <v>285.33333333333331</v>
           </cell>
         </row>
         <row r="12">
@@ -528,10 +530,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>8050</v>
+            <v>8861</v>
           </cell>
           <cell r="D12">
-            <v>731.81818181818187</v>
+            <v>738.41666666666663</v>
           </cell>
         </row>
         <row r="13">
@@ -542,10 +544,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>3908</v>
+            <v>4199</v>
           </cell>
           <cell r="D13">
-            <v>355.27272727272725</v>
+            <v>349.91666666666669</v>
           </cell>
         </row>
         <row r="14">
@@ -556,10 +558,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>38956</v>
+            <v>41620</v>
           </cell>
           <cell r="D14">
-            <v>3541.4545454545455</v>
+            <v>3468.3333333333335</v>
           </cell>
         </row>
         <row r="15">
@@ -570,10 +572,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>23927</v>
+            <v>25716</v>
           </cell>
           <cell r="D15">
-            <v>2175.181818181818</v>
+            <v>2143</v>
           </cell>
         </row>
         <row r="16">
@@ -584,10 +586,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>24425</v>
+            <v>26192</v>
           </cell>
           <cell r="D16">
-            <v>2220.4545454545455</v>
+            <v>2182.6666666666665</v>
           </cell>
         </row>
         <row r="17">
@@ -598,10 +600,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>29796</v>
+            <v>31881</v>
           </cell>
           <cell r="D17">
-            <v>2708.7272727272725</v>
+            <v>2656.75</v>
           </cell>
         </row>
         <row r="18">
@@ -612,10 +614,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>7754</v>
+            <v>8448</v>
           </cell>
           <cell r="D18">
-            <v>704.90909090909088</v>
+            <v>704</v>
           </cell>
         </row>
         <row r="19">
@@ -626,10 +628,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>9383</v>
+            <v>9831</v>
           </cell>
           <cell r="D19">
-            <v>853</v>
+            <v>819.25</v>
           </cell>
         </row>
         <row r="20">
@@ -640,10 +642,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>9525</v>
+            <v>10340</v>
           </cell>
           <cell r="D20">
-            <v>865.90909090909088</v>
+            <v>861.66666666666663</v>
           </cell>
         </row>
         <row r="21">
@@ -654,10 +656,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>2827</v>
+            <v>3072</v>
           </cell>
           <cell r="D21">
-            <v>257</v>
+            <v>256</v>
           </cell>
         </row>
         <row r="22">
@@ -668,10 +670,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>1365</v>
+            <v>1459</v>
           </cell>
           <cell r="D22">
-            <v>124.09090909090909</v>
+            <v>121.58333333333333</v>
           </cell>
         </row>
         <row r="23">
@@ -682,10 +684,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>5649</v>
+            <v>6175</v>
           </cell>
           <cell r="D23">
-            <v>513.5454545454545</v>
+            <v>514.58333333333337</v>
           </cell>
         </row>
         <row r="24">
@@ -696,10 +698,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>9381</v>
+            <v>10099</v>
           </cell>
           <cell r="D24">
-            <v>852.81818181818187</v>
+            <v>841.58333333333337</v>
           </cell>
         </row>
         <row r="25">
@@ -710,10 +712,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>630</v>
+            <v>930</v>
           </cell>
           <cell r="D25">
-            <v>57.272727272727273</v>
+            <v>77.5</v>
           </cell>
         </row>
         <row r="26">
@@ -724,10 +726,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>7910</v>
+            <v>8345</v>
           </cell>
           <cell r="D26">
-            <v>719.09090909090912</v>
+            <v>695.41666666666663</v>
           </cell>
         </row>
         <row r="27">
@@ -738,10 +740,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>12404</v>
+            <v>13347</v>
           </cell>
           <cell r="D27">
-            <v>1127.6363636363637</v>
+            <v>1112.25</v>
           </cell>
         </row>
         <row r="28">
@@ -752,10 +754,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>6246</v>
+            <v>6806</v>
           </cell>
           <cell r="D28">
-            <v>567.81818181818187</v>
+            <v>567.16666666666663</v>
           </cell>
         </row>
         <row r="29">
@@ -766,10 +768,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>4767</v>
+            <v>5219</v>
           </cell>
           <cell r="D29">
-            <v>433.36363636363637</v>
+            <v>434.91666666666669</v>
           </cell>
         </row>
         <row r="30">
@@ -780,10 +782,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>2509</v>
+            <v>2686</v>
           </cell>
           <cell r="D30">
-            <v>228.09090909090909</v>
+            <v>223.83333333333334</v>
           </cell>
         </row>
         <row r="31">
@@ -794,10 +796,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>3025</v>
+            <v>3213</v>
           </cell>
           <cell r="D31">
-            <v>275</v>
+            <v>267.75</v>
           </cell>
         </row>
         <row r="32">
@@ -808,10 +810,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>1535</v>
+            <v>1617</v>
           </cell>
           <cell r="D32">
-            <v>139.54545454545453</v>
+            <v>134.75</v>
           </cell>
         </row>
         <row r="33">
@@ -822,10 +824,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>1532</v>
+            <v>1638</v>
           </cell>
           <cell r="D33">
-            <v>139.27272727272728</v>
+            <v>136.5</v>
           </cell>
         </row>
         <row r="34">
@@ -836,10 +838,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>8377</v>
+            <v>9095</v>
           </cell>
           <cell r="D34">
-            <v>761.5454545454545</v>
+            <v>757.91666666666663</v>
           </cell>
         </row>
         <row r="35">
@@ -850,10 +852,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>6675</v>
+            <v>7097</v>
           </cell>
           <cell r="D35">
-            <v>606.81818181818187</v>
+            <v>591.41666666666663</v>
           </cell>
         </row>
         <row r="36">
@@ -864,10 +866,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>8796</v>
+            <v>9536</v>
           </cell>
           <cell r="D36">
-            <v>799.63636363636363</v>
+            <v>794.66666666666663</v>
           </cell>
         </row>
         <row r="37">
@@ -878,10 +880,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>5829</v>
+            <v>6209</v>
           </cell>
           <cell r="D37">
-            <v>529.90909090909088</v>
+            <v>517.41666666666663</v>
           </cell>
         </row>
         <row r="38">
@@ -895,7 +897,7 @@
             <v>51</v>
           </cell>
           <cell r="D38">
-            <v>4.6363636363636367</v>
+            <v>4.25</v>
           </cell>
         </row>
         <row r="39">
@@ -909,7 +911,7 @@
             <v>7</v>
           </cell>
           <cell r="D39">
-            <v>0.63636363636363635</v>
+            <v>0.58333333333333337</v>
           </cell>
         </row>
         <row r="40">
@@ -920,10 +922,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>1667</v>
+            <v>1757</v>
           </cell>
           <cell r="D40">
-            <v>151.54545454545453</v>
+            <v>146.41666666666666</v>
           </cell>
         </row>
         <row r="41">
@@ -934,10 +936,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>5868</v>
+            <v>6515</v>
           </cell>
           <cell r="D41">
-            <v>533.4545454545455</v>
+            <v>542.91666666666663</v>
           </cell>
         </row>
         <row r="42">
@@ -948,10 +950,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>4588</v>
+            <v>5043</v>
           </cell>
           <cell r="D42">
-            <v>417.09090909090907</v>
+            <v>420.25</v>
           </cell>
         </row>
         <row r="43">
@@ -962,10 +964,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>2088</v>
+            <v>2393</v>
           </cell>
           <cell r="D43">
-            <v>189.81818181818181</v>
+            <v>199.41666666666666</v>
           </cell>
         </row>
         <row r="44">
@@ -976,10 +978,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>5105</v>
+            <v>5693</v>
           </cell>
           <cell r="D44">
-            <v>464.09090909090907</v>
+            <v>474.41666666666669</v>
           </cell>
         </row>
         <row r="45">
@@ -990,10 +992,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>3218</v>
+            <v>3547</v>
           </cell>
           <cell r="D45">
-            <v>292.54545454545456</v>
+            <v>295.58333333333331</v>
           </cell>
         </row>
         <row r="46">
@@ -1004,10 +1006,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>2417</v>
+            <v>2754</v>
           </cell>
           <cell r="D46">
-            <v>219.72727272727272</v>
+            <v>229.5</v>
           </cell>
         </row>
         <row r="47">
@@ -1018,10 +1020,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>400</v>
+            <v>442</v>
           </cell>
           <cell r="D47">
-            <v>36.363636363636367</v>
+            <v>36.833333333333336</v>
           </cell>
         </row>
         <row r="48">
@@ -1032,10 +1034,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>1218</v>
+            <v>1327</v>
           </cell>
           <cell r="D48">
-            <v>110.72727272727273</v>
+            <v>110.58333333333333</v>
           </cell>
         </row>
         <row r="49">
@@ -1046,10 +1048,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>504</v>
+            <v>549</v>
           </cell>
           <cell r="D49">
-            <v>45.81818181818182</v>
+            <v>45.75</v>
           </cell>
         </row>
         <row r="50">
@@ -1060,14 +1062,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>673</v>
+            <v>726</v>
           </cell>
           <cell r="D50">
-            <v>61.18181818181818</v>
+            <v>60.5</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1414,11 +1416,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>13833</v>
+        <v>14842</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1257.5454545454545</v>
+        <v>1236.8333333333333</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1432,11 +1434,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>777</v>
+        <v>801</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>70.63636363636364</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,11 +1452,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>5628</v>
+        <v>5941</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>511.63636363636363</v>
+        <v>495.08333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1468,11 +1470,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1352</v>
+        <v>1439</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>122.90909090909091</v>
+        <v>119.91666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1486,11 +1488,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>15.363636363636363</v>
+        <v>15.416666666666666</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1504,11 +1506,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>16066</v>
+        <v>17164</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1460.5454545454545</v>
+        <v>1430.3333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1522,11 +1524,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1608</v>
+        <v>1768</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>146.18181818181819</v>
+        <v>147.33333333333334</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1540,11 +1542,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>3066</v>
+        <v>3424</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>278.72727272727275</v>
+        <v>285.33333333333331</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1558,11 +1560,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>8050</v>
+        <v>8861</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>731.81818181818187</v>
+        <v>738.41666666666663</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,11 +1578,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>3908</v>
+        <v>4199</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>355.27272727272725</v>
+        <v>349.91666666666669</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1594,11 +1596,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>38956</v>
+        <v>41620</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3541.4545454545455</v>
+        <v>3468.3333333333335</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1612,11 +1614,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>23927</v>
+        <v>25716</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2175.181818181818</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1630,11 +1632,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>24425</v>
+        <v>26192</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2220.4545454545455</v>
+        <v>2182.6666666666665</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1648,11 +1650,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>29796</v>
+        <v>31881</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2708.7272727272725</v>
+        <v>2656.75</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1666,11 +1668,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>7754</v>
+        <v>8448</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>704.90909090909088</v>
+        <v>704</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1684,11 +1686,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>9383</v>
+        <v>9831</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>853</v>
+        <v>819.25</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1702,11 +1704,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>9525</v>
+        <v>10340</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>865.90909090909088</v>
+        <v>861.66666666666663</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1720,11 +1722,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>2827</v>
+        <v>3072</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1738,11 +1740,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1365</v>
+        <v>1459</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>124.09090909090909</v>
+        <v>121.58333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1756,11 +1758,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>5649</v>
+        <v>6175</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>513.5454545454545</v>
+        <v>514.58333333333337</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1774,11 +1776,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>9381</v>
+        <v>10099</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>852.81818181818187</v>
+        <v>841.58333333333337</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1792,11 +1794,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>630</v>
+        <v>930</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>57.272727272727273</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1810,11 +1812,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>7910</v>
+        <v>8345</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>719.09090909090912</v>
+        <v>695.41666666666663</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1828,11 +1830,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>12404</v>
+        <v>13347</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1127.6363636363637</v>
+        <v>1112.25</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1846,11 +1848,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>6246</v>
+        <v>6806</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>567.81818181818187</v>
+        <v>567.16666666666663</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1864,11 +1866,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>4767</v>
+        <v>5219</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>433.36363636363637</v>
+        <v>434.91666666666669</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1882,11 +1884,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>2509</v>
+        <v>2686</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>228.09090909090909</v>
+        <v>223.83333333333334</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1900,11 +1902,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>3025</v>
+        <v>3213</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>275</v>
+        <v>267.75</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,11 +1920,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1535</v>
+        <v>1617</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>139.54545454545453</v>
+        <v>134.75</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1936,11 +1938,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1532</v>
+        <v>1638</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>139.27272727272728</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1954,11 +1956,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>8377</v>
+        <v>9095</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>761.5454545454545</v>
+        <v>757.91666666666663</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1972,11 +1974,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>6675</v>
+        <v>7097</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>606.81818181818187</v>
+        <v>591.41666666666663</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1990,11 +1992,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>8796</v>
+        <v>9536</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>799.63636363636363</v>
+        <v>794.66666666666663</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2008,11 +2010,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>5829</v>
+        <v>6209</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>529.90909090909088</v>
+        <v>517.41666666666663</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2030,7 +2032,7 @@
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4.6363636363636367</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2048,7 +2050,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.63636363636363635</v>
+        <v>0.58333333333333337</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2062,11 +2064,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1667</v>
+        <v>1757</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>151.54545454545453</v>
+        <v>146.41666666666666</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2080,11 +2082,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>5868</v>
+        <v>6515</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>533.4545454545455</v>
+        <v>542.91666666666663</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2098,11 +2100,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>4588</v>
+        <v>5043</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>417.09090909090907</v>
+        <v>420.25</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2116,11 +2118,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>2088</v>
+        <v>2393</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>189.81818181818181</v>
+        <v>199.41666666666666</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2134,11 +2136,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>5105</v>
+        <v>5693</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>464.09090909090907</v>
+        <v>474.41666666666669</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2152,11 +2154,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>3218</v>
+        <v>3547</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>292.54545454545456</v>
+        <v>295.58333333333331</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2170,11 +2172,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>2417</v>
+        <v>2754</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>219.72727272727272</v>
+        <v>229.5</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2188,11 +2190,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>400</v>
+        <v>442</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>36.363636363636367</v>
+        <v>36.833333333333336</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2206,11 +2208,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1218</v>
+        <v>1327</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>110.72727272727273</v>
+        <v>110.58333333333333</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2224,11 +2226,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>45.81818181818182</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2242,11 +2244,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>673</v>
+        <v>726</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>61.18181818181818</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2311,19 +2313,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>315484</v>
+        <v>339999</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>305645</v>
+        <v>330160</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>28680.363636363636</v>
+        <v>28333.25</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>630968</v>
+        <v>623331.5</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2331,11 +2333,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.46870928299442421</v>
+        <v>0.50513080697855117</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-42123</v>
+        <v>-49759.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2376,7 +2378,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2384,11 +2386,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004BBE0E-E2B4-4781-8720-9C0FF5C79003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5A58E1-8C6A-43C9-B05B-A10B3D662D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -302,6 +302,8 @@
       <sheetName val="INVENTARIO NACIONAL 15-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 16-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-09-16;15"/>
+      <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -322,7 +324,9 @@
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
-      <sheetData sheetId="14">
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -353,25 +357,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>339999</v>
+            <v>363804</v>
           </cell>
           <cell r="H3">
-            <v>330160</v>
+            <v>353965</v>
           </cell>
           <cell r="I3">
-            <v>28333.25</v>
+            <v>27984.923076923078</v>
           </cell>
           <cell r="J3">
-            <v>623331.5</v>
+            <v>615668.30769230775</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.50513080697855117</v>
+            <v>0.54049749588094331</v>
           </cell>
           <cell r="M3">
-            <v>-49759.5</v>
+            <v>-57422.692307692254</v>
           </cell>
         </row>
         <row r="4">
@@ -382,10 +386,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>14842</v>
+            <v>15880</v>
           </cell>
           <cell r="D4">
-            <v>1236.8333333333333</v>
+            <v>1221.5384615384614</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -414,10 +418,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>801</v>
+            <v>870</v>
           </cell>
           <cell r="D5">
-            <v>66.75</v>
+            <v>66.92307692307692</v>
           </cell>
           <cell r="G5">
             <v>9839</v>
@@ -426,16 +430,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46282</v>
+            <v>46283</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>12</v>
+            <v>13</v>
           </cell>
           <cell r="L5">
-            <v>10</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="6">
@@ -446,10 +450,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>5941</v>
+            <v>6480</v>
           </cell>
           <cell r="D6">
-            <v>495.08333333333331</v>
+            <v>498.46153846153845</v>
           </cell>
         </row>
         <row r="7">
@@ -460,10 +464,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1439</v>
+            <v>1508</v>
           </cell>
           <cell r="D7">
-            <v>119.91666666666667</v>
+            <v>116</v>
           </cell>
         </row>
         <row r="8">
@@ -474,10 +478,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>185</v>
+            <v>193</v>
           </cell>
           <cell r="D8">
-            <v>15.416666666666666</v>
+            <v>14.846153846153847</v>
           </cell>
         </row>
         <row r="9">
@@ -488,10 +492,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>17164</v>
+            <v>18704</v>
           </cell>
           <cell r="D9">
-            <v>1430.3333333333333</v>
+            <v>1438.7692307692307</v>
           </cell>
         </row>
         <row r="10">
@@ -502,10 +506,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>1768</v>
+            <v>1877</v>
           </cell>
           <cell r="D10">
-            <v>147.33333333333334</v>
+            <v>144.38461538461539</v>
           </cell>
         </row>
         <row r="11">
@@ -516,10 +520,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>3424</v>
+            <v>3654</v>
           </cell>
           <cell r="D11">
-            <v>285.33333333333331</v>
+            <v>281.07692307692309</v>
           </cell>
         </row>
         <row r="12">
@@ -530,10 +534,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>8861</v>
+            <v>9467</v>
           </cell>
           <cell r="D12">
-            <v>738.41666666666663</v>
+            <v>728.23076923076928</v>
           </cell>
         </row>
         <row r="13">
@@ -544,10 +548,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>4199</v>
+            <v>4436</v>
           </cell>
           <cell r="D13">
-            <v>349.91666666666669</v>
+            <v>341.23076923076923</v>
           </cell>
         </row>
         <row r="14">
@@ -558,10 +562,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>41620</v>
+            <v>44744</v>
           </cell>
           <cell r="D14">
-            <v>3468.3333333333335</v>
+            <v>3441.8461538461538</v>
           </cell>
         </row>
         <row r="15">
@@ -572,10 +576,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>25716</v>
+            <v>27639</v>
           </cell>
           <cell r="D15">
-            <v>2143</v>
+            <v>2126.0769230769229</v>
           </cell>
         </row>
         <row r="16">
@@ -586,10 +590,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>26192</v>
+            <v>28167</v>
           </cell>
           <cell r="D16">
-            <v>2182.6666666666665</v>
+            <v>2166.6923076923076</v>
           </cell>
         </row>
         <row r="17">
@@ -600,10 +604,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>31881</v>
+            <v>34306</v>
           </cell>
           <cell r="D17">
-            <v>2656.75</v>
+            <v>2638.9230769230771</v>
           </cell>
         </row>
         <row r="18">
@@ -614,10 +618,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>8448</v>
+            <v>9028</v>
           </cell>
           <cell r="D18">
-            <v>704</v>
+            <v>694.46153846153845</v>
           </cell>
         </row>
         <row r="19">
@@ -628,10 +632,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>9831</v>
+            <v>10246</v>
           </cell>
           <cell r="D19">
-            <v>819.25</v>
+            <v>788.15384615384619</v>
           </cell>
         </row>
         <row r="20">
@@ -642,10 +646,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>10340</v>
+            <v>10891</v>
           </cell>
           <cell r="D20">
-            <v>861.66666666666663</v>
+            <v>837.76923076923072</v>
           </cell>
         </row>
         <row r="21">
@@ -656,10 +660,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>3072</v>
+            <v>3252</v>
           </cell>
           <cell r="D21">
-            <v>256</v>
+            <v>250.15384615384616</v>
           </cell>
         </row>
         <row r="22">
@@ -670,10 +674,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>1459</v>
+            <v>1539</v>
           </cell>
           <cell r="D22">
-            <v>121.58333333333333</v>
+            <v>118.38461538461539</v>
           </cell>
         </row>
         <row r="23">
@@ -684,10 +688,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>6175</v>
+            <v>6467</v>
           </cell>
           <cell r="D23">
-            <v>514.58333333333337</v>
+            <v>497.46153846153845</v>
           </cell>
         </row>
         <row r="24">
@@ -698,10 +702,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>10099</v>
+            <v>10679</v>
           </cell>
           <cell r="D24">
-            <v>841.58333333333337</v>
+            <v>821.46153846153845</v>
           </cell>
         </row>
         <row r="25">
@@ -712,10 +716,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>930</v>
+            <v>960</v>
           </cell>
           <cell r="D25">
-            <v>77.5</v>
+            <v>73.84615384615384</v>
           </cell>
         </row>
         <row r="26">
@@ -726,10 +730,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>8345</v>
+            <v>9110</v>
           </cell>
           <cell r="D26">
-            <v>695.41666666666663</v>
+            <v>700.76923076923072</v>
           </cell>
         </row>
         <row r="27">
@@ -740,10 +744,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>13347</v>
+            <v>14646</v>
           </cell>
           <cell r="D27">
-            <v>1112.25</v>
+            <v>1126.6153846153845</v>
           </cell>
         </row>
         <row r="28">
@@ -754,10 +758,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>6806</v>
+            <v>7137</v>
           </cell>
           <cell r="D28">
-            <v>567.16666666666663</v>
+            <v>549</v>
           </cell>
         </row>
         <row r="29">
@@ -768,10 +772,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>5219</v>
+            <v>5575</v>
           </cell>
           <cell r="D29">
-            <v>434.91666666666669</v>
+            <v>428.84615384615387</v>
           </cell>
         </row>
         <row r="30">
@@ -782,10 +786,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>2686</v>
+            <v>3113</v>
           </cell>
           <cell r="D30">
-            <v>223.83333333333334</v>
+            <v>239.46153846153845</v>
           </cell>
         </row>
         <row r="31">
@@ -796,10 +800,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>3213</v>
+            <v>3766</v>
           </cell>
           <cell r="D31">
-            <v>267.75</v>
+            <v>289.69230769230768</v>
           </cell>
         </row>
         <row r="32">
@@ -810,10 +814,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>1617</v>
+            <v>1651</v>
           </cell>
           <cell r="D32">
-            <v>134.75</v>
+            <v>127</v>
           </cell>
         </row>
         <row r="33">
@@ -824,10 +828,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>1638</v>
+            <v>1690</v>
           </cell>
           <cell r="D33">
-            <v>136.5</v>
+            <v>130</v>
           </cell>
         </row>
         <row r="34">
@@ -838,10 +842,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>9095</v>
+            <v>9699</v>
           </cell>
           <cell r="D34">
-            <v>757.91666666666663</v>
+            <v>746.07692307692309</v>
           </cell>
         </row>
         <row r="35">
@@ -852,10 +856,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>7097</v>
+            <v>7466</v>
           </cell>
           <cell r="D35">
-            <v>591.41666666666663</v>
+            <v>574.30769230769226</v>
           </cell>
         </row>
         <row r="36">
@@ -866,10 +870,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>9536</v>
+            <v>10025</v>
           </cell>
           <cell r="D36">
-            <v>794.66666666666663</v>
+            <v>771.15384615384619</v>
           </cell>
         </row>
         <row r="37">
@@ -880,10 +884,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>6209</v>
+            <v>6509</v>
           </cell>
           <cell r="D37">
-            <v>517.41666666666663</v>
+            <v>500.69230769230768</v>
           </cell>
         </row>
         <row r="38">
@@ -894,10 +898,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>51</v>
+            <v>52</v>
           </cell>
           <cell r="D38">
-            <v>4.25</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="39">
@@ -911,7 +915,7 @@
             <v>7</v>
           </cell>
           <cell r="D39">
-            <v>0.58333333333333337</v>
+            <v>0.53846153846153844</v>
           </cell>
         </row>
         <row r="40">
@@ -922,10 +926,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>1757</v>
+            <v>1851</v>
           </cell>
           <cell r="D40">
-            <v>146.41666666666666</v>
+            <v>142.38461538461539</v>
           </cell>
         </row>
         <row r="41">
@@ -936,10 +940,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>6515</v>
+            <v>6864</v>
           </cell>
           <cell r="D41">
-            <v>542.91666666666663</v>
+            <v>528</v>
           </cell>
         </row>
         <row r="42">
@@ -950,10 +954,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>5043</v>
+            <v>5434</v>
           </cell>
           <cell r="D42">
-            <v>420.25</v>
+            <v>418</v>
           </cell>
         </row>
         <row r="43">
@@ -964,10 +968,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>2393</v>
+            <v>2523</v>
           </cell>
           <cell r="D43">
-            <v>199.41666666666666</v>
+            <v>194.07692307692307</v>
           </cell>
         </row>
         <row r="44">
@@ -978,10 +982,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>5693</v>
+            <v>5958</v>
           </cell>
           <cell r="D44">
-            <v>474.41666666666669</v>
+            <v>458.30769230769232</v>
           </cell>
         </row>
         <row r="45">
@@ -992,10 +996,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>3547</v>
+            <v>3719</v>
           </cell>
           <cell r="D45">
-            <v>295.58333333333331</v>
+            <v>286.07692307692309</v>
           </cell>
         </row>
         <row r="46">
@@ -1006,10 +1010,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>2754</v>
+            <v>2894</v>
           </cell>
           <cell r="D46">
-            <v>229.5</v>
+            <v>222.61538461538461</v>
           </cell>
         </row>
         <row r="47">
@@ -1020,10 +1024,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>442</v>
+            <v>468</v>
           </cell>
           <cell r="D47">
-            <v>36.833333333333336</v>
+            <v>36</v>
           </cell>
         </row>
         <row r="48">
@@ -1034,10 +1038,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>1327</v>
+            <v>1359</v>
           </cell>
           <cell r="D48">
-            <v>110.58333333333333</v>
+            <v>104.53846153846153</v>
           </cell>
         </row>
         <row r="49">
@@ -1048,10 +1052,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>549</v>
+            <v>561</v>
           </cell>
           <cell r="D49">
-            <v>45.75</v>
+            <v>43.153846153846153</v>
           </cell>
         </row>
         <row r="50">
@@ -1062,14 +1066,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>726</v>
+            <v>740</v>
           </cell>
           <cell r="D50">
-            <v>60.5</v>
+            <v>56.92307692307692</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="15"/>
+      <sheetData sheetId="17"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1416,11 +1420,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>14842</v>
+        <v>15880</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1236.8333333333333</v>
+        <v>1221.5384615384614</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1434,11 +1438,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>801</v>
+        <v>870</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>66.75</v>
+        <v>66.92307692307692</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,11 +1456,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>5941</v>
+        <v>6480</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>495.08333333333331</v>
+        <v>498.46153846153845</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1470,11 +1474,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1439</v>
+        <v>1508</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>119.91666666666667</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1488,11 +1492,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>15.416666666666666</v>
+        <v>14.846153846153847</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,11 +1510,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>17164</v>
+        <v>18704</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1430.3333333333333</v>
+        <v>1438.7692307692307</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,11 +1528,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1768</v>
+        <v>1877</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>147.33333333333334</v>
+        <v>144.38461538461539</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1542,11 +1546,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>3424</v>
+        <v>3654</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>285.33333333333331</v>
+        <v>281.07692307692309</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1560,11 +1564,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>8861</v>
+        <v>9467</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>738.41666666666663</v>
+        <v>728.23076923076928</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1578,11 +1582,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>4199</v>
+        <v>4436</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>349.91666666666669</v>
+        <v>341.23076923076923</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1596,11 +1600,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>41620</v>
+        <v>44744</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3468.3333333333335</v>
+        <v>3441.8461538461538</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1614,11 +1618,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>25716</v>
+        <v>27639</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2143</v>
+        <v>2126.0769230769229</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,11 +1636,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>26192</v>
+        <v>28167</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2182.6666666666665</v>
+        <v>2166.6923076923076</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1650,11 +1654,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>31881</v>
+        <v>34306</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2656.75</v>
+        <v>2638.9230769230771</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1668,11 +1672,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>8448</v>
+        <v>9028</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>704</v>
+        <v>694.46153846153845</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1686,11 +1690,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>9831</v>
+        <v>10246</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>819.25</v>
+        <v>788.15384615384619</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1704,11 +1708,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>10340</v>
+        <v>10891</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>861.66666666666663</v>
+        <v>837.76923076923072</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1722,11 +1726,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>3072</v>
+        <v>3252</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>256</v>
+        <v>250.15384615384616</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1740,11 +1744,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1459</v>
+        <v>1539</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>121.58333333333333</v>
+        <v>118.38461538461539</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1758,11 +1762,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>6175</v>
+        <v>6467</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>514.58333333333337</v>
+        <v>497.46153846153845</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1776,11 +1780,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>10099</v>
+        <v>10679</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>841.58333333333337</v>
+        <v>821.46153846153845</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1794,11 +1798,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>930</v>
+        <v>960</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>77.5</v>
+        <v>73.84615384615384</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,11 +1816,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>8345</v>
+        <v>9110</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>695.41666666666663</v>
+        <v>700.76923076923072</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1830,11 +1834,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>13347</v>
+        <v>14646</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1112.25</v>
+        <v>1126.6153846153845</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1848,11 +1852,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>6806</v>
+        <v>7137</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>567.16666666666663</v>
+        <v>549</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1866,11 +1870,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>5219</v>
+        <v>5575</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>434.91666666666669</v>
+        <v>428.84615384615387</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,11 +1888,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>2686</v>
+        <v>3113</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>223.83333333333334</v>
+        <v>239.46153846153845</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1902,11 +1906,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>3213</v>
+        <v>3766</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>267.75</v>
+        <v>289.69230769230768</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1920,11 +1924,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1617</v>
+        <v>1651</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>134.75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1938,11 +1942,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1638</v>
+        <v>1690</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>136.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1956,11 +1960,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>9095</v>
+        <v>9699</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>757.91666666666663</v>
+        <v>746.07692307692309</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1974,11 +1978,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>7097</v>
+        <v>7466</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>591.41666666666663</v>
+        <v>574.30769230769226</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1992,11 +1996,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>9536</v>
+        <v>10025</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>794.66666666666663</v>
+        <v>771.15384615384619</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2010,11 +2014,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>6209</v>
+        <v>6509</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>517.41666666666663</v>
+        <v>500.69230769230768</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2028,11 +2032,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2050,7 +2054,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.58333333333333337</v>
+        <v>0.53846153846153844</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2064,11 +2068,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1757</v>
+        <v>1851</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>146.41666666666666</v>
+        <v>142.38461538461539</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2082,11 +2086,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>6515</v>
+        <v>6864</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>542.91666666666663</v>
+        <v>528</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2100,11 +2104,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>5043</v>
+        <v>5434</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>420.25</v>
+        <v>418</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2118,11 +2122,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>2393</v>
+        <v>2523</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>199.41666666666666</v>
+        <v>194.07692307692307</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2136,11 +2140,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>5693</v>
+        <v>5958</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>474.41666666666669</v>
+        <v>458.30769230769232</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2154,11 +2158,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>3547</v>
+        <v>3719</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>295.58333333333331</v>
+        <v>286.07692307692309</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2172,11 +2176,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>2754</v>
+        <v>2894</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>229.5</v>
+        <v>222.61538461538461</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2190,11 +2194,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>36.833333333333336</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2208,11 +2212,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1327</v>
+        <v>1359</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>110.58333333333333</v>
+        <v>104.53846153846153</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2226,11 +2230,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>45.75</v>
+        <v>43.153846153846153</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2244,11 +2248,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>60.5</v>
+        <v>56.92307692307692</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2313,19 +2317,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>339999</v>
+        <v>363804</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>330160</v>
+        <v>353965</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>28333.25</v>
+        <v>27984.923076923078</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>623331.5</v>
+        <v>615668.30769230775</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2333,11 +2337,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.50513080697855117</v>
+        <v>0.54049749588094331</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-49759.5</v>
+        <v>-57422.692307692254</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2378,7 +2382,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2386,11 +2390,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5A58E1-8C6A-43C9-B05B-A10B3D662D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D206DA8-7F8A-40B1-A726-1070722BF1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -304,6 +304,7 @@
       <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-09-16;15"/>
       <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 20-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -326,7 +327,8 @@
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
-      <sheetData sheetId="16">
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -357,25 +359,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>363804</v>
+            <v>384787</v>
           </cell>
           <cell r="H3">
-            <v>353965</v>
+            <v>374948</v>
           </cell>
           <cell r="I3">
-            <v>27984.923076923078</v>
+            <v>27484.785714285714</v>
           </cell>
           <cell r="J3">
-            <v>615668.30769230775</v>
+            <v>604665.28571428568</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.54049749588094331</v>
+            <v>0.57167158675424279</v>
           </cell>
           <cell r="M3">
-            <v>-57422.692307692254</v>
+            <v>-68425.714285714319</v>
           </cell>
         </row>
         <row r="4">
@@ -386,10 +388,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>15880</v>
+            <v>16741</v>
           </cell>
           <cell r="D4">
-            <v>1221.5384615384614</v>
+            <v>1195.7857142857142</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -418,10 +420,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>870</v>
+            <v>879</v>
           </cell>
           <cell r="D5">
-            <v>66.92307692307692</v>
+            <v>62.785714285714285</v>
           </cell>
           <cell r="G5">
             <v>9839</v>
@@ -430,16 +432,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46283</v>
+            <v>46286</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>13</v>
+            <v>14</v>
           </cell>
           <cell r="L5">
-            <v>9</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="6">
@@ -450,10 +452,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>6480</v>
+            <v>6771</v>
           </cell>
           <cell r="D6">
-            <v>498.46153846153845</v>
+            <v>483.64285714285717</v>
           </cell>
         </row>
         <row r="7">
@@ -464,10 +466,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1508</v>
+            <v>1547</v>
           </cell>
           <cell r="D7">
-            <v>116</v>
+            <v>110.5</v>
           </cell>
         </row>
         <row r="8">
@@ -481,7 +483,7 @@
             <v>193</v>
           </cell>
           <cell r="D8">
-            <v>14.846153846153847</v>
+            <v>13.785714285714286</v>
           </cell>
         </row>
         <row r="9">
@@ -492,10 +494,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>18704</v>
+            <v>19721</v>
           </cell>
           <cell r="D9">
-            <v>1438.7692307692307</v>
+            <v>1408.6428571428571</v>
           </cell>
         </row>
         <row r="10">
@@ -506,10 +508,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>1877</v>
+            <v>2006</v>
           </cell>
           <cell r="D10">
-            <v>144.38461538461539</v>
+            <v>143.28571428571428</v>
           </cell>
         </row>
         <row r="11">
@@ -520,10 +522,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>3654</v>
+            <v>4057</v>
           </cell>
           <cell r="D11">
-            <v>281.07692307692309</v>
+            <v>289.78571428571428</v>
           </cell>
         </row>
         <row r="12">
@@ -534,10 +536,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>9467</v>
+            <v>10147</v>
           </cell>
           <cell r="D12">
-            <v>728.23076923076928</v>
+            <v>724.78571428571433</v>
           </cell>
         </row>
         <row r="13">
@@ -548,10 +550,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>4436</v>
+            <v>4787</v>
           </cell>
           <cell r="D13">
-            <v>341.23076923076923</v>
+            <v>341.92857142857144</v>
           </cell>
         </row>
         <row r="14">
@@ -562,10 +564,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>44744</v>
+            <v>46685</v>
           </cell>
           <cell r="D14">
-            <v>3441.8461538461538</v>
+            <v>3334.6428571428573</v>
           </cell>
         </row>
         <row r="15">
@@ -576,10 +578,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>27639</v>
+            <v>28881</v>
           </cell>
           <cell r="D15">
-            <v>2126.0769230769229</v>
+            <v>2062.9285714285716</v>
           </cell>
         </row>
         <row r="16">
@@ -590,10 +592,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>28167</v>
+            <v>29573</v>
           </cell>
           <cell r="D16">
-            <v>2166.6923076923076</v>
+            <v>2112.3571428571427</v>
           </cell>
         </row>
         <row r="17">
@@ -604,10 +606,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>34306</v>
+            <v>36027</v>
           </cell>
           <cell r="D17">
-            <v>2638.9230769230771</v>
+            <v>2573.3571428571427</v>
           </cell>
         </row>
         <row r="18">
@@ -618,10 +620,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>9028</v>
+            <v>9499</v>
           </cell>
           <cell r="D18">
-            <v>694.46153846153845</v>
+            <v>678.5</v>
           </cell>
         </row>
         <row r="19">
@@ -632,10 +634,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>10246</v>
+            <v>10771</v>
           </cell>
           <cell r="D19">
-            <v>788.15384615384619</v>
+            <v>769.35714285714289</v>
           </cell>
         </row>
         <row r="20">
@@ -646,10 +648,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>10891</v>
+            <v>11462</v>
           </cell>
           <cell r="D20">
-            <v>837.76923076923072</v>
+            <v>818.71428571428567</v>
           </cell>
         </row>
         <row r="21">
@@ -660,10 +662,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>3252</v>
+            <v>3408</v>
           </cell>
           <cell r="D21">
-            <v>250.15384615384616</v>
+            <v>243.42857142857142</v>
           </cell>
         </row>
         <row r="22">
@@ -674,10 +676,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>1539</v>
+            <v>1626</v>
           </cell>
           <cell r="D22">
-            <v>118.38461538461539</v>
+            <v>116.14285714285714</v>
           </cell>
         </row>
         <row r="23">
@@ -688,10 +690,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>6467</v>
+            <v>6771</v>
           </cell>
           <cell r="D23">
-            <v>497.46153846153845</v>
+            <v>483.64285714285717</v>
           </cell>
         </row>
         <row r="24">
@@ -702,10 +704,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>10679</v>
+            <v>11392</v>
           </cell>
           <cell r="D24">
-            <v>821.46153846153845</v>
+            <v>813.71428571428567</v>
           </cell>
         </row>
         <row r="25">
@@ -716,10 +718,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>960</v>
+            <v>992</v>
           </cell>
           <cell r="D25">
-            <v>73.84615384615384</v>
+            <v>70.857142857142861</v>
           </cell>
         </row>
         <row r="26">
@@ -730,10 +732,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>9110</v>
+            <v>9604</v>
           </cell>
           <cell r="D26">
-            <v>700.76923076923072</v>
+            <v>686</v>
           </cell>
         </row>
         <row r="27">
@@ -744,10 +746,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>14646</v>
+            <v>15085</v>
           </cell>
           <cell r="D27">
-            <v>1126.6153846153845</v>
+            <v>1077.5</v>
           </cell>
         </row>
         <row r="28">
@@ -758,10 +760,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>7137</v>
+            <v>7550</v>
           </cell>
           <cell r="D28">
-            <v>549</v>
+            <v>539.28571428571433</v>
           </cell>
         </row>
         <row r="29">
@@ -772,10 +774,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>5575</v>
+            <v>5884</v>
           </cell>
           <cell r="D29">
-            <v>428.84615384615387</v>
+            <v>420.28571428571428</v>
           </cell>
         </row>
         <row r="30">
@@ -786,10 +788,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>3113</v>
+            <v>3202</v>
           </cell>
           <cell r="D30">
-            <v>239.46153846153845</v>
+            <v>228.71428571428572</v>
           </cell>
         </row>
         <row r="31">
@@ -800,10 +802,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>3766</v>
+            <v>3847</v>
           </cell>
           <cell r="D31">
-            <v>289.69230769230768</v>
+            <v>274.78571428571428</v>
           </cell>
         </row>
         <row r="32">
@@ -814,10 +816,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>1651</v>
+            <v>1696</v>
           </cell>
           <cell r="D32">
-            <v>127</v>
+            <v>121.14285714285714</v>
           </cell>
         </row>
         <row r="33">
@@ -828,10 +830,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>1690</v>
+            <v>1864</v>
           </cell>
           <cell r="D33">
-            <v>130</v>
+            <v>133.14285714285714</v>
           </cell>
         </row>
         <row r="34">
@@ -842,10 +844,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>9699</v>
+            <v>10293</v>
           </cell>
           <cell r="D34">
-            <v>746.07692307692309</v>
+            <v>735.21428571428567</v>
           </cell>
         </row>
         <row r="35">
@@ -856,10 +858,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>7466</v>
+            <v>8032</v>
           </cell>
           <cell r="D35">
-            <v>574.30769230769226</v>
+            <v>573.71428571428567</v>
           </cell>
         </row>
         <row r="36">
@@ -870,10 +872,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>10025</v>
+            <v>10763</v>
           </cell>
           <cell r="D36">
-            <v>771.15384615384619</v>
+            <v>768.78571428571433</v>
           </cell>
         </row>
         <row r="37">
@@ -884,10 +886,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>6509</v>
+            <v>6944</v>
           </cell>
           <cell r="D37">
-            <v>500.69230769230768</v>
+            <v>496</v>
           </cell>
         </row>
         <row r="38">
@@ -898,10 +900,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>52</v>
+            <v>54</v>
           </cell>
           <cell r="D38">
-            <v>4</v>
+            <v>3.8571428571428572</v>
           </cell>
         </row>
         <row r="39">
@@ -915,7 +917,7 @@
             <v>7</v>
           </cell>
           <cell r="D39">
-            <v>0.53846153846153844</v>
+            <v>0.5</v>
           </cell>
         </row>
         <row r="40">
@@ -926,10 +928,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>1851</v>
+            <v>1944</v>
           </cell>
           <cell r="D40">
-            <v>142.38461538461539</v>
+            <v>138.85714285714286</v>
           </cell>
         </row>
         <row r="41">
@@ -940,10 +942,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>6864</v>
+            <v>7380</v>
           </cell>
           <cell r="D41">
-            <v>528</v>
+            <v>527.14285714285711</v>
           </cell>
         </row>
         <row r="42">
@@ -954,10 +956,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>5434</v>
+            <v>5762</v>
           </cell>
           <cell r="D42">
-            <v>418</v>
+            <v>411.57142857142856</v>
           </cell>
         </row>
         <row r="43">
@@ -968,10 +970,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>2523</v>
+            <v>2854</v>
           </cell>
           <cell r="D43">
-            <v>194.07692307692307</v>
+            <v>203.85714285714286</v>
           </cell>
         </row>
         <row r="44">
@@ -982,10 +984,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>5958</v>
+            <v>6379</v>
           </cell>
           <cell r="D44">
-            <v>458.30769230769232</v>
+            <v>455.64285714285717</v>
           </cell>
         </row>
         <row r="45">
@@ -996,10 +998,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>3719</v>
+            <v>3942</v>
           </cell>
           <cell r="D45">
-            <v>286.07692307692309</v>
+            <v>281.57142857142856</v>
           </cell>
         </row>
         <row r="46">
@@ -1010,10 +1012,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>2894</v>
+            <v>3878</v>
           </cell>
           <cell r="D46">
-            <v>222.61538461538461</v>
+            <v>277</v>
           </cell>
         </row>
         <row r="47">
@@ -1024,10 +1026,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>468</v>
+            <v>775</v>
           </cell>
           <cell r="D47">
-            <v>36</v>
+            <v>55.357142857142854</v>
           </cell>
         </row>
         <row r="48">
@@ -1038,10 +1040,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>1359</v>
+            <v>1809</v>
           </cell>
           <cell r="D48">
-            <v>104.53846153846153</v>
+            <v>129.21428571428572</v>
           </cell>
         </row>
         <row r="49">
@@ -1055,7 +1057,7 @@
             <v>561</v>
           </cell>
           <cell r="D49">
-            <v>43.153846153846153</v>
+            <v>40.071428571428569</v>
           </cell>
         </row>
         <row r="50">
@@ -1066,14 +1068,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>740</v>
+            <v>742</v>
           </cell>
           <cell r="D50">
-            <v>56.92307692307692</v>
+            <v>53</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1420,11 +1422,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>15880</v>
+        <v>16741</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1221.5384615384614</v>
+        <v>1195.7857142857142</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1438,11 +1440,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>66.92307692307692</v>
+        <v>62.785714285714285</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1456,11 +1458,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>6480</v>
+        <v>6771</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>498.46153846153845</v>
+        <v>483.64285714285717</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1474,11 +1476,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1508</v>
+        <v>1547</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>116</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1496,7 +1498,7 @@
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>14.846153846153847</v>
+        <v>13.785714285714286</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1510,11 +1512,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>18704</v>
+        <v>19721</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1438.7692307692307</v>
+        <v>1408.6428571428571</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1528,11 +1530,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1877</v>
+        <v>2006</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>144.38461538461539</v>
+        <v>143.28571428571428</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1546,11 +1548,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>3654</v>
+        <v>4057</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>281.07692307692309</v>
+        <v>289.78571428571428</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1564,11 +1566,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>9467</v>
+        <v>10147</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>728.23076923076928</v>
+        <v>724.78571428571433</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1582,11 +1584,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>4436</v>
+        <v>4787</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>341.23076923076923</v>
+        <v>341.92857142857144</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1600,11 +1602,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>44744</v>
+        <v>46685</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3441.8461538461538</v>
+        <v>3334.6428571428573</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1618,11 +1620,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>27639</v>
+        <v>28881</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2126.0769230769229</v>
+        <v>2062.9285714285716</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1636,11 +1638,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>28167</v>
+        <v>29573</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2166.6923076923076</v>
+        <v>2112.3571428571427</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1654,11 +1656,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>34306</v>
+        <v>36027</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2638.9230769230771</v>
+        <v>2573.3571428571427</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1672,11 +1674,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>9028</v>
+        <v>9499</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>694.46153846153845</v>
+        <v>678.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1690,11 +1692,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>10246</v>
+        <v>10771</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>788.15384615384619</v>
+        <v>769.35714285714289</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1708,11 +1710,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>10891</v>
+        <v>11462</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>837.76923076923072</v>
+        <v>818.71428571428567</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1726,11 +1728,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>3252</v>
+        <v>3408</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>250.15384615384616</v>
+        <v>243.42857142857142</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1744,11 +1746,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1539</v>
+        <v>1626</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>118.38461538461539</v>
+        <v>116.14285714285714</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1762,11 +1764,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>6467</v>
+        <v>6771</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>497.46153846153845</v>
+        <v>483.64285714285717</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1780,11 +1782,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>10679</v>
+        <v>11392</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>821.46153846153845</v>
+        <v>813.71428571428567</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1798,11 +1800,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>960</v>
+        <v>992</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>73.84615384615384</v>
+        <v>70.857142857142861</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1816,11 +1818,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>9110</v>
+        <v>9604</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>700.76923076923072</v>
+        <v>686</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1834,11 +1836,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>14646</v>
+        <v>15085</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1126.6153846153845</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1852,11 +1854,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>7137</v>
+        <v>7550</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>549</v>
+        <v>539.28571428571433</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1870,11 +1872,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>5575</v>
+        <v>5884</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>428.84615384615387</v>
+        <v>420.28571428571428</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1888,11 +1890,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>3113</v>
+        <v>3202</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>239.46153846153845</v>
+        <v>228.71428571428572</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1906,11 +1908,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>3766</v>
+        <v>3847</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>289.69230769230768</v>
+        <v>274.78571428571428</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1924,11 +1926,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1651</v>
+        <v>1696</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>127</v>
+        <v>121.14285714285714</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1942,11 +1944,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1690</v>
+        <v>1864</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>130</v>
+        <v>133.14285714285714</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1960,11 +1962,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>9699</v>
+        <v>10293</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>746.07692307692309</v>
+        <v>735.21428571428567</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1978,11 +1980,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>7466</v>
+        <v>8032</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>574.30769230769226</v>
+        <v>573.71428571428567</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1996,11 +1998,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>10025</v>
+        <v>10763</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>771.15384615384619</v>
+        <v>768.78571428571433</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2014,11 +2016,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>6509</v>
+        <v>6944</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>500.69230769230768</v>
+        <v>496</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2032,11 +2034,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4</v>
+        <v>3.8571428571428572</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2054,7 +2056,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.53846153846153844</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2068,11 +2070,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1851</v>
+        <v>1944</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>142.38461538461539</v>
+        <v>138.85714285714286</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2086,11 +2088,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>6864</v>
+        <v>7380</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>528</v>
+        <v>527.14285714285711</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2104,11 +2106,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>5434</v>
+        <v>5762</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>418</v>
+        <v>411.57142857142856</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2122,11 +2124,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>2523</v>
+        <v>2854</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>194.07692307692307</v>
+        <v>203.85714285714286</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2140,11 +2142,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>5958</v>
+        <v>6379</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>458.30769230769232</v>
+        <v>455.64285714285717</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2158,11 +2160,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>3719</v>
+        <v>3942</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>286.07692307692309</v>
+        <v>281.57142857142856</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2176,11 +2178,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>2894</v>
+        <v>3878</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>222.61538461538461</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2194,11 +2196,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>468</v>
+        <v>775</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>36</v>
+        <v>55.357142857142854</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2212,11 +2214,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1359</v>
+        <v>1809</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>104.53846153846153</v>
+        <v>129.21428571428572</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2234,7 +2236,7 @@
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>43.153846153846153</v>
+        <v>40.071428571428569</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2248,11 +2250,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>56.92307692307692</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2317,19 +2319,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>363804</v>
+        <v>384787</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>353965</v>
+        <v>374948</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>27984.923076923078</v>
+        <v>27484.785714285714</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>615668.30769230775</v>
+        <v>604665.28571428568</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2337,11 +2339,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.54049749588094331</v>
+        <v>0.57167158675424279</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-57422.692307692254</v>
+        <v>-68425.714285714319</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2382,7 +2384,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2390,11 +2392,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D206DA8-7F8A-40B1-A726-1070722BF1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EE98DD-8D61-4EA7-BE9D-03C847AB9769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -304,7 +304,8 @@
       <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-09-16;15"/>
       <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
-      <sheetName val="INVENTARIO NACIONAL 20-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 21-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -328,7 +329,8 @@
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
-      <sheetData sheetId="17">
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -359,25 +361,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>384787</v>
+            <v>417321</v>
           </cell>
           <cell r="H3">
-            <v>374948</v>
+            <v>405623</v>
           </cell>
           <cell r="I3">
-            <v>27484.785714285714</v>
+            <v>27821.4</v>
           </cell>
           <cell r="J3">
-            <v>604665.28571428568</v>
+            <v>612070.80000000005</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.57167158675424279</v>
+            <v>0.62000680442911882</v>
           </cell>
           <cell r="M3">
-            <v>-68425.714285714319</v>
+            <v>-61020.199999999953</v>
           </cell>
         </row>
         <row r="4">
@@ -388,10 +390,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>16741</v>
+            <v>18070</v>
           </cell>
           <cell r="D4">
-            <v>1195.7857142857142</v>
+            <v>1204.6666666666667</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -420,28 +422,28 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>879</v>
+            <v>886</v>
           </cell>
           <cell r="D5">
-            <v>62.785714285714285</v>
+            <v>59.06666666666667</v>
           </cell>
           <cell r="G5">
-            <v>9839</v>
+            <v>11698</v>
           </cell>
           <cell r="H5">
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46286</v>
+            <v>46287</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>14</v>
+            <v>15</v>
           </cell>
           <cell r="L5">
-            <v>8</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="6">
@@ -452,10 +454,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>6771</v>
+            <v>7427</v>
           </cell>
           <cell r="D6">
-            <v>483.64285714285717</v>
+            <v>495.13333333333333</v>
           </cell>
         </row>
         <row r="7">
@@ -466,10 +468,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1547</v>
+            <v>1581</v>
           </cell>
           <cell r="D7">
-            <v>110.5</v>
+            <v>105.4</v>
           </cell>
         </row>
         <row r="8">
@@ -480,10 +482,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>193</v>
+            <v>198</v>
           </cell>
           <cell r="D8">
-            <v>13.785714285714286</v>
+            <v>13.2</v>
           </cell>
         </row>
         <row r="9">
@@ -494,10 +496,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>19721</v>
+            <v>21334</v>
           </cell>
           <cell r="D9">
-            <v>1408.6428571428571</v>
+            <v>1422.2666666666667</v>
           </cell>
         </row>
         <row r="10">
@@ -508,10 +510,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>2006</v>
+            <v>2150</v>
           </cell>
           <cell r="D10">
-            <v>143.28571428571428</v>
+            <v>143.33333333333334</v>
           </cell>
         </row>
         <row r="11">
@@ -522,10 +524,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>4057</v>
+            <v>4435</v>
           </cell>
           <cell r="D11">
-            <v>289.78571428571428</v>
+            <v>295.66666666666669</v>
           </cell>
         </row>
         <row r="12">
@@ -536,10 +538,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>10147</v>
+            <v>11094</v>
           </cell>
           <cell r="D12">
-            <v>724.78571428571433</v>
+            <v>739.6</v>
           </cell>
         </row>
         <row r="13">
@@ -550,10 +552,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>4787</v>
+            <v>5269</v>
           </cell>
           <cell r="D13">
-            <v>341.92857142857144</v>
+            <v>351.26666666666665</v>
           </cell>
         </row>
         <row r="14">
@@ -564,10 +566,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>46685</v>
+            <v>50379</v>
           </cell>
           <cell r="D14">
-            <v>3334.6428571428573</v>
+            <v>3358.6</v>
           </cell>
         </row>
         <row r="15">
@@ -578,10 +580,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>28881</v>
+            <v>31208</v>
           </cell>
           <cell r="D15">
-            <v>2062.9285714285716</v>
+            <v>2080.5333333333333</v>
           </cell>
         </row>
         <row r="16">
@@ -592,10 +594,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>29573</v>
+            <v>31812</v>
           </cell>
           <cell r="D16">
-            <v>2112.3571428571427</v>
+            <v>2120.8000000000002</v>
           </cell>
         </row>
         <row r="17">
@@ -606,10 +608,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>36027</v>
+            <v>39028</v>
           </cell>
           <cell r="D17">
-            <v>2573.3571428571427</v>
+            <v>2601.8666666666668</v>
           </cell>
         </row>
         <row r="18">
@@ -620,10 +622,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>9499</v>
+            <v>10232</v>
           </cell>
           <cell r="D18">
-            <v>678.5</v>
+            <v>682.13333333333333</v>
           </cell>
         </row>
         <row r="19">
@@ -634,10 +636,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>10771</v>
+            <v>11727</v>
           </cell>
           <cell r="D19">
-            <v>769.35714285714289</v>
+            <v>781.8</v>
           </cell>
         </row>
         <row r="20">
@@ -648,10 +650,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>11462</v>
+            <v>12476</v>
           </cell>
           <cell r="D20">
-            <v>818.71428571428567</v>
+            <v>831.73333333333335</v>
           </cell>
         </row>
         <row r="21">
@@ -662,10 +664,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>3408</v>
+            <v>3867</v>
           </cell>
           <cell r="D21">
-            <v>243.42857142857142</v>
+            <v>257.8</v>
           </cell>
         </row>
         <row r="22">
@@ -676,10 +678,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>1626</v>
+            <v>1813</v>
           </cell>
           <cell r="D22">
-            <v>116.14285714285714</v>
+            <v>120.86666666666666</v>
           </cell>
         </row>
         <row r="23">
@@ -690,10 +692,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>6771</v>
+            <v>7457</v>
           </cell>
           <cell r="D23">
-            <v>483.64285714285717</v>
+            <v>497.13333333333333</v>
           </cell>
         </row>
         <row r="24">
@@ -704,10 +706,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>11392</v>
+            <v>12427</v>
           </cell>
           <cell r="D24">
-            <v>813.71428571428567</v>
+            <v>828.4666666666667</v>
           </cell>
         </row>
         <row r="25">
@@ -718,10 +720,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>992</v>
+            <v>1032</v>
           </cell>
           <cell r="D25">
-            <v>70.857142857142861</v>
+            <v>68.8</v>
           </cell>
         </row>
         <row r="26">
@@ -732,10 +734,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>9604</v>
+            <v>10450</v>
           </cell>
           <cell r="D26">
-            <v>686</v>
+            <v>696.66666666666663</v>
           </cell>
         </row>
         <row r="27">
@@ -746,10 +748,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>15085</v>
+            <v>16272</v>
           </cell>
           <cell r="D27">
-            <v>1077.5</v>
+            <v>1084.8</v>
           </cell>
         </row>
         <row r="28">
@@ -760,10 +762,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>7550</v>
+            <v>8112</v>
           </cell>
           <cell r="D28">
-            <v>539.28571428571433</v>
+            <v>540.79999999999995</v>
           </cell>
         </row>
         <row r="29">
@@ -774,10 +776,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>5884</v>
+            <v>6149</v>
           </cell>
           <cell r="D29">
-            <v>420.28571428571428</v>
+            <v>409.93333333333334</v>
           </cell>
         </row>
         <row r="30">
@@ -788,10 +790,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>3202</v>
+            <v>3650</v>
           </cell>
           <cell r="D30">
-            <v>228.71428571428572</v>
+            <v>243.33333333333334</v>
           </cell>
         </row>
         <row r="31">
@@ -802,10 +804,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>3847</v>
+            <v>4496</v>
           </cell>
           <cell r="D31">
-            <v>274.78571428571428</v>
+            <v>299.73333333333335</v>
           </cell>
         </row>
         <row r="32">
@@ -816,10 +818,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>1696</v>
+            <v>1861</v>
           </cell>
           <cell r="D32">
-            <v>121.14285714285714</v>
+            <v>124.06666666666666</v>
           </cell>
         </row>
         <row r="33">
@@ -830,10 +832,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>1864</v>
+            <v>2015</v>
           </cell>
           <cell r="D33">
-            <v>133.14285714285714</v>
+            <v>134.33333333333334</v>
           </cell>
         </row>
         <row r="34">
@@ -844,10 +846,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>10293</v>
+            <v>11075</v>
           </cell>
           <cell r="D34">
-            <v>735.21428571428567</v>
+            <v>738.33333333333337</v>
           </cell>
         </row>
         <row r="35">
@@ -858,10 +860,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>8032</v>
+            <v>8749</v>
           </cell>
           <cell r="D35">
-            <v>573.71428571428567</v>
+            <v>583.26666666666665</v>
           </cell>
         </row>
         <row r="36">
@@ -872,10 +874,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>10763</v>
+            <v>11595</v>
           </cell>
           <cell r="D36">
-            <v>768.78571428571433</v>
+            <v>773</v>
           </cell>
         </row>
         <row r="37">
@@ -886,10 +888,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>6944</v>
+            <v>7597</v>
           </cell>
           <cell r="D37">
-            <v>496</v>
+            <v>506.46666666666664</v>
           </cell>
         </row>
         <row r="38">
@@ -900,10 +902,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>54</v>
+            <v>55</v>
           </cell>
           <cell r="D38">
-            <v>3.8571428571428572</v>
+            <v>3.6666666666666665</v>
           </cell>
         </row>
         <row r="39">
@@ -917,7 +919,7 @@
             <v>7</v>
           </cell>
           <cell r="D39">
-            <v>0.5</v>
+            <v>0.46666666666666667</v>
           </cell>
         </row>
         <row r="40">
@@ -928,10 +930,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>1944</v>
+            <v>2131</v>
           </cell>
           <cell r="D40">
-            <v>138.85714285714286</v>
+            <v>142.06666666666666</v>
           </cell>
         </row>
         <row r="41">
@@ -942,10 +944,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>7380</v>
+            <v>8098</v>
           </cell>
           <cell r="D41">
-            <v>527.14285714285711</v>
+            <v>539.86666666666667</v>
           </cell>
         </row>
         <row r="42">
@@ -956,10 +958,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>5762</v>
+            <v>6157</v>
           </cell>
           <cell r="D42">
-            <v>411.57142857142856</v>
+            <v>410.46666666666664</v>
           </cell>
         </row>
         <row r="43">
@@ -970,10 +972,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>2854</v>
+            <v>3125</v>
           </cell>
           <cell r="D43">
-            <v>203.85714285714286</v>
+            <v>208.33333333333334</v>
           </cell>
         </row>
         <row r="44">
@@ -984,10 +986,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>6379</v>
+            <v>7083</v>
           </cell>
           <cell r="D44">
-            <v>455.64285714285717</v>
+            <v>472.2</v>
           </cell>
         </row>
         <row r="45">
@@ -998,10 +1000,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>3942</v>
+            <v>4214</v>
           </cell>
           <cell r="D45">
-            <v>281.57142857142856</v>
+            <v>280.93333333333334</v>
           </cell>
         </row>
         <row r="46">
@@ -1012,10 +1014,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>3878</v>
+            <v>4258</v>
           </cell>
           <cell r="D46">
-            <v>277</v>
+            <v>283.86666666666667</v>
           </cell>
         </row>
         <row r="47">
@@ -1026,10 +1028,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>775</v>
+            <v>867</v>
           </cell>
           <cell r="D47">
-            <v>55.357142857142854</v>
+            <v>57.8</v>
           </cell>
         </row>
         <row r="48">
@@ -1040,10 +1042,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>1809</v>
+            <v>1954</v>
           </cell>
           <cell r="D48">
-            <v>129.21428571428572</v>
+            <v>130.26666666666668</v>
           </cell>
         </row>
         <row r="49">
@@ -1054,10 +1056,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>561</v>
+            <v>658</v>
           </cell>
           <cell r="D49">
-            <v>40.071428571428569</v>
+            <v>43.866666666666667</v>
           </cell>
         </row>
         <row r="50">
@@ -1068,14 +1070,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>742</v>
+            <v>791</v>
           </cell>
           <cell r="D50">
-            <v>53</v>
+            <v>52.733333333333334</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1422,11 +1424,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>16741</v>
+        <v>18070</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1195.7857142857142</v>
+        <v>1204.6666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1440,11 +1442,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>62.785714285714285</v>
+        <v>59.06666666666667</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1458,11 +1460,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>6771</v>
+        <v>7427</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>483.64285714285717</v>
+        <v>495.13333333333333</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,11 +1478,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1547</v>
+        <v>1581</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>110.5</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,11 +1496,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>13.785714285714286</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1512,11 +1514,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>19721</v>
+        <v>21334</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1408.6428571428571</v>
+        <v>1422.2666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1530,11 +1532,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2006</v>
+        <v>2150</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>143.28571428571428</v>
+        <v>143.33333333333334</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1548,11 +1550,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>4057</v>
+        <v>4435</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>289.78571428571428</v>
+        <v>295.66666666666669</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1566,11 +1568,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>10147</v>
+        <v>11094</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>724.78571428571433</v>
+        <v>739.6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1584,11 +1586,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>4787</v>
+        <v>5269</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>341.92857142857144</v>
+        <v>351.26666666666665</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1602,11 +1604,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>46685</v>
+        <v>50379</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3334.6428571428573</v>
+        <v>3358.6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,11 +1622,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>28881</v>
+        <v>31208</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2062.9285714285716</v>
+        <v>2080.5333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1638,11 +1640,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>29573</v>
+        <v>31812</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2112.3571428571427</v>
+        <v>2120.8000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1656,11 +1658,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>36027</v>
+        <v>39028</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2573.3571428571427</v>
+        <v>2601.8666666666668</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1674,11 +1676,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>9499</v>
+        <v>10232</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>678.5</v>
+        <v>682.13333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1692,11 +1694,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>10771</v>
+        <v>11727</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>769.35714285714289</v>
+        <v>781.8</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1710,11 +1712,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>11462</v>
+        <v>12476</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>818.71428571428567</v>
+        <v>831.73333333333335</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1728,11 +1730,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>3408</v>
+        <v>3867</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>243.42857142857142</v>
+        <v>257.8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1746,11 +1748,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1626</v>
+        <v>1813</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>116.14285714285714</v>
+        <v>120.86666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1764,11 +1766,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>6771</v>
+        <v>7457</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>483.64285714285717</v>
+        <v>497.13333333333333</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1782,11 +1784,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>11392</v>
+        <v>12427</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>813.71428571428567</v>
+        <v>828.4666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1800,11 +1802,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>992</v>
+        <v>1032</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>70.857142857142861</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1818,11 +1820,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>9604</v>
+        <v>10450</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>686</v>
+        <v>696.66666666666663</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1836,11 +1838,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>15085</v>
+        <v>16272</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1077.5</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1854,11 +1856,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>7550</v>
+        <v>8112</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>539.28571428571433</v>
+        <v>540.79999999999995</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1872,11 +1874,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>5884</v>
+        <v>6149</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>420.28571428571428</v>
+        <v>409.93333333333334</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,11 +1892,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>3202</v>
+        <v>3650</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>228.71428571428572</v>
+        <v>243.33333333333334</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1908,11 +1910,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>3847</v>
+        <v>4496</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>274.78571428571428</v>
+        <v>299.73333333333335</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1926,11 +1928,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1696</v>
+        <v>1861</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>121.14285714285714</v>
+        <v>124.06666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1944,11 +1946,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1864</v>
+        <v>2015</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>133.14285714285714</v>
+        <v>134.33333333333334</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1962,11 +1964,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>10293</v>
+        <v>11075</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>735.21428571428567</v>
+        <v>738.33333333333337</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1980,11 +1982,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>8032</v>
+        <v>8749</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>573.71428571428567</v>
+        <v>583.26666666666665</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1998,11 +2000,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>10763</v>
+        <v>11595</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>768.78571428571433</v>
+        <v>773</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2016,11 +2018,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>6944</v>
+        <v>7597</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>496</v>
+        <v>506.46666666666664</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2034,11 +2036,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>3.8571428571428572</v>
+        <v>3.6666666666666665</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2056,7 +2058,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.5</v>
+        <v>0.46666666666666667</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2070,11 +2072,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1944</v>
+        <v>2131</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>138.85714285714286</v>
+        <v>142.06666666666666</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2088,11 +2090,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>7380</v>
+        <v>8098</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>527.14285714285711</v>
+        <v>539.86666666666667</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2106,11 +2108,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>5762</v>
+        <v>6157</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>411.57142857142856</v>
+        <v>410.46666666666664</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2124,11 +2126,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>2854</v>
+        <v>3125</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>203.85714285714286</v>
+        <v>208.33333333333334</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2142,11 +2144,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>6379</v>
+        <v>7083</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>455.64285714285717</v>
+        <v>472.2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2160,11 +2162,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>3942</v>
+        <v>4214</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>281.57142857142856</v>
+        <v>280.93333333333334</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2178,11 +2180,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>3878</v>
+        <v>4258</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>277</v>
+        <v>283.86666666666667</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2196,11 +2198,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>775</v>
+        <v>867</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>55.357142857142854</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2214,11 +2216,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1809</v>
+        <v>1954</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>129.21428571428572</v>
+        <v>130.26666666666668</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2232,11 +2234,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>561</v>
+        <v>658</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>40.071428571428569</v>
+        <v>43.866666666666667</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2250,11 +2252,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>742</v>
+        <v>791</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>53</v>
+        <v>52.733333333333334</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2319,19 +2321,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>384787</v>
+        <v>417321</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>374948</v>
+        <v>405623</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>27484.785714285714</v>
+        <v>27821.4</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>604665.28571428568</v>
+        <v>612070.80000000005</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2339,11 +2341,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.57167158675424279</v>
+        <v>0.62000680442911882</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-68425.714285714319</v>
+        <v>-61020.199999999953</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2376,7 +2378,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>9839</v>
+        <v>11698</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2384,7 +2386,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2392,11 +2394,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EE98DD-8D61-4EA7-BE9D-03C847AB9769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F9107C-5670-4E70-B4C7-8AA1C6B7D8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -306,6 +306,7 @@
       <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 21-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -330,7 +331,8 @@
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
-      <sheetData sheetId="18">
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -361,25 +363,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>417321</v>
+            <v>451601</v>
           </cell>
           <cell r="H3">
-            <v>405623</v>
+            <v>439903</v>
           </cell>
           <cell r="I3">
-            <v>27821.4</v>
+            <v>28225.0625</v>
           </cell>
           <cell r="J3">
-            <v>612070.80000000005</v>
+            <v>620951.375</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.62000680442911882</v>
+            <v>0.67093602499513438</v>
           </cell>
           <cell r="M3">
-            <v>-61020.199999999953</v>
+            <v>-52139.625</v>
           </cell>
         </row>
         <row r="4">
@@ -390,10 +392,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>18070</v>
+            <v>19299</v>
           </cell>
           <cell r="D4">
-            <v>1204.6666666666667</v>
+            <v>1206.1875</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -425,7 +427,7 @@
             <v>886</v>
           </cell>
           <cell r="D5">
-            <v>59.06666666666667</v>
+            <v>55.375</v>
           </cell>
           <cell r="G5">
             <v>11698</v>
@@ -434,16 +436,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46287</v>
+            <v>46288</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>15</v>
+            <v>16</v>
           </cell>
           <cell r="L5">
-            <v>7</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="6">
@@ -454,10 +456,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>7427</v>
+            <v>7890</v>
           </cell>
           <cell r="D6">
-            <v>495.13333333333333</v>
+            <v>493.125</v>
           </cell>
         </row>
         <row r="7">
@@ -468,10 +470,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1581</v>
+            <v>1720</v>
           </cell>
           <cell r="D7">
-            <v>105.4</v>
+            <v>107.5</v>
           </cell>
         </row>
         <row r="8">
@@ -482,10 +484,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>198</v>
+            <v>211</v>
           </cell>
           <cell r="D8">
-            <v>13.2</v>
+            <v>13.1875</v>
           </cell>
         </row>
         <row r="9">
@@ -496,10 +498,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>21334</v>
+            <v>22733</v>
           </cell>
           <cell r="D9">
-            <v>1422.2666666666667</v>
+            <v>1420.8125</v>
           </cell>
         </row>
         <row r="10">
@@ -510,10 +512,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>2150</v>
+            <v>2360</v>
           </cell>
           <cell r="D10">
-            <v>143.33333333333334</v>
+            <v>147.5</v>
           </cell>
         </row>
         <row r="11">
@@ -524,10 +526,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>4435</v>
+            <v>4908</v>
           </cell>
           <cell r="D11">
-            <v>295.66666666666669</v>
+            <v>306.75</v>
           </cell>
         </row>
         <row r="12">
@@ -538,10 +540,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>11094</v>
+            <v>12273</v>
           </cell>
           <cell r="D12">
-            <v>739.6</v>
+            <v>767.0625</v>
           </cell>
         </row>
         <row r="13">
@@ -552,10 +554,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>5269</v>
+            <v>5896</v>
           </cell>
           <cell r="D13">
-            <v>351.26666666666665</v>
+            <v>368.5</v>
           </cell>
         </row>
         <row r="14">
@@ -566,10 +568,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>50379</v>
+            <v>53757</v>
           </cell>
           <cell r="D14">
-            <v>3358.6</v>
+            <v>3359.8125</v>
           </cell>
         </row>
         <row r="15">
@@ -580,10 +582,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>31208</v>
+            <v>33632</v>
           </cell>
           <cell r="D15">
-            <v>2080.5333333333333</v>
+            <v>2102</v>
           </cell>
         </row>
         <row r="16">
@@ -594,10 +596,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>31812</v>
+            <v>34271</v>
           </cell>
           <cell r="D16">
-            <v>2120.8000000000002</v>
+            <v>2141.9375</v>
           </cell>
         </row>
         <row r="17">
@@ -608,10 +610,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>39028</v>
+            <v>41780</v>
           </cell>
           <cell r="D17">
-            <v>2601.8666666666668</v>
+            <v>2611.25</v>
           </cell>
         </row>
         <row r="18">
@@ -622,10 +624,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>10232</v>
+            <v>11351</v>
           </cell>
           <cell r="D18">
-            <v>682.13333333333333</v>
+            <v>709.4375</v>
           </cell>
         </row>
         <row r="19">
@@ -636,10 +638,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>11727</v>
+            <v>13015</v>
           </cell>
           <cell r="D19">
-            <v>781.8</v>
+            <v>813.4375</v>
           </cell>
         </row>
         <row r="20">
@@ -650,10 +652,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>12476</v>
+            <v>13714</v>
           </cell>
           <cell r="D20">
-            <v>831.73333333333335</v>
+            <v>857.125</v>
           </cell>
         </row>
         <row r="21">
@@ -664,10 +666,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>3867</v>
+            <v>4348</v>
           </cell>
           <cell r="D21">
-            <v>257.8</v>
+            <v>271.75</v>
           </cell>
         </row>
         <row r="22">
@@ -678,10 +680,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>1813</v>
+            <v>2044</v>
           </cell>
           <cell r="D22">
-            <v>120.86666666666666</v>
+            <v>127.75</v>
           </cell>
         </row>
         <row r="23">
@@ -692,10 +694,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>7457</v>
+            <v>8083</v>
           </cell>
           <cell r="D23">
-            <v>497.13333333333333</v>
+            <v>505.1875</v>
           </cell>
         </row>
         <row r="24">
@@ -706,10 +708,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>12427</v>
+            <v>13592</v>
           </cell>
           <cell r="D24">
-            <v>828.4666666666667</v>
+            <v>849.5</v>
           </cell>
         </row>
         <row r="25">
@@ -723,7 +725,7 @@
             <v>1032</v>
           </cell>
           <cell r="D25">
-            <v>68.8</v>
+            <v>64.5</v>
           </cell>
         </row>
         <row r="26">
@@ -734,10 +736,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>10450</v>
+            <v>11229</v>
           </cell>
           <cell r="D26">
-            <v>696.66666666666663</v>
+            <v>701.8125</v>
           </cell>
         </row>
         <row r="27">
@@ -748,10 +750,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>16272</v>
+            <v>17504</v>
           </cell>
           <cell r="D27">
-            <v>1084.8</v>
+            <v>1094</v>
           </cell>
         </row>
         <row r="28">
@@ -762,10 +764,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>8112</v>
+            <v>9032</v>
           </cell>
           <cell r="D28">
-            <v>540.79999999999995</v>
+            <v>564.5</v>
           </cell>
         </row>
         <row r="29">
@@ -776,10 +778,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>6149</v>
+            <v>6754</v>
           </cell>
           <cell r="D29">
-            <v>409.93333333333334</v>
+            <v>422.125</v>
           </cell>
         </row>
         <row r="30">
@@ -790,10 +792,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>3650</v>
+            <v>3852</v>
           </cell>
           <cell r="D30">
-            <v>243.33333333333334</v>
+            <v>240.75</v>
           </cell>
         </row>
         <row r="31">
@@ -804,10 +806,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>4496</v>
+            <v>4653</v>
           </cell>
           <cell r="D31">
-            <v>299.73333333333335</v>
+            <v>290.8125</v>
           </cell>
         </row>
         <row r="32">
@@ -818,10 +820,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>1861</v>
+            <v>2103</v>
           </cell>
           <cell r="D32">
-            <v>124.06666666666666</v>
+            <v>131.4375</v>
           </cell>
         </row>
         <row r="33">
@@ -832,10 +834,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>2015</v>
+            <v>2199</v>
           </cell>
           <cell r="D33">
-            <v>134.33333333333334</v>
+            <v>137.4375</v>
           </cell>
         </row>
         <row r="34">
@@ -846,10 +848,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>11075</v>
+            <v>12158</v>
           </cell>
           <cell r="D34">
-            <v>738.33333333333337</v>
+            <v>759.875</v>
           </cell>
         </row>
         <row r="35">
@@ -860,10 +862,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>8749</v>
+            <v>9573</v>
           </cell>
           <cell r="D35">
-            <v>583.26666666666665</v>
+            <v>598.3125</v>
           </cell>
         </row>
         <row r="36">
@@ -874,10 +876,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>11595</v>
+            <v>12666</v>
           </cell>
           <cell r="D36">
-            <v>773</v>
+            <v>791.625</v>
           </cell>
         </row>
         <row r="37">
@@ -888,10 +890,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>7597</v>
+            <v>8317</v>
           </cell>
           <cell r="D37">
-            <v>506.46666666666664</v>
+            <v>519.8125</v>
           </cell>
         </row>
         <row r="38">
@@ -902,10 +904,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>55</v>
+            <v>58</v>
           </cell>
           <cell r="D38">
-            <v>3.6666666666666665</v>
+            <v>3.625</v>
           </cell>
         </row>
         <row r="39">
@@ -919,7 +921,7 @@
             <v>7</v>
           </cell>
           <cell r="D39">
-            <v>0.46666666666666667</v>
+            <v>0.4375</v>
           </cell>
         </row>
         <row r="40">
@@ -930,10 +932,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>2131</v>
+            <v>2345</v>
           </cell>
           <cell r="D40">
-            <v>142.06666666666666</v>
+            <v>146.5625</v>
           </cell>
         </row>
         <row r="41">
@@ -944,10 +946,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>8098</v>
+            <v>9088</v>
           </cell>
           <cell r="D41">
-            <v>539.86666666666667</v>
+            <v>568</v>
           </cell>
         </row>
         <row r="42">
@@ -958,10 +960,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>6157</v>
+            <v>6538</v>
           </cell>
           <cell r="D42">
-            <v>410.46666666666664</v>
+            <v>408.625</v>
           </cell>
         </row>
         <row r="43">
@@ -972,10 +974,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>3125</v>
+            <v>3409</v>
           </cell>
           <cell r="D43">
-            <v>208.33333333333334</v>
+            <v>213.0625</v>
           </cell>
         </row>
         <row r="44">
@@ -986,10 +988,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>7083</v>
+            <v>7651</v>
           </cell>
           <cell r="D44">
-            <v>472.2</v>
+            <v>478.1875</v>
           </cell>
         </row>
         <row r="45">
@@ -1000,10 +1002,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>4214</v>
+            <v>4500</v>
           </cell>
           <cell r="D45">
-            <v>280.93333333333334</v>
+            <v>281.25</v>
           </cell>
         </row>
         <row r="46">
@@ -1014,10 +1016,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>4258</v>
+            <v>4578</v>
           </cell>
           <cell r="D46">
-            <v>283.86666666666667</v>
+            <v>286.125</v>
           </cell>
         </row>
         <row r="47">
@@ -1028,10 +1030,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>867</v>
+            <v>944</v>
           </cell>
           <cell r="D47">
-            <v>57.8</v>
+            <v>59</v>
           </cell>
         </row>
         <row r="48">
@@ -1042,10 +1044,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>1954</v>
+            <v>2062</v>
           </cell>
           <cell r="D48">
-            <v>130.26666666666668</v>
+            <v>128.875</v>
           </cell>
         </row>
         <row r="49">
@@ -1056,10 +1058,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>658</v>
+            <v>702</v>
           </cell>
           <cell r="D49">
-            <v>43.866666666666667</v>
+            <v>43.875</v>
           </cell>
         </row>
         <row r="50">
@@ -1070,14 +1072,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>791</v>
+            <v>884</v>
           </cell>
           <cell r="D50">
-            <v>52.733333333333334</v>
+            <v>55.25</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1424,11 +1426,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>18070</v>
+        <v>19299</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1204.6666666666667</v>
+        <v>1206.1875</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1446,7 +1448,7 @@
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>59.06666666666667</v>
+        <v>55.375</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1460,11 +1462,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>7427</v>
+        <v>7890</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>495.13333333333333</v>
+        <v>493.125</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,11 +1480,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1581</v>
+        <v>1720</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>105.4</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1496,11 +1498,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>13.2</v>
+        <v>13.1875</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1514,11 +1516,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>21334</v>
+        <v>22733</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1422.2666666666667</v>
+        <v>1420.8125</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1532,11 +1534,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2150</v>
+        <v>2360</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>143.33333333333334</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1550,11 +1552,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>4435</v>
+        <v>4908</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>295.66666666666669</v>
+        <v>306.75</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1568,11 +1570,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>11094</v>
+        <v>12273</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>739.6</v>
+        <v>767.0625</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1586,11 +1588,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>5269</v>
+        <v>5896</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>351.26666666666665</v>
+        <v>368.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,11 +1606,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>50379</v>
+        <v>53757</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3358.6</v>
+        <v>3359.8125</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1622,11 +1624,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>31208</v>
+        <v>33632</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2080.5333333333333</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1640,11 +1642,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>31812</v>
+        <v>34271</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2120.8000000000002</v>
+        <v>2141.9375</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1658,11 +1660,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>39028</v>
+        <v>41780</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2601.8666666666668</v>
+        <v>2611.25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1676,11 +1678,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>10232</v>
+        <v>11351</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>682.13333333333333</v>
+        <v>709.4375</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1694,11 +1696,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>11727</v>
+        <v>13015</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>781.8</v>
+        <v>813.4375</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1712,11 +1714,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>12476</v>
+        <v>13714</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>831.73333333333335</v>
+        <v>857.125</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,11 +1732,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>3867</v>
+        <v>4348</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>257.8</v>
+        <v>271.75</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1748,11 +1750,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1813</v>
+        <v>2044</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>120.86666666666666</v>
+        <v>127.75</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1766,11 +1768,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>7457</v>
+        <v>8083</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>497.13333333333333</v>
+        <v>505.1875</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1784,11 +1786,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>12427</v>
+        <v>13592</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>828.4666666666667</v>
+        <v>849.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1806,7 +1808,7 @@
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>68.8</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1820,11 +1822,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>10450</v>
+        <v>11229</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>696.66666666666663</v>
+        <v>701.8125</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1838,11 +1840,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>16272</v>
+        <v>17504</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1084.8</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1856,11 +1858,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>8112</v>
+        <v>9032</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>540.79999999999995</v>
+        <v>564.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1874,11 +1876,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>6149</v>
+        <v>6754</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>409.93333333333334</v>
+        <v>422.125</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1892,11 +1894,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>3650</v>
+        <v>3852</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>243.33333333333334</v>
+        <v>240.75</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1910,11 +1912,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>4496</v>
+        <v>4653</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>299.73333333333335</v>
+        <v>290.8125</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1928,11 +1930,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1861</v>
+        <v>2103</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>124.06666666666666</v>
+        <v>131.4375</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,11 +1948,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2015</v>
+        <v>2199</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>134.33333333333334</v>
+        <v>137.4375</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1964,11 +1966,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>11075</v>
+        <v>12158</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>738.33333333333337</v>
+        <v>759.875</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1982,11 +1984,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>8749</v>
+        <v>9573</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>583.26666666666665</v>
+        <v>598.3125</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2000,11 +2002,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>11595</v>
+        <v>12666</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>773</v>
+        <v>791.625</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2018,11 +2020,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>7597</v>
+        <v>8317</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>506.46666666666664</v>
+        <v>519.8125</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2036,11 +2038,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>3.6666666666666665</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2058,7 +2060,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.46666666666666667</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2072,11 +2074,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2131</v>
+        <v>2345</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>142.06666666666666</v>
+        <v>146.5625</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2090,11 +2092,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>8098</v>
+        <v>9088</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>539.86666666666667</v>
+        <v>568</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2108,11 +2110,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>6157</v>
+        <v>6538</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>410.46666666666664</v>
+        <v>408.625</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2126,11 +2128,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>3125</v>
+        <v>3409</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>208.33333333333334</v>
+        <v>213.0625</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2144,11 +2146,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>7083</v>
+        <v>7651</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>472.2</v>
+        <v>478.1875</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2162,11 +2164,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>4214</v>
+        <v>4500</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>280.93333333333334</v>
+        <v>281.25</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2180,11 +2182,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>4258</v>
+        <v>4578</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>283.86666666666667</v>
+        <v>286.125</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2198,11 +2200,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>867</v>
+        <v>944</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>57.8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2216,11 +2218,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1954</v>
+        <v>2062</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>130.26666666666668</v>
+        <v>128.875</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2234,11 +2236,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>658</v>
+        <v>702</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>43.866666666666667</v>
+        <v>43.875</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,11 +2254,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>791</v>
+        <v>884</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>52.733333333333334</v>
+        <v>55.25</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2321,19 +2323,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>417321</v>
+        <v>451601</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>405623</v>
+        <v>439903</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>27821.4</v>
+        <v>28225.0625</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>612070.80000000005</v>
+        <v>620951.375</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2341,11 +2343,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.62000680442911882</v>
+        <v>0.67093602499513438</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-61020.199999999953</v>
+        <v>-52139.625</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2386,7 +2388,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2394,11 +2396,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F9107C-5670-4E70-B4C7-8AA1C6B7D8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37C7FED-4C0E-44F0-9CC5-D846006CD446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -307,6 +307,7 @@
       <sheetName val="INVENTARIO NACIONAL 21-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -332,7 +333,8 @@
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
-      <sheetData sheetId="19">
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -363,25 +365,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>451601</v>
+            <v>486185</v>
           </cell>
           <cell r="H3">
-            <v>439903</v>
+            <v>474487</v>
           </cell>
           <cell r="I3">
-            <v>28225.0625</v>
+            <v>28599.117647058825</v>
           </cell>
           <cell r="J3">
-            <v>620951.375</v>
+            <v>629180.5882352941</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.67093602499513438</v>
+            <v>0.7223168932581181</v>
           </cell>
           <cell r="M3">
-            <v>-52139.625</v>
+            <v>-43910.411764705903</v>
           </cell>
         </row>
         <row r="4">
@@ -392,10 +394,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>19299</v>
+            <v>20490</v>
           </cell>
           <cell r="D4">
-            <v>1206.1875</v>
+            <v>1205.2941176470588</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -424,10 +426,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>886</v>
+            <v>915</v>
           </cell>
           <cell r="D5">
-            <v>55.375</v>
+            <v>53.823529411764703</v>
           </cell>
           <cell r="G5">
             <v>11698</v>
@@ -436,16 +438,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46288</v>
+            <v>46289</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>16</v>
+            <v>17</v>
           </cell>
           <cell r="L5">
-            <v>6</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="6">
@@ -456,10 +458,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>7890</v>
+            <v>8367</v>
           </cell>
           <cell r="D6">
-            <v>493.125</v>
+            <v>492.1764705882353</v>
           </cell>
         </row>
         <row r="7">
@@ -470,10 +472,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1720</v>
+            <v>1848</v>
           </cell>
           <cell r="D7">
-            <v>107.5</v>
+            <v>108.70588235294117</v>
           </cell>
         </row>
         <row r="8">
@@ -484,10 +486,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>211</v>
+            <v>241</v>
           </cell>
           <cell r="D8">
-            <v>13.1875</v>
+            <v>14.176470588235293</v>
           </cell>
         </row>
         <row r="9">
@@ -498,10 +500,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>22733</v>
+            <v>24019</v>
           </cell>
           <cell r="D9">
-            <v>1420.8125</v>
+            <v>1412.8823529411766</v>
           </cell>
         </row>
         <row r="10">
@@ -512,10 +514,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>2360</v>
+            <v>2508</v>
           </cell>
           <cell r="D10">
-            <v>147.5</v>
+            <v>147.52941176470588</v>
           </cell>
         </row>
         <row r="11">
@@ -526,10 +528,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>4908</v>
+            <v>5413</v>
           </cell>
           <cell r="D11">
-            <v>306.75</v>
+            <v>318.41176470588238</v>
           </cell>
         </row>
         <row r="12">
@@ -540,10 +542,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>12273</v>
+            <v>13404</v>
           </cell>
           <cell r="D12">
-            <v>767.0625</v>
+            <v>788.47058823529414</v>
           </cell>
         </row>
         <row r="13">
@@ -554,10 +556,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>5896</v>
+            <v>6525</v>
           </cell>
           <cell r="D13">
-            <v>368.5</v>
+            <v>383.8235294117647</v>
           </cell>
         </row>
         <row r="14">
@@ -568,10 +570,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>53757</v>
+            <v>58132</v>
           </cell>
           <cell r="D14">
-            <v>3359.8125</v>
+            <v>3419.5294117647059</v>
           </cell>
         </row>
         <row r="15">
@@ -582,10 +584,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>33632</v>
+            <v>36031</v>
           </cell>
           <cell r="D15">
-            <v>2102</v>
+            <v>2119.4705882352941</v>
           </cell>
         </row>
         <row r="16">
@@ -596,10 +598,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>34271</v>
+            <v>36501</v>
           </cell>
           <cell r="D16">
-            <v>2141.9375</v>
+            <v>2147.1176470588234</v>
           </cell>
         </row>
         <row r="17">
@@ -610,10 +612,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>41780</v>
+            <v>45155</v>
           </cell>
           <cell r="D17">
-            <v>2611.25</v>
+            <v>2656.1764705882351</v>
           </cell>
         </row>
         <row r="18">
@@ -624,10 +626,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>11351</v>
+            <v>12239</v>
           </cell>
           <cell r="D18">
-            <v>709.4375</v>
+            <v>719.94117647058829</v>
           </cell>
         </row>
         <row r="19">
@@ -638,10 +640,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>13015</v>
+            <v>14322</v>
           </cell>
           <cell r="D19">
-            <v>813.4375</v>
+            <v>842.47058823529414</v>
           </cell>
         </row>
         <row r="20">
@@ -652,10 +654,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>13714</v>
+            <v>14698</v>
           </cell>
           <cell r="D20">
-            <v>857.125</v>
+            <v>864.58823529411768</v>
           </cell>
         </row>
         <row r="21">
@@ -666,10 +668,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>4348</v>
+            <v>4777</v>
           </cell>
           <cell r="D21">
-            <v>271.75</v>
+            <v>281</v>
           </cell>
         </row>
         <row r="22">
@@ -680,10 +682,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>2044</v>
+            <v>2255</v>
           </cell>
           <cell r="D22">
-            <v>127.75</v>
+            <v>132.64705882352942</v>
           </cell>
         </row>
         <row r="23">
@@ -694,10 +696,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>8083</v>
+            <v>8825</v>
           </cell>
           <cell r="D23">
-            <v>505.1875</v>
+            <v>519.11764705882354</v>
           </cell>
         </row>
         <row r="24">
@@ -708,10 +710,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>13592</v>
+            <v>14865</v>
           </cell>
           <cell r="D24">
-            <v>849.5</v>
+            <v>874.41176470588232</v>
           </cell>
         </row>
         <row r="25">
@@ -725,7 +727,7 @@
             <v>1032</v>
           </cell>
           <cell r="D25">
-            <v>64.5</v>
+            <v>60.705882352941174</v>
           </cell>
         </row>
         <row r="26">
@@ -736,10 +738,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>11229</v>
+            <v>11861</v>
           </cell>
           <cell r="D26">
-            <v>701.8125</v>
+            <v>697.70588235294122</v>
           </cell>
         </row>
         <row r="27">
@@ -750,10 +752,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>17504</v>
+            <v>18264</v>
           </cell>
           <cell r="D27">
-            <v>1094</v>
+            <v>1074.3529411764705</v>
           </cell>
         </row>
         <row r="28">
@@ -764,10 +766,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>9032</v>
+            <v>9715</v>
           </cell>
           <cell r="D28">
-            <v>564.5</v>
+            <v>571.47058823529414</v>
           </cell>
         </row>
         <row r="29">
@@ -778,10 +780,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>6754</v>
+            <v>7295</v>
           </cell>
           <cell r="D29">
-            <v>422.125</v>
+            <v>429.11764705882354</v>
           </cell>
         </row>
         <row r="30">
@@ -792,10 +794,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>3852</v>
+            <v>3997</v>
           </cell>
           <cell r="D30">
-            <v>240.75</v>
+            <v>235.11764705882354</v>
           </cell>
         </row>
         <row r="31">
@@ -806,10 +808,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>4653</v>
+            <v>4889</v>
           </cell>
           <cell r="D31">
-            <v>290.8125</v>
+            <v>287.58823529411762</v>
           </cell>
         </row>
         <row r="32">
@@ -820,10 +822,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>2103</v>
+            <v>2252</v>
           </cell>
           <cell r="D32">
-            <v>131.4375</v>
+            <v>132.47058823529412</v>
           </cell>
         </row>
         <row r="33">
@@ -834,10 +836,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>2199</v>
+            <v>2356</v>
           </cell>
           <cell r="D33">
-            <v>137.4375</v>
+            <v>138.58823529411765</v>
           </cell>
         </row>
         <row r="34">
@@ -848,10 +850,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>12158</v>
+            <v>13208</v>
           </cell>
           <cell r="D34">
-            <v>759.875</v>
+            <v>776.94117647058829</v>
           </cell>
         </row>
         <row r="35">
@@ -862,10 +864,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>9573</v>
+            <v>10294</v>
           </cell>
           <cell r="D35">
-            <v>598.3125</v>
+            <v>605.52941176470586</v>
           </cell>
         </row>
         <row r="36">
@@ -876,10 +878,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>12666</v>
+            <v>13598</v>
           </cell>
           <cell r="D36">
-            <v>791.625</v>
+            <v>799.88235294117646</v>
           </cell>
         </row>
         <row r="37">
@@ -890,10 +892,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>8317</v>
+            <v>9026</v>
           </cell>
           <cell r="D37">
-            <v>519.8125</v>
+            <v>530.94117647058829</v>
           </cell>
         </row>
         <row r="38">
@@ -904,10 +906,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>58</v>
+            <v>69</v>
           </cell>
           <cell r="D38">
-            <v>3.625</v>
+            <v>4.0588235294117645</v>
           </cell>
         </row>
         <row r="39">
@@ -918,10 +920,10 @@
             <v>Cremigurt Griego Dulce 4 Kg</v>
           </cell>
           <cell r="C39">
-            <v>7</v>
+            <v>11</v>
           </cell>
           <cell r="D39">
-            <v>0.4375</v>
+            <v>0.6470588235294118</v>
           </cell>
         </row>
         <row r="40">
@@ -932,10 +934,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>2345</v>
+            <v>2537</v>
           </cell>
           <cell r="D40">
-            <v>146.5625</v>
+            <v>149.23529411764707</v>
           </cell>
         </row>
         <row r="41">
@@ -946,10 +948,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>9088</v>
+            <v>9745</v>
           </cell>
           <cell r="D41">
-            <v>568</v>
+            <v>573.23529411764707</v>
           </cell>
         </row>
         <row r="42">
@@ -960,10 +962,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>6538</v>
+            <v>7074</v>
           </cell>
           <cell r="D42">
-            <v>408.625</v>
+            <v>416.11764705882354</v>
           </cell>
         </row>
         <row r="43">
@@ -974,10 +976,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>3409</v>
+            <v>3996</v>
           </cell>
           <cell r="D43">
-            <v>213.0625</v>
+            <v>235.05882352941177</v>
           </cell>
         </row>
         <row r="44">
@@ -988,10 +990,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>7651</v>
+            <v>8487</v>
           </cell>
           <cell r="D44">
-            <v>478.1875</v>
+            <v>499.23529411764707</v>
           </cell>
         </row>
         <row r="45">
@@ -1002,10 +1004,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>4500</v>
+            <v>5079</v>
           </cell>
           <cell r="D45">
-            <v>281.25</v>
+            <v>298.76470588235293</v>
           </cell>
         </row>
         <row r="46">
@@ -1016,10 +1018,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>4578</v>
+            <v>5102</v>
           </cell>
           <cell r="D46">
-            <v>286.125</v>
+            <v>300.11764705882354</v>
           </cell>
         </row>
         <row r="47">
@@ -1030,10 +1032,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>944</v>
+            <v>980</v>
           </cell>
           <cell r="D47">
-            <v>59</v>
+            <v>57.647058823529413</v>
           </cell>
         </row>
         <row r="48">
@@ -1044,10 +1046,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>2062</v>
+            <v>2136</v>
           </cell>
           <cell r="D48">
-            <v>128.875</v>
+            <v>125.64705882352941</v>
           </cell>
         </row>
         <row r="49">
@@ -1058,10 +1060,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>702</v>
+            <v>743</v>
           </cell>
           <cell r="D49">
-            <v>43.875</v>
+            <v>43.705882352941174</v>
           </cell>
         </row>
         <row r="50">
@@ -1072,14 +1074,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>884</v>
+            <v>909</v>
           </cell>
           <cell r="D50">
-            <v>55.25</v>
+            <v>53.470588235294116</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1426,11 +1428,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>19299</v>
+        <v>20490</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1206.1875</v>
+        <v>1205.2941176470588</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1444,11 +1446,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>886</v>
+        <v>915</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>55.375</v>
+        <v>53.823529411764703</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1462,11 +1464,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>7890</v>
+        <v>8367</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>493.125</v>
+        <v>492.1764705882353</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,11 +1482,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1720</v>
+        <v>1848</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>107.5</v>
+        <v>108.70588235294117</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1498,11 +1500,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>13.1875</v>
+        <v>14.176470588235293</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1516,11 +1518,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>22733</v>
+        <v>24019</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1420.8125</v>
+        <v>1412.8823529411766</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1534,11 +1536,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2360</v>
+        <v>2508</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>147.5</v>
+        <v>147.52941176470588</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1552,11 +1554,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>4908</v>
+        <v>5413</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>306.75</v>
+        <v>318.41176470588238</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1570,11 +1572,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>12273</v>
+        <v>13404</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>767.0625</v>
+        <v>788.47058823529414</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1588,11 +1590,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>5896</v>
+        <v>6525</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>368.5</v>
+        <v>383.8235294117647</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1606,11 +1608,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>53757</v>
+        <v>58132</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3359.8125</v>
+        <v>3419.5294117647059</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1624,11 +1626,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>33632</v>
+        <v>36031</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2102</v>
+        <v>2119.4705882352941</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1642,11 +1644,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>34271</v>
+        <v>36501</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2141.9375</v>
+        <v>2147.1176470588234</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,11 +1662,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>41780</v>
+        <v>45155</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2611.25</v>
+        <v>2656.1764705882351</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1678,11 +1680,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>11351</v>
+        <v>12239</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>709.4375</v>
+        <v>719.94117647058829</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1696,11 +1698,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>13015</v>
+        <v>14322</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>813.4375</v>
+        <v>842.47058823529414</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1714,11 +1716,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>13714</v>
+        <v>14698</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>857.125</v>
+        <v>864.58823529411768</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1732,11 +1734,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>4348</v>
+        <v>4777</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>271.75</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1750,11 +1752,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2044</v>
+        <v>2255</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>127.75</v>
+        <v>132.64705882352942</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1768,11 +1770,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>8083</v>
+        <v>8825</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>505.1875</v>
+        <v>519.11764705882354</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1786,11 +1788,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>13592</v>
+        <v>14865</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>849.5</v>
+        <v>874.41176470588232</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1808,7 +1810,7 @@
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>64.5</v>
+        <v>60.705882352941174</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1822,11 +1824,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>11229</v>
+        <v>11861</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>701.8125</v>
+        <v>697.70588235294122</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1840,11 +1842,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>17504</v>
+        <v>18264</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1094</v>
+        <v>1074.3529411764705</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1858,11 +1860,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>9032</v>
+        <v>9715</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>564.5</v>
+        <v>571.47058823529414</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,11 +1878,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>6754</v>
+        <v>7295</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>422.125</v>
+        <v>429.11764705882354</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1894,11 +1896,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>3852</v>
+        <v>3997</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>240.75</v>
+        <v>235.11764705882354</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1912,11 +1914,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>4653</v>
+        <v>4889</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>290.8125</v>
+        <v>287.58823529411762</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1930,11 +1932,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>2103</v>
+        <v>2252</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>131.4375</v>
+        <v>132.47058823529412</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1948,11 +1950,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2199</v>
+        <v>2356</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>137.4375</v>
+        <v>138.58823529411765</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1966,11 +1968,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>12158</v>
+        <v>13208</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>759.875</v>
+        <v>776.94117647058829</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1984,11 +1986,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>9573</v>
+        <v>10294</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>598.3125</v>
+        <v>605.52941176470586</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2002,11 +2004,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>12666</v>
+        <v>13598</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>791.625</v>
+        <v>799.88235294117646</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2020,11 +2022,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>8317</v>
+        <v>9026</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>519.8125</v>
+        <v>530.94117647058829</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2038,11 +2040,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>3.625</v>
+        <v>4.0588235294117645</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2056,11 +2058,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.4375</v>
+        <v>0.6470588235294118</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2074,11 +2076,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2345</v>
+        <v>2537</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>146.5625</v>
+        <v>149.23529411764707</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2092,11 +2094,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>9088</v>
+        <v>9745</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>568</v>
+        <v>573.23529411764707</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2110,11 +2112,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>6538</v>
+        <v>7074</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>408.625</v>
+        <v>416.11764705882354</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2128,11 +2130,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>3409</v>
+        <v>3996</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>213.0625</v>
+        <v>235.05882352941177</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2146,11 +2148,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>7651</v>
+        <v>8487</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>478.1875</v>
+        <v>499.23529411764707</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2164,11 +2166,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>4500</v>
+        <v>5079</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>281.25</v>
+        <v>298.76470588235293</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2182,11 +2184,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>4578</v>
+        <v>5102</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>286.125</v>
+        <v>300.11764705882354</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2200,11 +2202,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>944</v>
+        <v>980</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>59</v>
+        <v>57.647058823529413</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2218,11 +2220,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>2062</v>
+        <v>2136</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>128.875</v>
+        <v>125.64705882352941</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2236,11 +2238,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>702</v>
+        <v>743</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>43.875</v>
+        <v>43.705882352941174</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2254,11 +2256,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>884</v>
+        <v>909</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>55.25</v>
+        <v>53.470588235294116</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2323,19 +2325,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>451601</v>
+        <v>486185</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>439903</v>
+        <v>474487</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>28225.0625</v>
+        <v>28599.117647058825</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>620951.375</v>
+        <v>629180.5882352941</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2343,11 +2345,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.67093602499513438</v>
+        <v>0.7223168932581181</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-52139.625</v>
+        <v>-43910.411764705903</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2388,7 +2390,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2396,11 +2398,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37C7FED-4C0E-44F0-9CC5-D846006CD446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47334304-882E-4EC2-BC35-7E300BE4518E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -308,6 +308,7 @@
       <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -334,7 +335,8 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
-      <sheetData sheetId="20">
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -365,25 +367,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>486185</v>
+            <v>518197</v>
           </cell>
           <cell r="H3">
-            <v>474487</v>
+            <v>506499</v>
           </cell>
           <cell r="I3">
-            <v>28599.117647058825</v>
+            <v>28788.722222222223</v>
           </cell>
           <cell r="J3">
-            <v>629180.5882352941</v>
+            <v>633351.88888888888</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.7223168932581181</v>
+            <v>0.76987658429543704</v>
           </cell>
           <cell r="M3">
-            <v>-43910.411764705903</v>
+            <v>-39739.111111111124</v>
           </cell>
         </row>
         <row r="4">
@@ -394,10 +396,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>20490</v>
+            <v>21607</v>
           </cell>
           <cell r="D4">
-            <v>1205.2941176470588</v>
+            <v>1200.3888888888889</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -426,10 +428,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>915</v>
+            <v>924</v>
           </cell>
           <cell r="D5">
-            <v>53.823529411764703</v>
+            <v>51.333333333333336</v>
           </cell>
           <cell r="G5">
             <v>11698</v>
@@ -438,16 +440,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46289</v>
+            <v>46290</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>17</v>
+            <v>18</v>
           </cell>
           <cell r="L5">
-            <v>5</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="6">
@@ -458,10 +460,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>8367</v>
+            <v>8894</v>
           </cell>
           <cell r="D6">
-            <v>492.1764705882353</v>
+            <v>494.11111111111109</v>
           </cell>
         </row>
         <row r="7">
@@ -472,10 +474,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1848</v>
+            <v>1966</v>
           </cell>
           <cell r="D7">
-            <v>108.70588235294117</v>
+            <v>109.22222222222223</v>
           </cell>
         </row>
         <row r="8">
@@ -486,10 +488,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>241</v>
+            <v>251</v>
           </cell>
           <cell r="D8">
-            <v>14.176470588235293</v>
+            <v>13.944444444444445</v>
           </cell>
         </row>
         <row r="9">
@@ -500,10 +502,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>24019</v>
+            <v>25770</v>
           </cell>
           <cell r="D9">
-            <v>1412.8823529411766</v>
+            <v>1431.6666666666667</v>
           </cell>
         </row>
         <row r="10">
@@ -514,10 +516,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>2508</v>
+            <v>2770</v>
           </cell>
           <cell r="D10">
-            <v>147.52941176470588</v>
+            <v>153.88888888888889</v>
           </cell>
         </row>
         <row r="11">
@@ -528,10 +530,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>5413</v>
+            <v>5811</v>
           </cell>
           <cell r="D11">
-            <v>318.41176470588238</v>
+            <v>322.83333333333331</v>
           </cell>
         </row>
         <row r="12">
@@ -542,10 +544,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>13404</v>
+            <v>14298</v>
           </cell>
           <cell r="D12">
-            <v>788.47058823529414</v>
+            <v>794.33333333333337</v>
           </cell>
         </row>
         <row r="13">
@@ -556,10 +558,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>6525</v>
+            <v>6984</v>
           </cell>
           <cell r="D13">
-            <v>383.8235294117647</v>
+            <v>388</v>
           </cell>
         </row>
         <row r="14">
@@ -570,10 +572,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>58132</v>
+            <v>61667</v>
           </cell>
           <cell r="D14">
-            <v>3419.5294117647059</v>
+            <v>3425.9444444444443</v>
           </cell>
         </row>
         <row r="15">
@@ -584,10 +586,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>36031</v>
+            <v>38596</v>
           </cell>
           <cell r="D15">
-            <v>2119.4705882352941</v>
+            <v>2144.2222222222222</v>
           </cell>
         </row>
         <row r="16">
@@ -598,10 +600,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>36501</v>
+            <v>38910</v>
           </cell>
           <cell r="D16">
-            <v>2147.1176470588234</v>
+            <v>2161.6666666666665</v>
           </cell>
         </row>
         <row r="17">
@@ -612,10 +614,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>45155</v>
+            <v>48079</v>
           </cell>
           <cell r="D17">
-            <v>2656.1764705882351</v>
+            <v>2671.0555555555557</v>
           </cell>
         </row>
         <row r="18">
@@ -626,10 +628,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>12239</v>
+            <v>13117</v>
           </cell>
           <cell r="D18">
-            <v>719.94117647058829</v>
+            <v>728.72222222222217</v>
           </cell>
         </row>
         <row r="19">
@@ -640,10 +642,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>14322</v>
+            <v>15459</v>
           </cell>
           <cell r="D19">
-            <v>842.47058823529414</v>
+            <v>858.83333333333337</v>
           </cell>
         </row>
         <row r="20">
@@ -654,10 +656,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>14698</v>
+            <v>15699</v>
           </cell>
           <cell r="D20">
-            <v>864.58823529411768</v>
+            <v>872.16666666666663</v>
           </cell>
         </row>
         <row r="21">
@@ -668,10 +670,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>4777</v>
+            <v>5001</v>
           </cell>
           <cell r="D21">
-            <v>281</v>
+            <v>277.83333333333331</v>
           </cell>
         </row>
         <row r="22">
@@ -682,10 +684,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>2255</v>
+            <v>2410</v>
           </cell>
           <cell r="D22">
-            <v>132.64705882352942</v>
+            <v>133.88888888888889</v>
           </cell>
         </row>
         <row r="23">
@@ -696,10 +698,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>8825</v>
+            <v>9224</v>
           </cell>
           <cell r="D23">
-            <v>519.11764705882354</v>
+            <v>512.44444444444446</v>
           </cell>
         </row>
         <row r="24">
@@ -710,10 +712,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>14865</v>
+            <v>15801</v>
           </cell>
           <cell r="D24">
-            <v>874.41176470588232</v>
+            <v>877.83333333333337</v>
           </cell>
         </row>
         <row r="25">
@@ -724,10 +726,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>1032</v>
+            <v>1152</v>
           </cell>
           <cell r="D25">
-            <v>60.705882352941174</v>
+            <v>64</v>
           </cell>
         </row>
         <row r="26">
@@ -738,10 +740,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>11861</v>
+            <v>12694</v>
           </cell>
           <cell r="D26">
-            <v>697.70588235294122</v>
+            <v>705.22222222222217</v>
           </cell>
         </row>
         <row r="27">
@@ -752,10 +754,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>18264</v>
+            <v>19520</v>
           </cell>
           <cell r="D27">
-            <v>1074.3529411764705</v>
+            <v>1084.4444444444443</v>
           </cell>
         </row>
         <row r="28">
@@ -766,10 +768,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>9715</v>
+            <v>10201</v>
           </cell>
           <cell r="D28">
-            <v>571.47058823529414</v>
+            <v>566.72222222222217</v>
           </cell>
         </row>
         <row r="29">
@@ -780,10 +782,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>7295</v>
+            <v>7886</v>
           </cell>
           <cell r="D29">
-            <v>429.11764705882354</v>
+            <v>438.11111111111109</v>
           </cell>
         </row>
         <row r="30">
@@ -794,10 +796,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>3997</v>
+            <v>4372</v>
           </cell>
           <cell r="D30">
-            <v>235.11764705882354</v>
+            <v>242.88888888888889</v>
           </cell>
         </row>
         <row r="31">
@@ -808,10 +810,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>4889</v>
+            <v>5317</v>
           </cell>
           <cell r="D31">
-            <v>287.58823529411762</v>
+            <v>295.38888888888891</v>
           </cell>
         </row>
         <row r="32">
@@ -822,10 +824,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>2252</v>
+            <v>2376</v>
           </cell>
           <cell r="D32">
-            <v>132.47058823529412</v>
+            <v>132</v>
           </cell>
         </row>
         <row r="33">
@@ -836,10 +838,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>2356</v>
+            <v>2517</v>
           </cell>
           <cell r="D33">
-            <v>138.58823529411765</v>
+            <v>139.83333333333334</v>
           </cell>
         </row>
         <row r="34">
@@ -850,10 +852,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>13208</v>
+            <v>14151</v>
           </cell>
           <cell r="D34">
-            <v>776.94117647058829</v>
+            <v>786.16666666666663</v>
           </cell>
         </row>
         <row r="35">
@@ -864,10 +866,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>10294</v>
+            <v>11067</v>
           </cell>
           <cell r="D35">
-            <v>605.52941176470586</v>
+            <v>614.83333333333337</v>
           </cell>
         </row>
         <row r="36">
@@ -878,10 +880,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>13598</v>
+            <v>14485</v>
           </cell>
           <cell r="D36">
-            <v>799.88235294117646</v>
+            <v>804.72222222222217</v>
           </cell>
         </row>
         <row r="37">
@@ -892,10 +894,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>9026</v>
+            <v>9640</v>
           </cell>
           <cell r="D37">
-            <v>530.94117647058829</v>
+            <v>535.55555555555554</v>
           </cell>
         </row>
         <row r="38">
@@ -906,10 +908,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>69</v>
+            <v>77</v>
           </cell>
           <cell r="D38">
-            <v>4.0588235294117645</v>
+            <v>4.2777777777777777</v>
           </cell>
         </row>
         <row r="39">
@@ -923,7 +925,7 @@
             <v>11</v>
           </cell>
           <cell r="D39">
-            <v>0.6470588235294118</v>
+            <v>0.61111111111111116</v>
           </cell>
         </row>
         <row r="40">
@@ -934,10 +936,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>2537</v>
+            <v>2613</v>
           </cell>
           <cell r="D40">
-            <v>149.23529411764707</v>
+            <v>145.16666666666666</v>
           </cell>
         </row>
         <row r="41">
@@ -948,10 +950,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>9745</v>
+            <v>10273</v>
           </cell>
           <cell r="D41">
-            <v>573.23529411764707</v>
+            <v>570.72222222222217</v>
           </cell>
         </row>
         <row r="42">
@@ -962,10 +964,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>7074</v>
+            <v>7576</v>
           </cell>
           <cell r="D42">
-            <v>416.11764705882354</v>
+            <v>420.88888888888891</v>
           </cell>
         </row>
         <row r="43">
@@ -976,10 +978,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>3996</v>
+            <v>4279</v>
           </cell>
           <cell r="D43">
-            <v>235.05882352941177</v>
+            <v>237.72222222222223</v>
           </cell>
         </row>
         <row r="44">
@@ -990,10 +992,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>8487</v>
+            <v>8920</v>
           </cell>
           <cell r="D44">
-            <v>499.23529411764707</v>
+            <v>495.55555555555554</v>
           </cell>
         </row>
         <row r="45">
@@ -1004,10 +1006,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>5079</v>
+            <v>5405</v>
           </cell>
           <cell r="D45">
-            <v>298.76470588235293</v>
+            <v>300.27777777777777</v>
           </cell>
         </row>
         <row r="46">
@@ -1018,10 +1020,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>5102</v>
+            <v>5388</v>
           </cell>
           <cell r="D46">
-            <v>300.11764705882354</v>
+            <v>299.33333333333331</v>
           </cell>
         </row>
         <row r="47">
@@ -1032,10 +1034,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>980</v>
+            <v>992</v>
           </cell>
           <cell r="D47">
-            <v>57.647058823529413</v>
+            <v>55.111111111111114</v>
           </cell>
         </row>
         <row r="48">
@@ -1046,10 +1048,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>2136</v>
+            <v>2283</v>
           </cell>
           <cell r="D48">
-            <v>125.64705882352941</v>
+            <v>126.83333333333333</v>
           </cell>
         </row>
         <row r="49">
@@ -1060,10 +1062,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>743</v>
+            <v>784</v>
           </cell>
           <cell r="D49">
-            <v>43.705882352941174</v>
+            <v>43.555555555555557</v>
           </cell>
         </row>
         <row r="50">
@@ -1074,14 +1076,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>909</v>
+            <v>980</v>
           </cell>
           <cell r="D50">
-            <v>53.470588235294116</v>
+            <v>54.444444444444443</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1428,11 +1430,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>20490</v>
+        <v>21607</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1205.2941176470588</v>
+        <v>1200.3888888888889</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1446,11 +1448,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>53.823529411764703</v>
+        <v>51.333333333333336</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,11 +1466,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>8367</v>
+        <v>8894</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>492.1764705882353</v>
+        <v>494.11111111111109</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1482,11 +1484,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1848</v>
+        <v>1966</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>108.70588235294117</v>
+        <v>109.22222222222223</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1500,11 +1502,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>14.176470588235293</v>
+        <v>13.944444444444445</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,11 +1520,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>24019</v>
+        <v>25770</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1412.8823529411766</v>
+        <v>1431.6666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,11 +1538,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2508</v>
+        <v>2770</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>147.52941176470588</v>
+        <v>153.88888888888889</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1554,11 +1556,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>5413</v>
+        <v>5811</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>318.41176470588238</v>
+        <v>322.83333333333331</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1572,11 +1574,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>13404</v>
+        <v>14298</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>788.47058823529414</v>
+        <v>794.33333333333337</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,11 +1592,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>6525</v>
+        <v>6984</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>383.8235294117647</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1608,11 +1610,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>58132</v>
+        <v>61667</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3419.5294117647059</v>
+        <v>3425.9444444444443</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1626,11 +1628,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>36031</v>
+        <v>38596</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2119.4705882352941</v>
+        <v>2144.2222222222222</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1644,11 +1646,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>36501</v>
+        <v>38910</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2147.1176470588234</v>
+        <v>2161.6666666666665</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,11 +1664,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>45155</v>
+        <v>48079</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2656.1764705882351</v>
+        <v>2671.0555555555557</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1680,11 +1682,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>12239</v>
+        <v>13117</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>719.94117647058829</v>
+        <v>728.72222222222217</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1698,11 +1700,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>14322</v>
+        <v>15459</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>842.47058823529414</v>
+        <v>858.83333333333337</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,11 +1718,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>14698</v>
+        <v>15699</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>864.58823529411768</v>
+        <v>872.16666666666663</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1734,11 +1736,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>4777</v>
+        <v>5001</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>281</v>
+        <v>277.83333333333331</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1752,11 +1754,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2255</v>
+        <v>2410</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>132.64705882352942</v>
+        <v>133.88888888888889</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1770,11 +1772,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>8825</v>
+        <v>9224</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>519.11764705882354</v>
+        <v>512.44444444444446</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1788,11 +1790,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>14865</v>
+        <v>15801</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>874.41176470588232</v>
+        <v>877.83333333333337</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1806,11 +1808,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>1032</v>
+        <v>1152</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>60.705882352941174</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1824,11 +1826,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>11861</v>
+        <v>12694</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>697.70588235294122</v>
+        <v>705.22222222222217</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1842,11 +1844,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>18264</v>
+        <v>19520</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1074.3529411764705</v>
+        <v>1084.4444444444443</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1860,11 +1862,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>9715</v>
+        <v>10201</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>571.47058823529414</v>
+        <v>566.72222222222217</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1878,11 +1880,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>7295</v>
+        <v>7886</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>429.11764705882354</v>
+        <v>438.11111111111109</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1896,11 +1898,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>3997</v>
+        <v>4372</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>235.11764705882354</v>
+        <v>242.88888888888889</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1914,11 +1916,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>4889</v>
+        <v>5317</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>287.58823529411762</v>
+        <v>295.38888888888891</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,11 +1934,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>2252</v>
+        <v>2376</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>132.47058823529412</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1950,11 +1952,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2356</v>
+        <v>2517</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>138.58823529411765</v>
+        <v>139.83333333333334</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1968,11 +1970,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>13208</v>
+        <v>14151</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>776.94117647058829</v>
+        <v>786.16666666666663</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1986,11 +1988,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>10294</v>
+        <v>11067</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>605.52941176470586</v>
+        <v>614.83333333333337</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2004,11 +2006,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>13598</v>
+        <v>14485</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>799.88235294117646</v>
+        <v>804.72222222222217</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2022,11 +2024,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>9026</v>
+        <v>9640</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>530.94117647058829</v>
+        <v>535.55555555555554</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2040,11 +2042,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4.0588235294117645</v>
+        <v>4.2777777777777777</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2062,7 +2064,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.6470588235294118</v>
+        <v>0.61111111111111116</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2076,11 +2078,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2537</v>
+        <v>2613</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>149.23529411764707</v>
+        <v>145.16666666666666</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2094,11 +2096,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>9745</v>
+        <v>10273</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>573.23529411764707</v>
+        <v>570.72222222222217</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2112,11 +2114,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>7074</v>
+        <v>7576</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>416.11764705882354</v>
+        <v>420.88888888888891</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2130,11 +2132,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>3996</v>
+        <v>4279</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>235.05882352941177</v>
+        <v>237.72222222222223</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2148,11 +2150,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>8487</v>
+        <v>8920</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>499.23529411764707</v>
+        <v>495.55555555555554</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2166,11 +2168,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>5079</v>
+        <v>5405</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>298.76470588235293</v>
+        <v>300.27777777777777</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2184,11 +2186,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>5102</v>
+        <v>5388</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>300.11764705882354</v>
+        <v>299.33333333333331</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2202,11 +2204,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>57.647058823529413</v>
+        <v>55.111111111111114</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2220,11 +2222,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>2136</v>
+        <v>2283</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>125.64705882352941</v>
+        <v>126.83333333333333</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2238,11 +2240,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>743</v>
+        <v>784</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>43.705882352941174</v>
+        <v>43.555555555555557</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2256,11 +2258,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>909</v>
+        <v>980</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>53.470588235294116</v>
+        <v>54.444444444444443</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2325,19 +2327,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>486185</v>
+        <v>518197</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>474487</v>
+        <v>506499</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>28599.117647058825</v>
+        <v>28788.722222222223</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>629180.5882352941</v>
+        <v>633351.88888888888</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2345,11 +2347,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.7223168932581181</v>
+        <v>0.76987658429543704</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-43910.411764705903</v>
+        <v>-39739.111111111124</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2390,7 +2392,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2398,11 +2400,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47334304-882E-4EC2-BC35-7E300BE4518E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB3B1FA-1728-445B-9BDF-159782A6E6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -309,6 +309,7 @@
       <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 28-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -336,7 +337,8 @@
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
-      <sheetData sheetId="21">
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -367,25 +369,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>518197</v>
+            <v>538322</v>
           </cell>
           <cell r="H3">
-            <v>506499</v>
+            <v>526624</v>
           </cell>
           <cell r="I3">
-            <v>28788.722222222223</v>
+            <v>28332.736842105263</v>
           </cell>
           <cell r="J3">
-            <v>633351.88888888888</v>
+            <v>623320.21052631573</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.76987658429543704</v>
+            <v>0.79977595897137232</v>
           </cell>
           <cell r="M3">
-            <v>-39739.111111111124</v>
+            <v>-49770.789473684272</v>
           </cell>
         </row>
         <row r="4">
@@ -396,10 +398,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>21607</v>
+            <v>22297</v>
           </cell>
           <cell r="D4">
-            <v>1200.3888888888889</v>
+            <v>1173.5263157894738</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -431,7 +433,7 @@
             <v>924</v>
           </cell>
           <cell r="D5">
-            <v>51.333333333333336</v>
+            <v>48.631578947368418</v>
           </cell>
           <cell r="G5">
             <v>11698</v>
@@ -440,16 +442,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46290</v>
+            <v>46293</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>18</v>
+            <v>19</v>
           </cell>
           <cell r="L5">
-            <v>4</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="6">
@@ -460,10 +462,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>8894</v>
+            <v>9343</v>
           </cell>
           <cell r="D6">
-            <v>494.11111111111109</v>
+            <v>491.73684210526318</v>
           </cell>
         </row>
         <row r="7">
@@ -474,10 +476,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1966</v>
+            <v>1987</v>
           </cell>
           <cell r="D7">
-            <v>109.22222222222223</v>
+            <v>104.57894736842105</v>
           </cell>
         </row>
         <row r="8">
@@ -488,10 +490,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>251</v>
+            <v>252</v>
           </cell>
           <cell r="D8">
-            <v>13.944444444444445</v>
+            <v>13.263157894736842</v>
           </cell>
         </row>
         <row r="9">
@@ -502,10 +504,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>25770</v>
+            <v>26631</v>
           </cell>
           <cell r="D9">
-            <v>1431.6666666666667</v>
+            <v>1401.6315789473683</v>
           </cell>
         </row>
         <row r="10">
@@ -516,10 +518,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>2770</v>
+            <v>2804</v>
           </cell>
           <cell r="D10">
-            <v>153.88888888888889</v>
+            <v>147.57894736842104</v>
           </cell>
         </row>
         <row r="11">
@@ -530,10 +532,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>5811</v>
+            <v>5905</v>
           </cell>
           <cell r="D11">
-            <v>322.83333333333331</v>
+            <v>310.78947368421052</v>
           </cell>
         </row>
         <row r="12">
@@ -544,10 +546,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>14298</v>
+            <v>14758</v>
           </cell>
           <cell r="D12">
-            <v>794.33333333333337</v>
+            <v>776.73684210526312</v>
           </cell>
         </row>
         <row r="13">
@@ -558,10 +560,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>6984</v>
+            <v>7170</v>
           </cell>
           <cell r="D13">
-            <v>388</v>
+            <v>377.36842105263156</v>
           </cell>
         </row>
         <row r="14">
@@ -572,10 +574,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>61667</v>
+            <v>63741</v>
           </cell>
           <cell r="D14">
-            <v>3425.9444444444443</v>
+            <v>3354.7894736842104</v>
           </cell>
         </row>
         <row r="15">
@@ -586,10 +588,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>38596</v>
+            <v>40339</v>
           </cell>
           <cell r="D15">
-            <v>2144.2222222222222</v>
+            <v>2123.1052631578946</v>
           </cell>
         </row>
         <row r="16">
@@ -600,10 +602,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>38910</v>
+            <v>40312</v>
           </cell>
           <cell r="D16">
-            <v>2161.6666666666665</v>
+            <v>2121.6842105263158</v>
           </cell>
         </row>
         <row r="17">
@@ -614,10 +616,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>48079</v>
+            <v>49802</v>
           </cell>
           <cell r="D17">
-            <v>2671.0555555555557</v>
+            <v>2621.1578947368421</v>
           </cell>
         </row>
         <row r="18">
@@ -628,10 +630,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>13117</v>
+            <v>13445</v>
           </cell>
           <cell r="D18">
-            <v>728.72222222222217</v>
+            <v>707.63157894736844</v>
           </cell>
         </row>
         <row r="19">
@@ -642,10 +644,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>15459</v>
+            <v>15895</v>
           </cell>
           <cell r="D19">
-            <v>858.83333333333337</v>
+            <v>836.57894736842104</v>
           </cell>
         </row>
         <row r="20">
@@ -656,10 +658,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>15699</v>
+            <v>16083</v>
           </cell>
           <cell r="D20">
-            <v>872.16666666666663</v>
+            <v>846.47368421052636</v>
           </cell>
         </row>
         <row r="21">
@@ -670,10 +672,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>5001</v>
+            <v>5164</v>
           </cell>
           <cell r="D21">
-            <v>277.83333333333331</v>
+            <v>271.78947368421052</v>
           </cell>
         </row>
         <row r="22">
@@ -684,10 +686,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>2410</v>
+            <v>2516</v>
           </cell>
           <cell r="D22">
-            <v>133.88888888888889</v>
+            <v>132.42105263157896</v>
           </cell>
         </row>
         <row r="23">
@@ -698,10 +700,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>9224</v>
+            <v>9586</v>
           </cell>
           <cell r="D23">
-            <v>512.44444444444446</v>
+            <v>504.5263157894737</v>
           </cell>
         </row>
         <row r="24">
@@ -712,10 +714,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>15801</v>
+            <v>16378</v>
           </cell>
           <cell r="D24">
-            <v>877.83333333333337</v>
+            <v>862</v>
           </cell>
         </row>
         <row r="25">
@@ -729,7 +731,7 @@
             <v>1152</v>
           </cell>
           <cell r="D25">
-            <v>64</v>
+            <v>60.631578947368418</v>
           </cell>
         </row>
         <row r="26">
@@ -740,10 +742,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>12694</v>
+            <v>13311</v>
           </cell>
           <cell r="D26">
-            <v>705.22222222222217</v>
+            <v>700.57894736842104</v>
           </cell>
         </row>
         <row r="27">
@@ -754,10 +756,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>19520</v>
+            <v>20615</v>
           </cell>
           <cell r="D27">
-            <v>1084.4444444444443</v>
+            <v>1085</v>
           </cell>
         </row>
         <row r="28">
@@ -768,10 +770,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>10201</v>
+            <v>10664</v>
           </cell>
           <cell r="D28">
-            <v>566.72222222222217</v>
+            <v>561.26315789473688</v>
           </cell>
         </row>
         <row r="29">
@@ -782,10 +784,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>7886</v>
+            <v>8140</v>
           </cell>
           <cell r="D29">
-            <v>438.11111111111109</v>
+            <v>428.42105263157896</v>
           </cell>
         </row>
         <row r="30">
@@ -796,10 +798,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>4372</v>
+            <v>4746</v>
           </cell>
           <cell r="D30">
-            <v>242.88888888888889</v>
+            <v>249.78947368421052</v>
           </cell>
         </row>
         <row r="31">
@@ -810,10 +812,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>5317</v>
+            <v>5736</v>
           </cell>
           <cell r="D31">
-            <v>295.38888888888891</v>
+            <v>301.89473684210526</v>
           </cell>
         </row>
         <row r="32">
@@ -824,10 +826,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>2376</v>
+            <v>2457</v>
           </cell>
           <cell r="D32">
-            <v>132</v>
+            <v>129.31578947368422</v>
           </cell>
         </row>
         <row r="33">
@@ -838,10 +840,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>2517</v>
+            <v>2694</v>
           </cell>
           <cell r="D33">
-            <v>139.83333333333334</v>
+            <v>141.78947368421052</v>
           </cell>
         </row>
         <row r="34">
@@ -852,10 +854,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>14151</v>
+            <v>14915</v>
           </cell>
           <cell r="D34">
-            <v>786.16666666666663</v>
+            <v>785</v>
           </cell>
         </row>
         <row r="35">
@@ -866,10 +868,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>11067</v>
+            <v>11547</v>
           </cell>
           <cell r="D35">
-            <v>614.83333333333337</v>
+            <v>607.73684210526312</v>
           </cell>
         </row>
         <row r="36">
@@ -880,10 +882,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>14485</v>
+            <v>15283</v>
           </cell>
           <cell r="D36">
-            <v>804.72222222222217</v>
+            <v>804.36842105263156</v>
           </cell>
         </row>
         <row r="37">
@@ -894,10 +896,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>9640</v>
+            <v>10118</v>
           </cell>
           <cell r="D37">
-            <v>535.55555555555554</v>
+            <v>532.52631578947364</v>
           </cell>
         </row>
         <row r="38">
@@ -908,10 +910,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>77</v>
+            <v>78</v>
           </cell>
           <cell r="D38">
-            <v>4.2777777777777777</v>
+            <v>4.1052631578947372</v>
           </cell>
         </row>
         <row r="39">
@@ -925,7 +927,7 @@
             <v>11</v>
           </cell>
           <cell r="D39">
-            <v>0.61111111111111116</v>
+            <v>0.57894736842105265</v>
           </cell>
         </row>
         <row r="40">
@@ -936,10 +938,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>2613</v>
+            <v>2642</v>
           </cell>
           <cell r="D40">
-            <v>145.16666666666666</v>
+            <v>139.05263157894737</v>
           </cell>
         </row>
         <row r="41">
@@ -950,10 +952,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>10273</v>
+            <v>10708</v>
           </cell>
           <cell r="D41">
-            <v>570.72222222222217</v>
+            <v>563.57894736842104</v>
           </cell>
         </row>
         <row r="42">
@@ -964,10 +966,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>7576</v>
+            <v>7709</v>
           </cell>
           <cell r="D42">
-            <v>420.88888888888891</v>
+            <v>405.73684210526318</v>
           </cell>
         </row>
         <row r="43">
@@ -978,10 +980,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>4279</v>
+            <v>4527</v>
           </cell>
           <cell r="D43">
-            <v>237.72222222222223</v>
+            <v>238.26315789473685</v>
           </cell>
         </row>
         <row r="44">
@@ -992,10 +994,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>8920</v>
+            <v>9415</v>
           </cell>
           <cell r="D44">
-            <v>495.55555555555554</v>
+            <v>495.5263157894737</v>
           </cell>
         </row>
         <row r="45">
@@ -1006,10 +1008,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>5405</v>
+            <v>5766</v>
           </cell>
           <cell r="D45">
-            <v>300.27777777777777</v>
+            <v>303.4736842105263</v>
           </cell>
         </row>
         <row r="46">
@@ -1020,10 +1022,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>5388</v>
+            <v>5661</v>
           </cell>
           <cell r="D46">
-            <v>299.33333333333331</v>
+            <v>297.94736842105266</v>
           </cell>
         </row>
         <row r="47">
@@ -1034,10 +1036,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>992</v>
+            <v>1021</v>
           </cell>
           <cell r="D47">
-            <v>55.111111111111114</v>
+            <v>53.736842105263158</v>
           </cell>
         </row>
         <row r="48">
@@ -1048,10 +1050,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>2283</v>
+            <v>2288</v>
           </cell>
           <cell r="D48">
-            <v>126.83333333333333</v>
+            <v>120.42105263157895</v>
           </cell>
         </row>
         <row r="49">
@@ -1062,10 +1064,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>784</v>
+            <v>790</v>
           </cell>
           <cell r="D49">
-            <v>43.555555555555557</v>
+            <v>41.578947368421055</v>
           </cell>
         </row>
         <row r="50">
@@ -1076,14 +1078,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>980</v>
+            <v>996</v>
           </cell>
           <cell r="D50">
-            <v>54.444444444444443</v>
+            <v>52.421052631578945</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1430,11 +1432,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>21607</v>
+        <v>22297</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1200.3888888888889</v>
+        <v>1173.5263157894738</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,7 +1454,7 @@
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>51.333333333333336</v>
+        <v>48.631578947368418</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1466,11 +1468,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>8894</v>
+        <v>9343</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>494.11111111111109</v>
+        <v>491.73684210526318</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1484,11 +1486,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1966</v>
+        <v>1987</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>109.22222222222223</v>
+        <v>104.57894736842105</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1502,11 +1504,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>13.944444444444445</v>
+        <v>13.263157894736842</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,11 +1522,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>25770</v>
+        <v>26631</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1431.6666666666667</v>
+        <v>1401.6315789473683</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,11 +1540,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2770</v>
+        <v>2804</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>153.88888888888889</v>
+        <v>147.57894736842104</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1556,11 +1558,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>5811</v>
+        <v>5905</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>322.83333333333331</v>
+        <v>310.78947368421052</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1574,11 +1576,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>14298</v>
+        <v>14758</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>794.33333333333337</v>
+        <v>776.73684210526312</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1592,11 +1594,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>6984</v>
+        <v>7170</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>388</v>
+        <v>377.36842105263156</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1610,11 +1612,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>61667</v>
+        <v>63741</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3425.9444444444443</v>
+        <v>3354.7894736842104</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1628,11 +1630,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>38596</v>
+        <v>40339</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2144.2222222222222</v>
+        <v>2123.1052631578946</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1646,11 +1648,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>38910</v>
+        <v>40312</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2161.6666666666665</v>
+        <v>2121.6842105263158</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1664,11 +1666,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>48079</v>
+        <v>49802</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2671.0555555555557</v>
+        <v>2621.1578947368421</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1682,11 +1684,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>13117</v>
+        <v>13445</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>728.72222222222217</v>
+        <v>707.63157894736844</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1700,11 +1702,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>15459</v>
+        <v>15895</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>858.83333333333337</v>
+        <v>836.57894736842104</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1718,11 +1720,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>15699</v>
+        <v>16083</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>872.16666666666663</v>
+        <v>846.47368421052636</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1736,11 +1738,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>5001</v>
+        <v>5164</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>277.83333333333331</v>
+        <v>271.78947368421052</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1754,11 +1756,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2410</v>
+        <v>2516</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>133.88888888888889</v>
+        <v>132.42105263157896</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1772,11 +1774,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>9224</v>
+        <v>9586</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>512.44444444444446</v>
+        <v>504.5263157894737</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1790,11 +1792,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>15801</v>
+        <v>16378</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>877.83333333333337</v>
+        <v>862</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,7 +1814,7 @@
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>64</v>
+        <v>60.631578947368418</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1826,11 +1828,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>12694</v>
+        <v>13311</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>705.22222222222217</v>
+        <v>700.57894736842104</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1844,11 +1846,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>19520</v>
+        <v>20615</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1084.4444444444443</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1862,11 +1864,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>10201</v>
+        <v>10664</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>566.72222222222217</v>
+        <v>561.26315789473688</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1880,11 +1882,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>7886</v>
+        <v>8140</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>438.11111111111109</v>
+        <v>428.42105263157896</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1898,11 +1900,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>4372</v>
+        <v>4746</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>242.88888888888889</v>
+        <v>249.78947368421052</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1916,11 +1918,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>5317</v>
+        <v>5736</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>295.38888888888891</v>
+        <v>301.89473684210526</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1934,11 +1936,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>2376</v>
+        <v>2457</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>132</v>
+        <v>129.31578947368422</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1952,11 +1954,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2517</v>
+        <v>2694</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>139.83333333333334</v>
+        <v>141.78947368421052</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1970,11 +1972,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>14151</v>
+        <v>14915</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>786.16666666666663</v>
+        <v>785</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1988,11 +1990,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>11067</v>
+        <v>11547</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>614.83333333333337</v>
+        <v>607.73684210526312</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2006,11 +2008,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>14485</v>
+        <v>15283</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>804.72222222222217</v>
+        <v>804.36842105263156</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2024,11 +2026,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>9640</v>
+        <v>10118</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>535.55555555555554</v>
+        <v>532.52631578947364</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2042,11 +2044,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4.2777777777777777</v>
+        <v>4.1052631578947372</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2064,7 +2066,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.61111111111111116</v>
+        <v>0.57894736842105265</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2078,11 +2080,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2613</v>
+        <v>2642</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>145.16666666666666</v>
+        <v>139.05263157894737</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2096,11 +2098,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>10273</v>
+        <v>10708</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>570.72222222222217</v>
+        <v>563.57894736842104</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2114,11 +2116,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>7576</v>
+        <v>7709</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>420.88888888888891</v>
+        <v>405.73684210526318</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2132,11 +2134,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>4279</v>
+        <v>4527</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>237.72222222222223</v>
+        <v>238.26315789473685</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2150,11 +2152,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>8920</v>
+        <v>9415</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>495.55555555555554</v>
+        <v>495.5263157894737</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2168,11 +2170,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>5405</v>
+        <v>5766</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>300.27777777777777</v>
+        <v>303.4736842105263</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2186,11 +2188,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>5388</v>
+        <v>5661</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>299.33333333333331</v>
+        <v>297.94736842105266</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2204,11 +2206,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>992</v>
+        <v>1021</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>55.111111111111114</v>
+        <v>53.736842105263158</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2222,11 +2224,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>2283</v>
+        <v>2288</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>126.83333333333333</v>
+        <v>120.42105263157895</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2240,11 +2242,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>43.555555555555557</v>
+        <v>41.578947368421055</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2258,11 +2260,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>54.444444444444443</v>
+        <v>52.421052631578945</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2327,19 +2329,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>518197</v>
+        <v>538322</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>506499</v>
+        <v>526624</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>28788.722222222223</v>
+        <v>28332.736842105263</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>633351.88888888888</v>
+        <v>623320.21052631573</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2347,11 +2349,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.76987658429543704</v>
+        <v>0.79977595897137232</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-39739.111111111124</v>
+        <v>-49770.789473684272</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2392,7 +2394,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2400,11 +2402,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB3B1FA-1728-445B-9BDF-159782A6E6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD37BC39-2DA6-4B27-A5E5-CBDDAC6444B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -310,6 +310,7 @@
       <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 29-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -338,7 +339,8 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
-      <sheetData sheetId="22">
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -369,25 +371,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>538322</v>
+            <v>565256</v>
           </cell>
           <cell r="H3">
-            <v>526624</v>
+            <v>553558</v>
           </cell>
           <cell r="I3">
-            <v>28332.736842105263</v>
+            <v>28262.799999999999</v>
           </cell>
           <cell r="J3">
-            <v>623320.21052631573</v>
+            <v>621781.6</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.79977595897137232</v>
+            <v>0.83979135064946642</v>
           </cell>
           <cell r="M3">
-            <v>-49770.789473684272</v>
+            <v>-51309.400000000023</v>
           </cell>
         </row>
         <row r="4">
@@ -398,10 +400,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>22297</v>
+            <v>23358</v>
           </cell>
           <cell r="D4">
-            <v>1173.5263157894738</v>
+            <v>1167.9000000000001</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -430,10 +432,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>924</v>
+            <v>929</v>
           </cell>
           <cell r="D5">
-            <v>48.631578947368418</v>
+            <v>46.45</v>
           </cell>
           <cell r="G5">
             <v>11698</v>
@@ -442,16 +444,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46293</v>
+            <v>46294</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>19</v>
+            <v>20</v>
           </cell>
           <cell r="L5">
-            <v>3</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="6">
@@ -462,10 +464,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>9343</v>
+            <v>9821</v>
           </cell>
           <cell r="D6">
-            <v>491.73684210526318</v>
+            <v>491.05</v>
           </cell>
         </row>
         <row r="7">
@@ -476,10 +478,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>1987</v>
+            <v>2089</v>
           </cell>
           <cell r="D7">
-            <v>104.57894736842105</v>
+            <v>104.45</v>
           </cell>
         </row>
         <row r="8">
@@ -490,10 +492,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>252</v>
+            <v>280</v>
           </cell>
           <cell r="D8">
-            <v>13.263157894736842</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="9">
@@ -504,10 +506,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>26631</v>
+            <v>28107</v>
           </cell>
           <cell r="D9">
-            <v>1401.6315789473683</v>
+            <v>1405.35</v>
           </cell>
         </row>
         <row r="10">
@@ -518,10 +520,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>2804</v>
+            <v>2941</v>
           </cell>
           <cell r="D10">
-            <v>147.57894736842104</v>
+            <v>147.05000000000001</v>
           </cell>
         </row>
         <row r="11">
@@ -532,10 +534,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>5905</v>
+            <v>6284</v>
           </cell>
           <cell r="D11">
-            <v>310.78947368421052</v>
+            <v>314.2</v>
           </cell>
         </row>
         <row r="12">
@@ -546,10 +548,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>14758</v>
+            <v>15352</v>
           </cell>
           <cell r="D12">
-            <v>776.73684210526312</v>
+            <v>767.6</v>
           </cell>
         </row>
         <row r="13">
@@ -560,10 +562,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>7170</v>
+            <v>7499</v>
           </cell>
           <cell r="D13">
-            <v>377.36842105263156</v>
+            <v>374.95</v>
           </cell>
         </row>
         <row r="14">
@@ -574,10 +576,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>63741</v>
+            <v>66947</v>
           </cell>
           <cell r="D14">
-            <v>3354.7894736842104</v>
+            <v>3347.35</v>
           </cell>
         </row>
         <row r="15">
@@ -588,10 +590,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>40339</v>
+            <v>42252</v>
           </cell>
           <cell r="D15">
-            <v>2123.1052631578946</v>
+            <v>2112.6</v>
           </cell>
         </row>
         <row r="16">
@@ -602,10 +604,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>40312</v>
+            <v>42433</v>
           </cell>
           <cell r="D16">
-            <v>2121.6842105263158</v>
+            <v>2121.65</v>
           </cell>
         </row>
         <row r="17">
@@ -616,10 +618,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>49802</v>
+            <v>52159</v>
           </cell>
           <cell r="D17">
-            <v>2621.1578947368421</v>
+            <v>2607.9499999999998</v>
           </cell>
         </row>
         <row r="18">
@@ -630,10 +632,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>13445</v>
+            <v>14058</v>
           </cell>
           <cell r="D18">
-            <v>707.63157894736844</v>
+            <v>702.9</v>
           </cell>
         </row>
         <row r="19">
@@ -644,10 +646,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>15895</v>
+            <v>16722</v>
           </cell>
           <cell r="D19">
-            <v>836.57894736842104</v>
+            <v>836.1</v>
           </cell>
         </row>
         <row r="20">
@@ -658,10 +660,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>16083</v>
+            <v>16864</v>
           </cell>
           <cell r="D20">
-            <v>846.47368421052636</v>
+            <v>843.2</v>
           </cell>
         </row>
         <row r="21">
@@ -672,10 +674,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>5164</v>
+            <v>5377</v>
           </cell>
           <cell r="D21">
-            <v>271.78947368421052</v>
+            <v>268.85000000000002</v>
           </cell>
         </row>
         <row r="22">
@@ -686,10 +688,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>2516</v>
+            <v>2630</v>
           </cell>
           <cell r="D22">
-            <v>132.42105263157896</v>
+            <v>131.5</v>
           </cell>
         </row>
         <row r="23">
@@ -700,10 +702,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>9586</v>
+            <v>10072</v>
           </cell>
           <cell r="D23">
-            <v>504.5263157894737</v>
+            <v>503.6</v>
           </cell>
         </row>
         <row r="24">
@@ -714,10 +716,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>16378</v>
+            <v>17012</v>
           </cell>
           <cell r="D24">
-            <v>862</v>
+            <v>850.6</v>
           </cell>
         </row>
         <row r="25">
@@ -728,10 +730,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>1152</v>
+            <v>1200</v>
           </cell>
           <cell r="D25">
-            <v>60.631578947368418</v>
+            <v>60</v>
           </cell>
         </row>
         <row r="26">
@@ -742,10 +744,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>13311</v>
+            <v>14069</v>
           </cell>
           <cell r="D26">
-            <v>700.57894736842104</v>
+            <v>703.45</v>
           </cell>
         </row>
         <row r="27">
@@ -756,10 +758,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>20615</v>
+            <v>21797</v>
           </cell>
           <cell r="D27">
-            <v>1085</v>
+            <v>1089.8499999999999</v>
           </cell>
         </row>
         <row r="28">
@@ -770,10 +772,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>10664</v>
+            <v>11056</v>
           </cell>
           <cell r="D28">
-            <v>561.26315789473688</v>
+            <v>552.79999999999995</v>
           </cell>
         </row>
         <row r="29">
@@ -784,10 +786,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>8140</v>
+            <v>8750</v>
           </cell>
           <cell r="D29">
-            <v>428.42105263157896</v>
+            <v>437.5</v>
           </cell>
         </row>
         <row r="30">
@@ -798,10 +800,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>4746</v>
+            <v>5084</v>
           </cell>
           <cell r="D30">
-            <v>249.78947368421052</v>
+            <v>254.2</v>
           </cell>
         </row>
         <row r="31">
@@ -812,10 +814,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>5736</v>
+            <v>6256</v>
           </cell>
           <cell r="D31">
-            <v>301.89473684210526</v>
+            <v>312.8</v>
           </cell>
         </row>
         <row r="32">
@@ -826,10 +828,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>2457</v>
+            <v>2559</v>
           </cell>
           <cell r="D32">
-            <v>129.31578947368422</v>
+            <v>127.95</v>
           </cell>
         </row>
         <row r="33">
@@ -840,10 +842,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>2694</v>
+            <v>2894</v>
           </cell>
           <cell r="D33">
-            <v>141.78947368421052</v>
+            <v>144.69999999999999</v>
           </cell>
         </row>
         <row r="34">
@@ -854,10 +856,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>14915</v>
+            <v>15687</v>
           </cell>
           <cell r="D34">
-            <v>785</v>
+            <v>784.35</v>
           </cell>
         </row>
         <row r="35">
@@ -868,10 +870,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>11547</v>
+            <v>12011</v>
           </cell>
           <cell r="D35">
-            <v>607.73684210526312</v>
+            <v>600.54999999999995</v>
           </cell>
         </row>
         <row r="36">
@@ -882,10 +884,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>15283</v>
+            <v>16019</v>
           </cell>
           <cell r="D36">
-            <v>804.36842105263156</v>
+            <v>800.95</v>
           </cell>
         </row>
         <row r="37">
@@ -896,10 +898,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>10118</v>
+            <v>10529</v>
           </cell>
           <cell r="D37">
-            <v>532.52631578947364</v>
+            <v>526.45000000000005</v>
           </cell>
         </row>
         <row r="38">
@@ -910,10 +912,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>78</v>
+            <v>80</v>
           </cell>
           <cell r="D38">
-            <v>4.1052631578947372</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="39">
@@ -927,7 +929,7 @@
             <v>11</v>
           </cell>
           <cell r="D39">
-            <v>0.57894736842105265</v>
+            <v>0.55000000000000004</v>
           </cell>
         </row>
         <row r="40">
@@ -938,10 +940,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>2642</v>
+            <v>2684</v>
           </cell>
           <cell r="D40">
-            <v>139.05263157894737</v>
+            <v>134.19999999999999</v>
           </cell>
         </row>
         <row r="41">
@@ -952,10 +954,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>10708</v>
+            <v>11345</v>
           </cell>
           <cell r="D41">
-            <v>563.57894736842104</v>
+            <v>567.25</v>
           </cell>
         </row>
         <row r="42">
@@ -966,10 +968,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>7709</v>
+            <v>8105</v>
           </cell>
           <cell r="D42">
-            <v>405.73684210526318</v>
+            <v>405.25</v>
           </cell>
         </row>
         <row r="43">
@@ -980,10 +982,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>4527</v>
+            <v>4933</v>
           </cell>
           <cell r="D43">
-            <v>238.26315789473685</v>
+            <v>246.65</v>
           </cell>
         </row>
         <row r="44">
@@ -994,10 +996,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>9415</v>
+            <v>9829</v>
           </cell>
           <cell r="D44">
-            <v>495.5263157894737</v>
+            <v>491.45</v>
           </cell>
         </row>
         <row r="45">
@@ -1008,10 +1010,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>5766</v>
+            <v>5971</v>
           </cell>
           <cell r="D45">
-            <v>303.4736842105263</v>
+            <v>298.55</v>
           </cell>
         </row>
         <row r="46">
@@ -1022,10 +1024,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>5661</v>
+            <v>5867</v>
           </cell>
           <cell r="D46">
-            <v>297.94736842105266</v>
+            <v>293.35000000000002</v>
           </cell>
         </row>
         <row r="47">
@@ -1036,10 +1038,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>1021</v>
+            <v>1060</v>
           </cell>
           <cell r="D47">
-            <v>53.736842105263158</v>
+            <v>53</v>
           </cell>
         </row>
         <row r="48">
@@ -1050,10 +1052,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>2288</v>
+            <v>2442</v>
           </cell>
           <cell r="D48">
-            <v>120.42105263157895</v>
+            <v>122.1</v>
           </cell>
         </row>
         <row r="49">
@@ -1064,10 +1066,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>790</v>
+            <v>806</v>
           </cell>
           <cell r="D49">
-            <v>41.578947368421055</v>
+            <v>40.299999999999997</v>
           </cell>
         </row>
         <row r="50">
@@ -1078,14 +1080,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>996</v>
+            <v>1026</v>
           </cell>
           <cell r="D50">
-            <v>52.421052631578945</v>
+            <v>51.3</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1432,11 +1434,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>22297</v>
+        <v>23358</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1173.5263157894738</v>
+        <v>1167.9000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,11 +1452,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>48.631578947368418</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1468,11 +1470,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>9343</v>
+        <v>9821</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>491.73684210526318</v>
+        <v>491.05</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1486,11 +1488,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1987</v>
+        <v>2089</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>104.57894736842105</v>
+        <v>104.45</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1504,11 +1506,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>13.263157894736842</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1522,11 +1524,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>26631</v>
+        <v>28107</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1401.6315789473683</v>
+        <v>1405.35</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1540,11 +1542,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2804</v>
+        <v>2941</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>147.57894736842104</v>
+        <v>147.05000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1558,11 +1560,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>5905</v>
+        <v>6284</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>310.78947368421052</v>
+        <v>314.2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,11 +1578,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>14758</v>
+        <v>15352</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>776.73684210526312</v>
+        <v>767.6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1594,11 +1596,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>7170</v>
+        <v>7499</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>377.36842105263156</v>
+        <v>374.95</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1612,11 +1614,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>63741</v>
+        <v>66947</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3354.7894736842104</v>
+        <v>3347.35</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1630,11 +1632,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>40339</v>
+        <v>42252</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2123.1052631578946</v>
+        <v>2112.6</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1648,11 +1650,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>40312</v>
+        <v>42433</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2121.6842105263158</v>
+        <v>2121.65</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1666,11 +1668,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>49802</v>
+        <v>52159</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2621.1578947368421</v>
+        <v>2607.9499999999998</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1684,11 +1686,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>13445</v>
+        <v>14058</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>707.63157894736844</v>
+        <v>702.9</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1702,11 +1704,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>15895</v>
+        <v>16722</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>836.57894736842104</v>
+        <v>836.1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1720,11 +1722,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>16083</v>
+        <v>16864</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>846.47368421052636</v>
+        <v>843.2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1738,11 +1740,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>5164</v>
+        <v>5377</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>271.78947368421052</v>
+        <v>268.85000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1756,11 +1758,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2516</v>
+        <v>2630</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>132.42105263157896</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1774,11 +1776,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>9586</v>
+        <v>10072</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>504.5263157894737</v>
+        <v>503.6</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1792,11 +1794,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>16378</v>
+        <v>17012</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>862</v>
+        <v>850.6</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1810,11 +1812,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>1152</v>
+        <v>1200</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>60.631578947368418</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1828,11 +1830,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>13311</v>
+        <v>14069</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>700.57894736842104</v>
+        <v>703.45</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1846,11 +1848,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>20615</v>
+        <v>21797</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1085</v>
+        <v>1089.8499999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1864,11 +1866,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>10664</v>
+        <v>11056</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>561.26315789473688</v>
+        <v>552.79999999999995</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1882,11 +1884,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>8140</v>
+        <v>8750</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>428.42105263157896</v>
+        <v>437.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1900,11 +1902,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>4746</v>
+        <v>5084</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>249.78947368421052</v>
+        <v>254.2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,11 +1920,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>5736</v>
+        <v>6256</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>301.89473684210526</v>
+        <v>312.8</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1936,11 +1938,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>2457</v>
+        <v>2559</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>129.31578947368422</v>
+        <v>127.95</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1954,11 +1956,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2694</v>
+        <v>2894</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>141.78947368421052</v>
+        <v>144.69999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1972,11 +1974,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>14915</v>
+        <v>15687</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>785</v>
+        <v>784.35</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1990,11 +1992,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>11547</v>
+        <v>12011</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>607.73684210526312</v>
+        <v>600.54999999999995</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2008,11 +2010,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>15283</v>
+        <v>16019</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>804.36842105263156</v>
+        <v>800.95</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2026,11 +2028,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>10118</v>
+        <v>10529</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>532.52631578947364</v>
+        <v>526.45000000000005</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2044,11 +2046,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4.1052631578947372</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2066,7 +2068,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.57894736842105265</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2080,11 +2082,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2642</v>
+        <v>2684</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>139.05263157894737</v>
+        <v>134.19999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2098,11 +2100,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>10708</v>
+        <v>11345</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>563.57894736842104</v>
+        <v>567.25</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2116,11 +2118,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>7709</v>
+        <v>8105</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>405.73684210526318</v>
+        <v>405.25</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2134,11 +2136,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>4527</v>
+        <v>4933</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>238.26315789473685</v>
+        <v>246.65</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2152,11 +2154,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>9415</v>
+        <v>9829</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>495.5263157894737</v>
+        <v>491.45</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2170,11 +2172,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>5766</v>
+        <v>5971</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>303.4736842105263</v>
+        <v>298.55</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2188,11 +2190,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>5661</v>
+        <v>5867</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>297.94736842105266</v>
+        <v>293.35000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2206,11 +2208,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>1021</v>
+        <v>1060</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>53.736842105263158</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2224,11 +2226,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>2288</v>
+        <v>2442</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>120.42105263157895</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2242,11 +2244,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>790</v>
+        <v>806</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>41.578947368421055</v>
+        <v>40.299999999999997</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2260,11 +2262,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>996</v>
+        <v>1026</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>52.421052631578945</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2329,19 +2331,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>538322</v>
+        <v>565256</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>526624</v>
+        <v>553558</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>28332.736842105263</v>
+        <v>28262.799999999999</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>623320.21052631573</v>
+        <v>621781.6</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2349,11 +2351,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.79977595897137232</v>
+        <v>0.83979135064946642</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-49770.789473684272</v>
+        <v>-51309.400000000023</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2394,7 +2396,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2402,11 +2404,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD37BC39-2DA6-4B27-A5E5-CBDDAC6444B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CB1F37-49BD-4E42-8686-B75902F2FECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -311,6 +311,7 @@
       <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 29-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 30-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -340,7 +341,8 @@
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
-      <sheetData sheetId="23">
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -371,25 +373,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>565256</v>
+            <v>598800</v>
           </cell>
           <cell r="H3">
-            <v>553558</v>
+            <v>587102</v>
           </cell>
           <cell r="I3">
-            <v>28262.799999999999</v>
+            <v>28514.285714285714</v>
           </cell>
           <cell r="J3">
-            <v>621781.6</v>
+            <v>627314.28571428568</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.83979135064946642</v>
+            <v>0.88962710837019066</v>
           </cell>
           <cell r="M3">
-            <v>-51309.400000000023</v>
+            <v>-45776.714285714319</v>
           </cell>
         </row>
         <row r="4">
@@ -400,10 +402,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>23358</v>
+            <v>24787</v>
           </cell>
           <cell r="D4">
-            <v>1167.9000000000001</v>
+            <v>1180.3333333333333</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -432,10 +434,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>929</v>
+            <v>937</v>
           </cell>
           <cell r="D5">
-            <v>46.45</v>
+            <v>44.61904761904762</v>
           </cell>
           <cell r="G5">
             <v>11698</v>
@@ -444,16 +446,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46294</v>
+            <v>46295</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>20</v>
+            <v>21</v>
           </cell>
           <cell r="L5">
-            <v>2</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="6">
@@ -464,10 +466,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>9821</v>
+            <v>10278</v>
           </cell>
           <cell r="D6">
-            <v>491.05</v>
+            <v>489.42857142857144</v>
           </cell>
         </row>
         <row r="7">
@@ -478,10 +480,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>2089</v>
+            <v>2257</v>
           </cell>
           <cell r="D7">
-            <v>104.45</v>
+            <v>107.47619047619048</v>
           </cell>
         </row>
         <row r="8">
@@ -492,10 +494,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>280</v>
+            <v>306</v>
           </cell>
           <cell r="D8">
-            <v>14</v>
+            <v>14.571428571428571</v>
           </cell>
         </row>
         <row r="9">
@@ -506,10 +508,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>28107</v>
+            <v>29227</v>
           </cell>
           <cell r="D9">
-            <v>1405.35</v>
+            <v>1391.7619047619048</v>
           </cell>
         </row>
         <row r="10">
@@ -520,10 +522,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>2941</v>
+            <v>3113</v>
           </cell>
           <cell r="D10">
-            <v>147.05000000000001</v>
+            <v>148.23809523809524</v>
           </cell>
         </row>
         <row r="11">
@@ -534,10 +536,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>6284</v>
+            <v>6747</v>
           </cell>
           <cell r="D11">
-            <v>314.2</v>
+            <v>321.28571428571428</v>
           </cell>
         </row>
         <row r="12">
@@ -548,10 +550,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>15352</v>
+            <v>16541</v>
           </cell>
           <cell r="D12">
-            <v>767.6</v>
+            <v>787.66666666666663</v>
           </cell>
         </row>
         <row r="13">
@@ -562,10 +564,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>7499</v>
+            <v>8151</v>
           </cell>
           <cell r="D13">
-            <v>374.95</v>
+            <v>388.14285714285717</v>
           </cell>
         </row>
         <row r="14">
@@ -576,10 +578,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>66947</v>
+            <v>70692</v>
           </cell>
           <cell r="D14">
-            <v>3347.35</v>
+            <v>3366.2857142857142</v>
           </cell>
         </row>
         <row r="15">
@@ -590,10 +592,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>42252</v>
+            <v>44499</v>
           </cell>
           <cell r="D15">
-            <v>2112.6</v>
+            <v>2119</v>
           </cell>
         </row>
         <row r="16">
@@ -604,10 +606,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>42433</v>
+            <v>44630</v>
           </cell>
           <cell r="D16">
-            <v>2121.65</v>
+            <v>2125.2380952380954</v>
           </cell>
         </row>
         <row r="17">
@@ -618,10 +620,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>52159</v>
+            <v>55127</v>
           </cell>
           <cell r="D17">
-            <v>2607.9499999999998</v>
+            <v>2625.0952380952381</v>
           </cell>
         </row>
         <row r="18">
@@ -632,10 +634,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>14058</v>
+            <v>14905</v>
           </cell>
           <cell r="D18">
-            <v>702.9</v>
+            <v>709.76190476190482</v>
           </cell>
         </row>
         <row r="19">
@@ -646,10 +648,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>16722</v>
+            <v>17819</v>
           </cell>
           <cell r="D19">
-            <v>836.1</v>
+            <v>848.52380952380952</v>
           </cell>
         </row>
         <row r="20">
@@ -660,10 +662,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>16864</v>
+            <v>17897</v>
           </cell>
           <cell r="D20">
-            <v>843.2</v>
+            <v>852.23809523809518</v>
           </cell>
         </row>
         <row r="21">
@@ -674,10 +676,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>5377</v>
+            <v>5809</v>
           </cell>
           <cell r="D21">
-            <v>268.85000000000002</v>
+            <v>276.61904761904759</v>
           </cell>
         </row>
         <row r="22">
@@ -688,10 +690,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>2630</v>
+            <v>2873</v>
           </cell>
           <cell r="D22">
-            <v>131.5</v>
+            <v>136.8095238095238</v>
           </cell>
         </row>
         <row r="23">
@@ -702,10 +704,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>10072</v>
+            <v>10830</v>
           </cell>
           <cell r="D23">
-            <v>503.6</v>
+            <v>515.71428571428567</v>
           </cell>
         </row>
         <row r="24">
@@ -716,10 +718,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>17012</v>
+            <v>18374</v>
           </cell>
           <cell r="D24">
-            <v>850.6</v>
+            <v>874.95238095238096</v>
           </cell>
         </row>
         <row r="25">
@@ -730,10 +732,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>1200</v>
+            <v>1440</v>
           </cell>
           <cell r="D25">
-            <v>60</v>
+            <v>68.571428571428569</v>
           </cell>
         </row>
         <row r="26">
@@ -744,10 +746,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>14069</v>
+            <v>14758</v>
           </cell>
           <cell r="D26">
-            <v>703.45</v>
+            <v>702.76190476190482</v>
           </cell>
         </row>
         <row r="27">
@@ -758,10 +760,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>21797</v>
+            <v>22794</v>
           </cell>
           <cell r="D27">
-            <v>1089.8499999999999</v>
+            <v>1085.4285714285713</v>
           </cell>
         </row>
         <row r="28">
@@ -772,10 +774,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>11056</v>
+            <v>11895</v>
           </cell>
           <cell r="D28">
-            <v>552.79999999999995</v>
+            <v>566.42857142857144</v>
           </cell>
         </row>
         <row r="29">
@@ -786,10 +788,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>8750</v>
+            <v>9458</v>
           </cell>
           <cell r="D29">
-            <v>437.5</v>
+            <v>450.38095238095241</v>
           </cell>
         </row>
         <row r="30">
@@ -800,10 +802,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>5084</v>
+            <v>5248</v>
           </cell>
           <cell r="D30">
-            <v>254.2</v>
+            <v>249.9047619047619</v>
           </cell>
         </row>
         <row r="31">
@@ -814,10 +816,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>6256</v>
+            <v>6416</v>
           </cell>
           <cell r="D31">
-            <v>312.8</v>
+            <v>305.52380952380952</v>
           </cell>
         </row>
         <row r="32">
@@ -828,10 +830,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>2559</v>
+            <v>2790</v>
           </cell>
           <cell r="D32">
-            <v>127.95</v>
+            <v>132.85714285714286</v>
           </cell>
         </row>
         <row r="33">
@@ -842,10 +844,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>2894</v>
+            <v>3099</v>
           </cell>
           <cell r="D33">
-            <v>144.69999999999999</v>
+            <v>147.57142857142858</v>
           </cell>
         </row>
         <row r="34">
@@ -856,10 +858,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>15687</v>
+            <v>16707</v>
           </cell>
           <cell r="D34">
-            <v>784.35</v>
+            <v>795.57142857142856</v>
           </cell>
         </row>
         <row r="35">
@@ -870,10 +872,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>12011</v>
+            <v>12836</v>
           </cell>
           <cell r="D35">
-            <v>600.54999999999995</v>
+            <v>611.23809523809518</v>
           </cell>
         </row>
         <row r="36">
@@ -884,10 +886,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>16019</v>
+            <v>17012</v>
           </cell>
           <cell r="D36">
-            <v>800.95</v>
+            <v>810.09523809523807</v>
           </cell>
         </row>
         <row r="37">
@@ -898,10 +900,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>10529</v>
+            <v>11324</v>
           </cell>
           <cell r="D37">
-            <v>526.45000000000005</v>
+            <v>539.23809523809518</v>
           </cell>
         </row>
         <row r="38">
@@ -915,7 +917,7 @@
             <v>80</v>
           </cell>
           <cell r="D38">
-            <v>4</v>
+            <v>3.8095238095238093</v>
           </cell>
         </row>
         <row r="39">
@@ -929,7 +931,7 @@
             <v>11</v>
           </cell>
           <cell r="D39">
-            <v>0.55000000000000004</v>
+            <v>0.52380952380952384</v>
           </cell>
         </row>
         <row r="40">
@@ -940,10 +942,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>2684</v>
+            <v>2705</v>
           </cell>
           <cell r="D40">
-            <v>134.19999999999999</v>
+            <v>128.8095238095238</v>
           </cell>
         </row>
         <row r="41">
@@ -954,10 +956,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>11345</v>
+            <v>12255</v>
           </cell>
           <cell r="D41">
-            <v>567.25</v>
+            <v>583.57142857142856</v>
           </cell>
         </row>
         <row r="42">
@@ -968,10 +970,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>8105</v>
+            <v>8738</v>
           </cell>
           <cell r="D42">
-            <v>405.25</v>
+            <v>416.09523809523807</v>
           </cell>
         </row>
         <row r="43">
@@ -982,10 +984,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>4933</v>
+            <v>5325</v>
           </cell>
           <cell r="D43">
-            <v>246.65</v>
+            <v>253.57142857142858</v>
           </cell>
         </row>
         <row r="44">
@@ -996,10 +998,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>9829</v>
+            <v>10342</v>
           </cell>
           <cell r="D44">
-            <v>491.45</v>
+            <v>492.47619047619048</v>
           </cell>
         </row>
         <row r="45">
@@ -1010,10 +1012,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>5971</v>
+            <v>6148</v>
           </cell>
           <cell r="D45">
-            <v>298.55</v>
+            <v>292.76190476190476</v>
           </cell>
         </row>
         <row r="46">
@@ -1024,10 +1026,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>5867</v>
+            <v>6035</v>
           </cell>
           <cell r="D46">
-            <v>293.35000000000002</v>
+            <v>287.38095238095241</v>
           </cell>
         </row>
         <row r="47">
@@ -1038,10 +1040,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>1060</v>
+            <v>1124</v>
           </cell>
           <cell r="D47">
-            <v>53</v>
+            <v>53.523809523809526</v>
           </cell>
         </row>
         <row r="48">
@@ -1052,10 +1054,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>2442</v>
+            <v>2523</v>
           </cell>
           <cell r="D48">
-            <v>122.1</v>
+            <v>120.14285714285714</v>
           </cell>
         </row>
         <row r="49">
@@ -1066,10 +1068,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>806</v>
+            <v>872</v>
           </cell>
           <cell r="D49">
-            <v>40.299999999999997</v>
+            <v>41.523809523809526</v>
           </cell>
         </row>
         <row r="50">
@@ -1080,14 +1082,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>1026</v>
+            <v>1066</v>
           </cell>
           <cell r="D50">
-            <v>51.3</v>
+            <v>50.761904761904759</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1434,11 +1436,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>23358</v>
+        <v>24787</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1167.9000000000001</v>
+        <v>1180.3333333333333</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,11 +1454,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>46.45</v>
+        <v>44.61904761904762</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1470,11 +1472,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>9821</v>
+        <v>10278</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>491.05</v>
+        <v>489.42857142857144</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1488,11 +1490,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>2089</v>
+        <v>2257</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>104.45</v>
+        <v>107.47619047619048</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,11 +1508,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>14</v>
+        <v>14.571428571428571</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,11 +1526,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>28107</v>
+        <v>29227</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1405.35</v>
+        <v>1391.7619047619048</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1542,11 +1544,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2941</v>
+        <v>3113</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>147.05000000000001</v>
+        <v>148.23809523809524</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1560,11 +1562,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>6284</v>
+        <v>6747</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>314.2</v>
+        <v>321.28571428571428</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1578,11 +1580,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>15352</v>
+        <v>16541</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>767.6</v>
+        <v>787.66666666666663</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1596,11 +1598,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>7499</v>
+        <v>8151</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>374.95</v>
+        <v>388.14285714285717</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1614,11 +1616,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>66947</v>
+        <v>70692</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3347.35</v>
+        <v>3366.2857142857142</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,11 +1634,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>42252</v>
+        <v>44499</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2112.6</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1650,11 +1652,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>42433</v>
+        <v>44630</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2121.65</v>
+        <v>2125.2380952380954</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1668,11 +1670,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>52159</v>
+        <v>55127</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2607.9499999999998</v>
+        <v>2625.0952380952381</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1686,11 +1688,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>14058</v>
+        <v>14905</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>702.9</v>
+        <v>709.76190476190482</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1704,11 +1706,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>16722</v>
+        <v>17819</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>836.1</v>
+        <v>848.52380952380952</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1722,11 +1724,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>16864</v>
+        <v>17897</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>843.2</v>
+        <v>852.23809523809518</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1740,11 +1742,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>5377</v>
+        <v>5809</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>268.85000000000002</v>
+        <v>276.61904761904759</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1758,11 +1760,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2630</v>
+        <v>2873</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>131.5</v>
+        <v>136.8095238095238</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1776,11 +1778,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>10072</v>
+        <v>10830</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>503.6</v>
+        <v>515.71428571428567</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1794,11 +1796,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>17012</v>
+        <v>18374</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>850.6</v>
+        <v>874.95238095238096</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,11 +1814,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>1200</v>
+        <v>1440</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>60</v>
+        <v>68.571428571428569</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1830,11 +1832,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>14069</v>
+        <v>14758</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>703.45</v>
+        <v>702.76190476190482</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1848,11 +1850,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>21797</v>
+        <v>22794</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1089.8499999999999</v>
+        <v>1085.4285714285713</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1866,11 +1868,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>11056</v>
+        <v>11895</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>552.79999999999995</v>
+        <v>566.42857142857144</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,11 +1886,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>8750</v>
+        <v>9458</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>437.5</v>
+        <v>450.38095238095241</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1902,11 +1904,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>5084</v>
+        <v>5248</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>254.2</v>
+        <v>249.9047619047619</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1920,11 +1922,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>6256</v>
+        <v>6416</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>312.8</v>
+        <v>305.52380952380952</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1938,11 +1940,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>2559</v>
+        <v>2790</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>127.95</v>
+        <v>132.85714285714286</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1956,11 +1958,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2894</v>
+        <v>3099</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>144.69999999999999</v>
+        <v>147.57142857142858</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1974,11 +1976,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>15687</v>
+        <v>16707</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>784.35</v>
+        <v>795.57142857142856</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1992,11 +1994,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>12011</v>
+        <v>12836</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>600.54999999999995</v>
+        <v>611.23809523809518</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2010,11 +2012,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>16019</v>
+        <v>17012</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>800.95</v>
+        <v>810.09523809523807</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2028,11 +2030,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>10529</v>
+        <v>11324</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>526.45000000000005</v>
+        <v>539.23809523809518</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2050,7 +2052,7 @@
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4</v>
+        <v>3.8095238095238093</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2068,7 +2070,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.55000000000000004</v>
+        <v>0.52380952380952384</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2082,11 +2084,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2684</v>
+        <v>2705</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>134.19999999999999</v>
+        <v>128.8095238095238</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2100,11 +2102,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>11345</v>
+        <v>12255</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>567.25</v>
+        <v>583.57142857142856</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2118,11 +2120,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>8105</v>
+        <v>8738</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>405.25</v>
+        <v>416.09523809523807</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2136,11 +2138,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>4933</v>
+        <v>5325</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>246.65</v>
+        <v>253.57142857142858</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2154,11 +2156,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>9829</v>
+        <v>10342</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>491.45</v>
+        <v>492.47619047619048</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2172,11 +2174,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>5971</v>
+        <v>6148</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>298.55</v>
+        <v>292.76190476190476</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2190,11 +2192,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>5867</v>
+        <v>6035</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>293.35000000000002</v>
+        <v>287.38095238095241</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2208,11 +2210,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>1060</v>
+        <v>1124</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>53</v>
+        <v>53.523809523809526</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2226,11 +2228,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>2442</v>
+        <v>2523</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>122.1</v>
+        <v>120.14285714285714</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2244,11 +2246,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>806</v>
+        <v>872</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>40.299999999999997</v>
+        <v>41.523809523809526</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2262,11 +2264,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>1026</v>
+        <v>1066</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>51.3</v>
+        <v>50.761904761904759</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2331,19 +2333,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>565256</v>
+        <v>598800</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>553558</v>
+        <v>587102</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>28262.799999999999</v>
+        <v>28514.285714285714</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>621781.6</v>
+        <v>627314.28571428568</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2351,11 +2353,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.83979135064946642</v>
+        <v>0.88962710837019066</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-51309.400000000023</v>
+        <v>-45776.714285714319</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2396,7 +2398,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2404,11 +2406,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CB1F37-49BD-4E42-8686-B75902F2FECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD28C379-E093-4DB8-B333-C1874732F91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -371,29 +372,6 @@
             <v>DIF UNITS</v>
           </cell>
         </row>
-        <row r="3">
-          <cell r="G3">
-            <v>598800</v>
-          </cell>
-          <cell r="H3">
-            <v>587102</v>
-          </cell>
-          <cell r="I3">
-            <v>28514.285714285714</v>
-          </cell>
-          <cell r="J3">
-            <v>627314.28571428568</v>
-          </cell>
-          <cell r="K3">
-            <v>673091</v>
-          </cell>
-          <cell r="L3">
-            <v>0.88962710837019066</v>
-          </cell>
-          <cell r="M3">
-            <v>-45776.714285714319</v>
-          </cell>
-        </row>
         <row r="4">
           <cell r="A4">
             <v>110150</v>
@@ -401,30 +379,6 @@
           <cell r="B4" t="str">
             <v>Cremosillo Tradicional 150g</v>
           </cell>
-          <cell r="C4">
-            <v>24787</v>
-          </cell>
-          <cell r="D4">
-            <v>1180.3333333333333</v>
-          </cell>
-          <cell r="G4" t="str">
-            <v>UNITS RETURN</v>
-          </cell>
-          <cell r="H4" t="str">
-            <v>INICIO DE VENTA</v>
-          </cell>
-          <cell r="I4" t="str">
-            <v>TRANSC. VENTA</v>
-          </cell>
-          <cell r="J4" t="str">
-            <v>FINAL DE VENTA</v>
-          </cell>
-          <cell r="K4" t="str">
-            <v>DIAS VENTA EFECT.</v>
-          </cell>
-          <cell r="L4" t="str">
-            <v>DIAS VENTA RESTA.</v>
-          </cell>
         </row>
         <row r="5">
           <cell r="A5">
@@ -433,30 +387,6 @@
           <cell r="B5" t="str">
             <v>Cremosillo Coco 150g</v>
           </cell>
-          <cell r="C5">
-            <v>937</v>
-          </cell>
-          <cell r="D5">
-            <v>44.61904761904762</v>
-          </cell>
-          <cell r="G5">
-            <v>11698</v>
-          </cell>
-          <cell r="H5">
-            <v>46266</v>
-          </cell>
-          <cell r="I5">
-            <v>46295</v>
-          </cell>
-          <cell r="J5">
-            <v>46295</v>
-          </cell>
-          <cell r="K5">
-            <v>21</v>
-          </cell>
-          <cell r="L5">
-            <v>1</v>
-          </cell>
         </row>
         <row r="6">
           <cell r="A6">
@@ -465,12 +395,6 @@
           <cell r="B6" t="str">
             <v>Cremosillo Tradicional 230g</v>
           </cell>
-          <cell r="C6">
-            <v>10278</v>
-          </cell>
-          <cell r="D6">
-            <v>489.42857142857144</v>
-          </cell>
         </row>
         <row r="7">
           <cell r="A7">
@@ -479,12 +403,6 @@
           <cell r="B7" t="str">
             <v>Cremosillo Tradicional 400g</v>
           </cell>
-          <cell r="C7">
-            <v>2257</v>
-          </cell>
-          <cell r="D7">
-            <v>107.47619047619048</v>
-          </cell>
         </row>
         <row r="8">
           <cell r="A8">
@@ -493,12 +411,6 @@
           <cell r="B8" t="str">
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
-          <cell r="C8">
-            <v>306</v>
-          </cell>
-          <cell r="D8">
-            <v>14.571428571428571</v>
-          </cell>
         </row>
         <row r="9">
           <cell r="A9">
@@ -507,12 +419,6 @@
           <cell r="B9" t="str">
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
-          <cell r="C9">
-            <v>29227</v>
-          </cell>
-          <cell r="D9">
-            <v>1391.7619047619048</v>
-          </cell>
         </row>
         <row r="10">
           <cell r="A10">
@@ -521,12 +427,6 @@
           <cell r="B10" t="str">
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
-          <cell r="C10">
-            <v>3113</v>
-          </cell>
-          <cell r="D10">
-            <v>148.23809523809524</v>
-          </cell>
         </row>
         <row r="11">
           <cell r="A11">
@@ -535,12 +435,6 @@
           <cell r="B11" t="str">
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
-          <cell r="C11">
-            <v>6747</v>
-          </cell>
-          <cell r="D11">
-            <v>321.28571428571428</v>
-          </cell>
         </row>
         <row r="12">
           <cell r="A12">
@@ -549,12 +443,6 @@
           <cell r="B12" t="str">
             <v>Cremigurt Natural 150g</v>
           </cell>
-          <cell r="C12">
-            <v>16541</v>
-          </cell>
-          <cell r="D12">
-            <v>787.66666666666663</v>
-          </cell>
         </row>
         <row r="13">
           <cell r="A13">
@@ -563,12 +451,6 @@
           <cell r="B13" t="str">
             <v>Cremigurt Dulce 150g</v>
           </cell>
-          <cell r="C13">
-            <v>8151</v>
-          </cell>
-          <cell r="D13">
-            <v>388.14285714285717</v>
-          </cell>
         </row>
         <row r="14">
           <cell r="A14">
@@ -577,12 +459,6 @@
           <cell r="B14" t="str">
             <v>Cremigurt Fresa 150g</v>
           </cell>
-          <cell r="C14">
-            <v>70692</v>
-          </cell>
-          <cell r="D14">
-            <v>3366.2857142857142</v>
-          </cell>
         </row>
         <row r="15">
           <cell r="A15">
@@ -591,12 +467,6 @@
           <cell r="B15" t="str">
             <v>Cremigurt Durazno 150g</v>
           </cell>
-          <cell r="C15">
-            <v>44499</v>
-          </cell>
-          <cell r="D15">
-            <v>2119</v>
-          </cell>
         </row>
         <row r="16">
           <cell r="A16">
@@ -605,12 +475,6 @@
           <cell r="B16" t="str">
             <v>Cremigurt Piña 150g</v>
           </cell>
-          <cell r="C16">
-            <v>44630</v>
-          </cell>
-          <cell r="D16">
-            <v>2125.2380952380954</v>
-          </cell>
         </row>
         <row r="17">
           <cell r="A17">
@@ -619,12 +483,6 @@
           <cell r="B17" t="str">
             <v>Cremigurt Griego 150g</v>
           </cell>
-          <cell r="C17">
-            <v>55127</v>
-          </cell>
-          <cell r="D17">
-            <v>2625.0952380952381</v>
-          </cell>
         </row>
         <row r="18">
           <cell r="A18">
@@ -633,12 +491,6 @@
           <cell r="B18" t="str">
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
-          <cell r="C18">
-            <v>14905</v>
-          </cell>
-          <cell r="D18">
-            <v>709.76190476190482</v>
-          </cell>
         </row>
         <row r="19">
           <cell r="A19">
@@ -647,12 +499,6 @@
           <cell r="B19" t="str">
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
-          <cell r="C19">
-            <v>17819</v>
-          </cell>
-          <cell r="D19">
-            <v>848.52380952380952</v>
-          </cell>
         </row>
         <row r="20">
           <cell r="A20">
@@ -661,12 +507,6 @@
           <cell r="B20" t="str">
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
-          <cell r="C20">
-            <v>17897</v>
-          </cell>
-          <cell r="D20">
-            <v>852.23809523809518</v>
-          </cell>
         </row>
         <row r="21">
           <cell r="A21">
@@ -675,12 +515,6 @@
           <cell r="B21" t="str">
             <v>Cremigurt Natural 700g</v>
           </cell>
-          <cell r="C21">
-            <v>5809</v>
-          </cell>
-          <cell r="D21">
-            <v>276.61904761904759</v>
-          </cell>
         </row>
         <row r="22">
           <cell r="A22">
@@ -689,12 +523,6 @@
           <cell r="B22" t="str">
             <v>Cremigurt Dulce 700g</v>
           </cell>
-          <cell r="C22">
-            <v>2873</v>
-          </cell>
-          <cell r="D22">
-            <v>136.8095238095238</v>
-          </cell>
         </row>
         <row r="23">
           <cell r="A23">
@@ -703,12 +531,6 @@
           <cell r="B23" t="str">
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
-          <cell r="C23">
-            <v>10830</v>
-          </cell>
-          <cell r="D23">
-            <v>515.71428571428567</v>
-          </cell>
         </row>
         <row r="24">
           <cell r="A24">
@@ -717,12 +539,6 @@
           <cell r="B24" t="str">
             <v>Cremigurt Griego 700g</v>
           </cell>
-          <cell r="C24">
-            <v>18374</v>
-          </cell>
-          <cell r="D24">
-            <v>874.95238095238096</v>
-          </cell>
         </row>
         <row r="25">
           <cell r="A25">
@@ -731,12 +547,6 @@
           <cell r="B25" t="str">
             <v>Griego Mykonos 700g</v>
           </cell>
-          <cell r="C25">
-            <v>1440</v>
-          </cell>
-          <cell r="D25">
-            <v>68.571428571428569</v>
-          </cell>
         </row>
         <row r="26">
           <cell r="A26">
@@ -745,12 +555,6 @@
           <cell r="B26" t="str">
             <v>Cremigurt Power Natural 150g</v>
           </cell>
-          <cell r="C26">
-            <v>14758</v>
-          </cell>
-          <cell r="D26">
-            <v>702.76190476190482</v>
-          </cell>
         </row>
         <row r="27">
           <cell r="A27">
@@ -759,12 +563,6 @@
           <cell r="B27" t="str">
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
-          <cell r="C27">
-            <v>22794</v>
-          </cell>
-          <cell r="D27">
-            <v>1085.4285714285713</v>
-          </cell>
         </row>
         <row r="28">
           <cell r="A28">
@@ -773,12 +571,6 @@
           <cell r="B28" t="str">
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
-          <cell r="C28">
-            <v>11895</v>
-          </cell>
-          <cell r="D28">
-            <v>566.42857142857144</v>
-          </cell>
         </row>
         <row r="29">
           <cell r="A29">
@@ -787,12 +579,6 @@
           <cell r="B29" t="str">
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
-          <cell r="C29">
-            <v>9458</v>
-          </cell>
-          <cell r="D29">
-            <v>450.38095238095241</v>
-          </cell>
         </row>
         <row r="30">
           <cell r="A30">
@@ -801,12 +587,6 @@
           <cell r="B30" t="str">
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
-          <cell r="C30">
-            <v>5248</v>
-          </cell>
-          <cell r="D30">
-            <v>249.9047619047619</v>
-          </cell>
         </row>
         <row r="31">
           <cell r="A31">
@@ -815,12 +595,6 @@
           <cell r="B31" t="str">
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
-          <cell r="C31">
-            <v>6416</v>
-          </cell>
-          <cell r="D31">
-            <v>305.52380952380952</v>
-          </cell>
         </row>
         <row r="32">
           <cell r="A32">
@@ -829,12 +603,6 @@
           <cell r="B32" t="str">
             <v>Cremigurt Power Natural 700g</v>
           </cell>
-          <cell r="C32">
-            <v>2790</v>
-          </cell>
-          <cell r="D32">
-            <v>132.85714285714286</v>
-          </cell>
         </row>
         <row r="33">
           <cell r="A33">
@@ -843,12 +611,6 @@
           <cell r="B33" t="str">
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
-          <cell r="C33">
-            <v>3099</v>
-          </cell>
-          <cell r="D33">
-            <v>147.57142857142858</v>
-          </cell>
         </row>
         <row r="34">
           <cell r="A34">
@@ -857,12 +619,6 @@
           <cell r="B34" t="str">
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
-          <cell r="C34">
-            <v>16707</v>
-          </cell>
-          <cell r="D34">
-            <v>795.57142857142856</v>
-          </cell>
         </row>
         <row r="35">
           <cell r="A35">
@@ -871,12 +627,6 @@
           <cell r="B35" t="str">
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
-          <cell r="C35">
-            <v>12836</v>
-          </cell>
-          <cell r="D35">
-            <v>611.23809523809518</v>
-          </cell>
         </row>
         <row r="36">
           <cell r="A36">
@@ -885,12 +635,6 @@
           <cell r="B36" t="str">
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
-          <cell r="C36">
-            <v>17012</v>
-          </cell>
-          <cell r="D36">
-            <v>810.09523809523807</v>
-          </cell>
         </row>
         <row r="37">
           <cell r="A37">
@@ -899,12 +643,6 @@
           <cell r="B37" t="str">
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
-          <cell r="C37">
-            <v>11324</v>
-          </cell>
-          <cell r="D37">
-            <v>539.23809523809518</v>
-          </cell>
         </row>
         <row r="38">
           <cell r="A38">
@@ -913,12 +651,6 @@
           <cell r="B38" t="str">
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
-          <cell r="C38">
-            <v>80</v>
-          </cell>
-          <cell r="D38">
-            <v>3.8095238095238093</v>
-          </cell>
         </row>
         <row r="39">
           <cell r="A39">
@@ -927,12 +659,6 @@
           <cell r="B39" t="str">
             <v>Cremigurt Griego Dulce 4 Kg</v>
           </cell>
-          <cell r="C39">
-            <v>11</v>
-          </cell>
-          <cell r="D39">
-            <v>0.52380952380952384</v>
-          </cell>
         </row>
         <row r="40">
           <cell r="A40">
@@ -941,12 +667,6 @@
           <cell r="B40" t="str">
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
-          <cell r="C40">
-            <v>2705</v>
-          </cell>
-          <cell r="D40">
-            <v>128.8095238095238</v>
-          </cell>
         </row>
         <row r="41">
           <cell r="A41">
@@ -955,12 +675,6 @@
           <cell r="B41" t="str">
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
-          <cell r="C41">
-            <v>12255</v>
-          </cell>
-          <cell r="D41">
-            <v>583.57142857142856</v>
-          </cell>
         </row>
         <row r="42">
           <cell r="A42">
@@ -969,12 +683,6 @@
           <cell r="B42" t="str">
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
-          <cell r="C42">
-            <v>8738</v>
-          </cell>
-          <cell r="D42">
-            <v>416.09523809523807</v>
-          </cell>
         </row>
         <row r="43">
           <cell r="A43">
@@ -983,12 +691,6 @@
           <cell r="B43" t="str">
             <v>Tevia Limon 360ml</v>
           </cell>
-          <cell r="C43">
-            <v>5325</v>
-          </cell>
-          <cell r="D43">
-            <v>253.57142857142858</v>
-          </cell>
         </row>
         <row r="44">
           <cell r="A44">
@@ -997,12 +699,6 @@
           <cell r="B44" t="str">
             <v>Tevia Durazno 360ml</v>
           </cell>
-          <cell r="C44">
-            <v>10342</v>
-          </cell>
-          <cell r="D44">
-            <v>492.47619047619048</v>
-          </cell>
         </row>
         <row r="45">
           <cell r="A45">
@@ -1011,12 +707,6 @@
           <cell r="B45" t="str">
             <v>Tevia Blueberry 360ml</v>
           </cell>
-          <cell r="C45">
-            <v>6148</v>
-          </cell>
-          <cell r="D45">
-            <v>292.76190476190476</v>
-          </cell>
         </row>
         <row r="46">
           <cell r="A46">
@@ -1025,12 +715,6 @@
           <cell r="B46" t="str">
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
-          <cell r="C46">
-            <v>6035</v>
-          </cell>
-          <cell r="D46">
-            <v>287.38095238095241</v>
-          </cell>
         </row>
         <row r="47">
           <cell r="A47">
@@ -1039,12 +723,6 @@
           <cell r="B47" t="str">
             <v>Tevia Limon 1.5L</v>
           </cell>
-          <cell r="C47">
-            <v>1124</v>
-          </cell>
-          <cell r="D47">
-            <v>53.523809523809526</v>
-          </cell>
         </row>
         <row r="48">
           <cell r="A48">
@@ -1053,12 +731,6 @@
           <cell r="B48" t="str">
             <v>Tevia Durazno 1.5 L</v>
           </cell>
-          <cell r="C48">
-            <v>2523</v>
-          </cell>
-          <cell r="D48">
-            <v>120.14285714285714</v>
-          </cell>
         </row>
         <row r="49">
           <cell r="A49">
@@ -1067,12 +739,6 @@
           <cell r="B49" t="str">
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
-          <cell r="C49">
-            <v>872</v>
-          </cell>
-          <cell r="D49">
-            <v>41.523809523809526</v>
-          </cell>
         </row>
         <row r="50">
           <cell r="A50">
@@ -1081,15 +747,471 @@
           <cell r="B50" t="str">
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
-          <cell r="C50">
-            <v>1066</v>
-          </cell>
-          <cell r="D50">
-            <v>50.761904761904759</v>
-          </cell>
         </row>
       </sheetData>
       <sheetData sheetId="25"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="INVENTARIO NACIONAL 01-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 02-10-26"/>
+      <sheetName val="CCC"/>
+      <sheetName val="VINCULO VTS BY SKU SEPTIEMBRE"/>
+      <sheetName val="VINCULO VTS BY SKU OPEN"/>
+      <sheetName val="DESV. VTS BY SKU"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
+        <row r="3">
+          <cell r="G3">
+            <v>20466</v>
+          </cell>
+          <cell r="H3">
+            <v>20012</v>
+          </cell>
+          <cell r="I3">
+            <v>20466</v>
+          </cell>
+          <cell r="J3">
+            <v>429786</v>
+          </cell>
+          <cell r="K3">
+            <v>688000</v>
+          </cell>
+          <cell r="L3">
+            <v>2.9747093023255813E-2</v>
+          </cell>
+          <cell r="M3">
+            <v>-258214</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4">
+            <v>770</v>
+          </cell>
+          <cell r="D4">
+            <v>770</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>UNITS RETURN</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>INICIO DE VENTA</v>
+          </cell>
+          <cell r="I4" t="str">
+            <v>TRANSC. VENTA</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>FINAL DE VENTA</v>
+          </cell>
+          <cell r="K4" t="str">
+            <v>DIAS VENTA EFECT.</v>
+          </cell>
+          <cell r="L4" t="str">
+            <v>DIAS VENTA RESTA.</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>0</v>
+          </cell>
+          <cell r="D5">
+            <v>0</v>
+          </cell>
+          <cell r="G5">
+            <v>454</v>
+          </cell>
+          <cell r="H5">
+            <v>46296</v>
+          </cell>
+          <cell r="I5">
+            <v>46297</v>
+          </cell>
+          <cell r="J5">
+            <v>46326</v>
+          </cell>
+          <cell r="K5">
+            <v>1</v>
+          </cell>
+          <cell r="L5">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>380</v>
+          </cell>
+          <cell r="D6">
+            <v>380</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>56</v>
+          </cell>
+          <cell r="D7">
+            <v>56</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>2</v>
+          </cell>
+          <cell r="D8">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>1256</v>
+          </cell>
+          <cell r="D9">
+            <v>1256</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>108</v>
+          </cell>
+          <cell r="D10">
+            <v>108</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>231</v>
+          </cell>
+          <cell r="D11">
+            <v>231</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>450</v>
+          </cell>
+          <cell r="D12">
+            <v>450</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>220</v>
+          </cell>
+          <cell r="D13">
+            <v>220</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>2663</v>
+          </cell>
+          <cell r="D14">
+            <v>2663</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>1618</v>
+          </cell>
+          <cell r="D15">
+            <v>1618</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1602</v>
+          </cell>
+          <cell r="D16">
+            <v>1602</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>2030</v>
+          </cell>
+          <cell r="D17">
+            <v>2030</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>552</v>
+          </cell>
+          <cell r="D18">
+            <v>552</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>687</v>
+          </cell>
+          <cell r="D19">
+            <v>687</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>646</v>
+          </cell>
+          <cell r="D20">
+            <v>646</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>151</v>
+          </cell>
+          <cell r="D21">
+            <v>151</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>52</v>
+          </cell>
+          <cell r="D22">
+            <v>52</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>287</v>
+          </cell>
+          <cell r="D23">
+            <v>287</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>463</v>
+          </cell>
+          <cell r="D24">
+            <v>463</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>0</v>
+          </cell>
+          <cell r="D25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>440</v>
+          </cell>
+          <cell r="D26">
+            <v>440</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>954</v>
+          </cell>
+          <cell r="D27">
+            <v>954</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>284</v>
+          </cell>
+          <cell r="D28">
+            <v>284</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>243</v>
+          </cell>
+          <cell r="D29">
+            <v>243</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>339</v>
+          </cell>
+          <cell r="D30">
+            <v>339</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>361</v>
+          </cell>
+          <cell r="D31">
+            <v>361</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>55</v>
+          </cell>
+          <cell r="D32">
+            <v>55</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>80</v>
+          </cell>
+          <cell r="D33">
+            <v>80</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="C34">
+            <v>561</v>
+          </cell>
+          <cell r="D34">
+            <v>561</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="C35">
+            <v>339</v>
+          </cell>
+          <cell r="D35">
+            <v>339</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36">
+            <v>498</v>
+          </cell>
+          <cell r="D36">
+            <v>498</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="C37">
+            <v>351</v>
+          </cell>
+          <cell r="D37">
+            <v>351</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="C38">
+            <v>1</v>
+          </cell>
+          <cell r="D38">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="C39">
+            <v>0</v>
+          </cell>
+          <cell r="D39">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="C40">
+            <v>56</v>
+          </cell>
+          <cell r="D40">
+            <v>56</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="C41">
+            <v>371</v>
+          </cell>
+          <cell r="D41">
+            <v>371</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="C42">
+            <v>342</v>
+          </cell>
+          <cell r="D42">
+            <v>342</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>202</v>
+          </cell>
+          <cell r="D43">
+            <v>202</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>330</v>
+          </cell>
+          <cell r="D44">
+            <v>330</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>151</v>
+          </cell>
+          <cell r="D45">
+            <v>151</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46">
+            <v>216</v>
+          </cell>
+          <cell r="D46">
+            <v>216</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="C47">
+            <v>16</v>
+          </cell>
+          <cell r="D47">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="C48">
+            <v>24</v>
+          </cell>
+          <cell r="D48">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="C49">
+            <v>12</v>
+          </cell>
+          <cell r="D49">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="C50">
+            <v>16</v>
+          </cell>
+          <cell r="D50">
+            <v>16</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1435,12 +1557,12 @@
         <v>Cremosillo Tradicional 150g</v>
       </c>
       <c r="C2" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>24787</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C4</f>
+        <v>770</v>
       </c>
       <c r="D2" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1180.3333333333333</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D4</f>
+        <v>770</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1453,12 +1575,12 @@
         <v>Cremosillo Coco 150g</v>
       </c>
       <c r="C3" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>937</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C5</f>
+        <v>0</v>
       </c>
       <c r="D3" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>44.61904761904762</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D5</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,12 +1593,12 @@
         <v>Cremosillo Tradicional 230g</v>
       </c>
       <c r="C4" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>10278</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C6</f>
+        <v>380</v>
       </c>
       <c r="D4" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>489.42857142857144</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D6</f>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1489,12 +1611,12 @@
         <v>Cremosillo Tradicional 400g</v>
       </c>
       <c r="C5" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>2257</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C7</f>
+        <v>56</v>
       </c>
       <c r="D5" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>107.47619047619048</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D7</f>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1507,12 +1629,12 @@
         <v>Cremosillo Tradicional 1000g</v>
       </c>
       <c r="C6" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>306</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C8</f>
+        <v>2</v>
       </c>
       <c r="D6" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>14.571428571428571</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D8</f>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1525,12 +1647,12 @@
         <v>Gelatina Saltarina Fresa 130g</v>
       </c>
       <c r="C7" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>29227</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C9</f>
+        <v>1256</v>
       </c>
       <c r="D7" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1391.7619047619048</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D9</f>
+        <v>1256</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1543,12 +1665,12 @@
         <v>Gelatina Saltarina Chicle 130g</v>
       </c>
       <c r="C8" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>3113</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C10</f>
+        <v>108</v>
       </c>
       <c r="D8" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>148.23809523809524</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D10</f>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1561,12 +1683,12 @@
         <v>Gelatina Saltarina Kolita 130g</v>
       </c>
       <c r="C9" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>6747</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C11</f>
+        <v>231</v>
       </c>
       <c r="D9" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>321.28571428571428</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D11</f>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1579,12 +1701,12 @@
         <v>Cremigurt Natural 150g</v>
       </c>
       <c r="C10" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>16541</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C12</f>
+        <v>450</v>
       </c>
       <c r="D10" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>787.66666666666663</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D12</f>
+        <v>450</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1597,12 +1719,12 @@
         <v>Cremigurt Dulce 150g</v>
       </c>
       <c r="C11" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>8151</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C13</f>
+        <v>220</v>
       </c>
       <c r="D11" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>388.14285714285717</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D13</f>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,12 +1737,12 @@
         <v>Cremigurt Fresa 150g</v>
       </c>
       <c r="C12" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>70692</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C14</f>
+        <v>2663</v>
       </c>
       <c r="D12" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3366.2857142857142</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D14</f>
+        <v>2663</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1633,12 +1755,12 @@
         <v>Cremigurt Durazno 150g</v>
       </c>
       <c r="C13" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>44499</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C15</f>
+        <v>1618</v>
       </c>
       <c r="D13" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2119</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D15</f>
+        <v>1618</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,12 +1773,12 @@
         <v>Cremigurt Piña 150g</v>
       </c>
       <c r="C14" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>44630</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C16</f>
+        <v>1602</v>
       </c>
       <c r="D14" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2125.2380952380954</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D16</f>
+        <v>1602</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1669,12 +1791,12 @@
         <v>Cremigurt Griego 150g</v>
       </c>
       <c r="C15" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>55127</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C17</f>
+        <v>2030</v>
       </c>
       <c r="D15" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2625.0952380952381</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D17</f>
+        <v>2030</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1687,12 +1809,12 @@
         <v>Cremigurt Griego Mango 150g</v>
       </c>
       <c r="C16" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>14905</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C18</f>
+        <v>552</v>
       </c>
       <c r="D16" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>709.76190476190482</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D18</f>
+        <v>552</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1705,12 +1827,12 @@
         <v>Cremigurt Griego Ciruela 150g</v>
       </c>
       <c r="C17" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>17819</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C19</f>
+        <v>687</v>
       </c>
       <c r="D17" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>848.52380952380952</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D19</f>
+        <v>687</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1723,12 +1845,12 @@
         <v>Cremigurt Griego Mora 150g</v>
       </c>
       <c r="C18" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>17897</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C20</f>
+        <v>646</v>
       </c>
       <c r="D18" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>852.23809523809518</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D20</f>
+        <v>646</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1741,12 +1863,12 @@
         <v>Cremigurt Natural 700g</v>
       </c>
       <c r="C19" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>5809</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C21</f>
+        <v>151</v>
       </c>
       <c r="D19" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>276.61904761904759</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D21</f>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1759,12 +1881,12 @@
         <v>Cremigurt Dulce 700g</v>
       </c>
       <c r="C20" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2873</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C22</f>
+        <v>52</v>
       </c>
       <c r="D20" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>136.8095238095238</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D22</f>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1777,12 +1899,12 @@
         <v>Cremigurt Griego Fresa 700g</v>
       </c>
       <c r="C21" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>10830</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C23</f>
+        <v>287</v>
       </c>
       <c r="D21" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>515.71428571428567</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D23</f>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1795,12 +1917,12 @@
         <v>Cremigurt Griego 700g</v>
       </c>
       <c r="C22" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>18374</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C24</f>
+        <v>463</v>
       </c>
       <c r="D22" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>874.95238095238096</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D24</f>
+        <v>463</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1813,12 +1935,12 @@
         <v>Griego Mykonos 700g</v>
       </c>
       <c r="C23" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>1440</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C25</f>
+        <v>0</v>
       </c>
       <c r="D23" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>68.571428571428569</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D25</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1831,12 +1953,12 @@
         <v>Cremigurt Power Natural 150g</v>
       </c>
       <c r="C24" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>14758</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C26</f>
+        <v>440</v>
       </c>
       <c r="D24" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>702.76190476190482</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D26</f>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1849,12 +1971,12 @@
         <v>Cremigurt Power Mantecado 150g</v>
       </c>
       <c r="C25" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>22794</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C27</f>
+        <v>954</v>
       </c>
       <c r="D25" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1085.4285714285713</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D27</f>
+        <v>954</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,12 +1989,12 @@
         <v>Cremigurt Power CheesseCake Fresa 150g</v>
       </c>
       <c r="C26" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>11895</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C28</f>
+        <v>284</v>
       </c>
       <c r="D26" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>566.42857142857144</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D28</f>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1885,12 +2007,12 @@
         <v>Cremigurt Power Cookies and Cream 150g</v>
       </c>
       <c r="C27" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>9458</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C29</f>
+        <v>243</v>
       </c>
       <c r="D27" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>450.38095238095241</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D29</f>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1903,12 +2025,12 @@
         <v>Cremigurt Power Piña Colada 150g</v>
       </c>
       <c r="C28" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>5248</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C30</f>
+        <v>339</v>
       </c>
       <c r="D28" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>249.9047619047619</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D30</f>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1921,12 +2043,12 @@
         <v>Cremigurt Power Dulce de Leche 150g</v>
       </c>
       <c r="C29" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>6416</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C31</f>
+        <v>361</v>
       </c>
       <c r="D29" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>305.52380952380952</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D31</f>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1939,12 +2061,12 @@
         <v>Cremigurt Power Natural 700g</v>
       </c>
       <c r="C30" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>2790</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C32</f>
+        <v>55</v>
       </c>
       <c r="D30" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>132.85714285714286</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D32</f>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1957,12 +2079,12 @@
         <v>Cremigurt Power Mantecado 700g</v>
       </c>
       <c r="C31" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>3099</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C33</f>
+        <v>80</v>
       </c>
       <c r="D31" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>147.57142857142858</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D33</f>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1975,12 +2097,12 @@
         <v>Cremigurt Griego Fresa S/A 150g</v>
       </c>
       <c r="C32" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>16707</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C34</f>
+        <v>561</v>
       </c>
       <c r="D32" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>795.57142857142856</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D34</f>
+        <v>561</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1993,12 +2115,12 @@
         <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
       </c>
       <c r="C33" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>12836</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C35</f>
+        <v>339</v>
       </c>
       <c r="D33" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>611.23809523809518</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D35</f>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2011,12 +2133,12 @@
         <v>Cremigurt Griego Pie de Limón S/A 150g</v>
       </c>
       <c r="C34" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>17012</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C36</f>
+        <v>498</v>
       </c>
       <c r="D34" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>810.09523809523807</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D36</f>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2029,12 +2151,12 @@
         <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
       </c>
       <c r="C35" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>11324</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C37</f>
+        <v>351</v>
       </c>
       <c r="D35" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>539.23809523809518</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D37</f>
+        <v>351</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2047,12 +2169,12 @@
         <v>Cremigurt Griego Natural 4 Kg</v>
       </c>
       <c r="C36" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>80</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C38</f>
+        <v>1</v>
       </c>
       <c r="D36" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>3.8095238095238093</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D38</f>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2065,12 +2187,12 @@
         <v>Cremigurt Griego Dulce 4 Kg</v>
       </c>
       <c r="C37" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>11</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C39</f>
+        <v>0</v>
       </c>
       <c r="D37" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.52380952380952384</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D39</f>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2083,12 +2205,12 @@
         <v>Cremigurt Líquido Dulce 230g</v>
       </c>
       <c r="C38" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2705</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C40</f>
+        <v>56</v>
       </c>
       <c r="D38" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>128.8095238095238</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D40</f>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2101,12 +2223,12 @@
         <v>Cremigurt Líquido Fresa 230g</v>
       </c>
       <c r="C39" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>12255</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C41</f>
+        <v>371</v>
       </c>
       <c r="D39" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>583.57142857142856</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D41</f>
+        <v>371</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2119,12 +2241,12 @@
         <v>Cremigurt Líquido Durazno 230g</v>
       </c>
       <c r="C40" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>8738</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C42</f>
+        <v>342</v>
       </c>
       <c r="D40" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>416.09523809523807</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D42</f>
+        <v>342</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2137,12 +2259,12 @@
         <v>Tevia Limon 360ml</v>
       </c>
       <c r="C41" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>5325</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C43</f>
+        <v>202</v>
       </c>
       <c r="D41" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>253.57142857142858</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D43</f>
+        <v>202</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2155,12 +2277,12 @@
         <v>Tevia Durazno 360ml</v>
       </c>
       <c r="C42" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>10342</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C44</f>
+        <v>330</v>
       </c>
       <c r="D42" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>492.47619047619048</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D44</f>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2173,12 +2295,12 @@
         <v>Tevia Blueberry 360ml</v>
       </c>
       <c r="C43" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>6148</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C45</f>
+        <v>151</v>
       </c>
       <c r="D43" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>292.76190476190476</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D45</f>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2191,12 +2313,12 @@
         <v>Tevia Tropical Punch 360ml</v>
       </c>
       <c r="C44" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>6035</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C46</f>
+        <v>216</v>
       </c>
       <c r="D44" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>287.38095238095241</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D46</f>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2209,12 +2331,12 @@
         <v>Tevia Limon 1.5L</v>
       </c>
       <c r="C45" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>1124</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C47</f>
+        <v>16</v>
       </c>
       <c r="D45" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>53.523809523809526</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D47</f>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2227,12 +2349,12 @@
         <v>Tevia Durazno 1.5 L</v>
       </c>
       <c r="C46" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>2523</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C48</f>
+        <v>24</v>
       </c>
       <c r="D46" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>120.14285714285714</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D48</f>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2245,12 +2367,12 @@
         <v>Tevia Blueberry 1.5 L</v>
       </c>
       <c r="C47" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>872</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C49</f>
+        <v>12</v>
       </c>
       <c r="D47" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>41.523809523809526</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D49</f>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2263,12 +2385,12 @@
         <v>Tevia Tropical Punch 1.5 L</v>
       </c>
       <c r="C48" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>1066</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C50</f>
+        <v>16</v>
       </c>
       <c r="D48" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>50.761904761904759</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D50</f>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2332,85 +2454,85 @@
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>598800</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!G3</f>
+        <v>20466</v>
       </c>
       <c r="B3" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>587102</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!H3</f>
+        <v>20012</v>
       </c>
       <c r="C3" s="4">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>28514.285714285714</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!I3</f>
+        <v>20466</v>
       </c>
       <c r="D3" s="5">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>627314.28571428568</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!J3</f>
+        <v>429786</v>
       </c>
       <c r="E3" s="4">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
-        <v>673091</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!K3</f>
+        <v>688000</v>
       </c>
       <c r="F3" s="6">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.88962710837019066</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!L3</f>
+        <v>2.9747093023255813E-2</v>
       </c>
       <c r="G3" s="7">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-45776.714285714319</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!M3</f>
+        <v>-258214</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="str">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!G4</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!G4</f>
         <v>UNITS RETURN</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H4</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!H4</f>
         <v>INICIO DE VENTA</v>
       </c>
       <c r="C4" s="18" t="str">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!I4</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!I4</f>
         <v>TRANSC. VENTA</v>
       </c>
       <c r="D4" s="18" t="str">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!J4</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!J4</f>
         <v>FINAL DE VENTA</v>
       </c>
       <c r="E4" s="18" t="str">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!K4</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!K4</f>
         <v>DIAS VENTA EFECT.</v>
       </c>
       <c r="F4" s="18" t="str">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!L4</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!L4</f>
         <v>DIAS VENTA RESTA.</v>
       </c>
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>11698</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!G5</f>
+        <v>454</v>
       </c>
       <c r="B5" s="16">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
-        <v>46266</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!H5</f>
+        <v>46296</v>
       </c>
       <c r="C5" s="16">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46295</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!I5</f>
+        <v>46297</v>
       </c>
       <c r="D5" s="16">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
-        <v>46295</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!J5</f>
+        <v>46326</v>
       </c>
       <c r="E5" s="19">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>21</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!K5</f>
+        <v>1</v>
       </c>
       <c r="F5" s="17">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>1</v>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!L5</f>
+        <v>20</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD28C379-E093-4DB8-B333-C1874732F91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B6EC6A-5E6E-4080-867A-CF0C63ED12E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -289,6 +289,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INVENTARIO NACIONAL INICIO"/>
@@ -321,7 +322,13 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2">
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>Referencia interna</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
@@ -760,10 +767,13 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INVENTARIO NACIONAL 01-10-26"/>
       <sheetName val="INVENTARIO NACIONAL 02-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 05-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 06-10-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU SEPTIEMBRE"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -774,36 +784,38 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
         <row r="3">
           <cell r="G3">
-            <v>20466</v>
+            <v>64658</v>
           </cell>
           <cell r="H3">
-            <v>20012</v>
+            <v>63679</v>
           </cell>
           <cell r="I3">
-            <v>20466</v>
+            <v>21552.666666666668</v>
           </cell>
           <cell r="J3">
-            <v>429786</v>
+            <v>452606</v>
           </cell>
           <cell r="K3">
             <v>688000</v>
           </cell>
           <cell r="L3">
-            <v>2.9747093023255813E-2</v>
+            <v>9.3979651162790695E-2</v>
           </cell>
           <cell r="M3">
-            <v>-258214</v>
+            <v>-235394</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>770</v>
+            <v>2759</v>
           </cell>
           <cell r="D4">
-            <v>770</v>
+            <v>1379.5</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -826,292 +838,292 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="D5">
-            <v>0</v>
+            <v>1.5</v>
           </cell>
           <cell r="G5">
-            <v>454</v>
+            <v>979</v>
           </cell>
           <cell r="H5">
             <v>46296</v>
           </cell>
           <cell r="I5">
-            <v>46297</v>
+            <v>46300</v>
           </cell>
           <cell r="J5">
             <v>46326</v>
           </cell>
           <cell r="K5">
-            <v>1</v>
+            <v>3</v>
           </cell>
           <cell r="L5">
-            <v>20</v>
+            <v>18</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>380</v>
+            <v>1244</v>
           </cell>
           <cell r="D6">
-            <v>380</v>
+            <v>622</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>56</v>
+            <v>173</v>
           </cell>
           <cell r="D7">
-            <v>56</v>
+            <v>86.5</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>2</v>
+            <v>17</v>
           </cell>
           <cell r="D8">
-            <v>2</v>
+            <v>8.5</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>1256</v>
+            <v>4014</v>
           </cell>
           <cell r="D9">
-            <v>1256</v>
+            <v>2007</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>108</v>
+            <v>422</v>
           </cell>
           <cell r="D10">
-            <v>108</v>
+            <v>211</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>231</v>
+            <v>891</v>
           </cell>
           <cell r="D11">
-            <v>231</v>
+            <v>445.5</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>450</v>
+            <v>1649</v>
           </cell>
           <cell r="D12">
-            <v>450</v>
+            <v>824.5</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>220</v>
+            <v>668</v>
           </cell>
           <cell r="D13">
-            <v>220</v>
+            <v>334</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>2663</v>
+            <v>7789</v>
           </cell>
           <cell r="D14">
-            <v>2663</v>
+            <v>3894.5</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>1618</v>
+            <v>5027</v>
           </cell>
           <cell r="D15">
-            <v>1618</v>
+            <v>2513.5</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>1602</v>
+            <v>4808</v>
           </cell>
           <cell r="D16">
-            <v>1602</v>
+            <v>2404</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>2030</v>
+            <v>5754</v>
           </cell>
           <cell r="D17">
-            <v>2030</v>
+            <v>2877</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>552</v>
+            <v>1550</v>
           </cell>
           <cell r="D18">
-            <v>552</v>
+            <v>775</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>687</v>
+            <v>2100</v>
           </cell>
           <cell r="D19">
-            <v>687</v>
+            <v>1050</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>646</v>
+            <v>2058</v>
           </cell>
           <cell r="D20">
-            <v>646</v>
+            <v>1029</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>151</v>
+            <v>416</v>
           </cell>
           <cell r="D21">
-            <v>151</v>
+            <v>208</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>52</v>
+            <v>198</v>
           </cell>
           <cell r="D22">
-            <v>52</v>
+            <v>99</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>287</v>
+            <v>922</v>
           </cell>
           <cell r="D23">
-            <v>287</v>
+            <v>461</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>463</v>
+            <v>1592</v>
           </cell>
           <cell r="D24">
-            <v>463</v>
+            <v>796</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>0</v>
+            <v>260</v>
           </cell>
           <cell r="D25">
-            <v>0</v>
+            <v>130</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>440</v>
+            <v>1554</v>
           </cell>
           <cell r="D26">
-            <v>440</v>
+            <v>777</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>954</v>
+            <v>2645</v>
           </cell>
           <cell r="D27">
-            <v>954</v>
+            <v>1322.5</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>284</v>
+            <v>1133</v>
           </cell>
           <cell r="D28">
-            <v>284</v>
+            <v>566.5</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>243</v>
+            <v>1026</v>
           </cell>
           <cell r="D29">
-            <v>243</v>
+            <v>513</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>339</v>
+            <v>790</v>
           </cell>
           <cell r="D30">
-            <v>339</v>
+            <v>395</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>361</v>
+            <v>1020</v>
           </cell>
           <cell r="D31">
-            <v>361</v>
+            <v>510</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>55</v>
+            <v>154</v>
           </cell>
           <cell r="D32">
-            <v>55</v>
+            <v>77</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>80</v>
+            <v>298</v>
           </cell>
           <cell r="D33">
-            <v>80</v>
+            <v>149</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>561</v>
+            <v>1916</v>
           </cell>
           <cell r="D34">
-            <v>561</v>
+            <v>958</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>339</v>
+            <v>1310</v>
           </cell>
           <cell r="D35">
-            <v>339</v>
+            <v>655</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>498</v>
+            <v>1746</v>
           </cell>
           <cell r="D36">
-            <v>498</v>
+            <v>873</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>351</v>
+            <v>1171</v>
           </cell>
           <cell r="D37">
-            <v>351</v>
+            <v>585.5</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>1</v>
+            <v>6</v>
           </cell>
           <cell r="D38">
-            <v>1</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="39">
@@ -1124,94 +1136,94 @@
         </row>
         <row r="40">
           <cell r="C40">
-            <v>56</v>
+            <v>120</v>
           </cell>
           <cell r="D40">
-            <v>56</v>
+            <v>60</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>371</v>
+            <v>1237</v>
           </cell>
           <cell r="D41">
-            <v>371</v>
+            <v>618.5</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>342</v>
+            <v>920</v>
           </cell>
           <cell r="D42">
-            <v>342</v>
+            <v>460</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>202</v>
+            <v>620</v>
           </cell>
           <cell r="D43">
-            <v>202</v>
+            <v>310</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>330</v>
+            <v>1150</v>
           </cell>
           <cell r="D44">
-            <v>330</v>
+            <v>575</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>151</v>
+            <v>584</v>
           </cell>
           <cell r="D45">
-            <v>151</v>
+            <v>292</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>216</v>
+            <v>632</v>
           </cell>
           <cell r="D46">
-            <v>216</v>
+            <v>316</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>16</v>
+            <v>63</v>
           </cell>
           <cell r="D47">
-            <v>16</v>
+            <v>31.5</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>24</v>
+            <v>130</v>
           </cell>
           <cell r="D48">
-            <v>24</v>
+            <v>65</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>12</v>
+            <v>51</v>
           </cell>
           <cell r="D49">
-            <v>12</v>
+            <v>25.5</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>16</v>
+            <v>68</v>
           </cell>
           <cell r="D50">
-            <v>16</v>
+            <v>34</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="7"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1515,25 +1527,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CD20E1-8530-482E-BAF2-454F195C9DA1}">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="10"/>
-    <col min="2" max="2" width="50.7109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="10"/>
+    <col min="2" max="2" width="50.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.5546875" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="24.6640625" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1547,7 +1559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A4</f>
         <v>110150</v>
@@ -1558,14 +1570,14 @@
       </c>
       <c r="C2" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>770</v>
+        <v>2759</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>770</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1379.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A5</f>
         <v>110151</v>
@@ -1576,14 +1588,14 @@
       </c>
       <c r="C3" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A6</f>
         <v>110230</v>
@@ -1594,14 +1606,14 @@
       </c>
       <c r="C4" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>380</v>
+        <v>1244</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>380</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A7</f>
         <v>110400</v>
@@ -1612,14 +1624,14 @@
       </c>
       <c r="C5" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>86.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A8</f>
         <v>111000</v>
@@ -1630,14 +1642,14 @@
       </c>
       <c r="C6" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A9</f>
         <v>120130</v>
@@ -1648,14 +1660,14 @@
       </c>
       <c r="C7" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>1256</v>
+        <v>4014</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A10</f>
         <v>120131</v>
@@ -1666,14 +1678,14 @@
       </c>
       <c r="C8" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>108</v>
+        <v>422</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A11</f>
         <v>120132</v>
@@ -1684,14 +1696,14 @@
       </c>
       <c r="C9" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>231</v>
+        <v>891</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>231</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>445.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A12</f>
         <v>130150</v>
@@ -1702,14 +1714,14 @@
       </c>
       <c r="C10" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>450</v>
+        <v>1649</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>450</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>824.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A13</f>
         <v>130151</v>
@@ -1720,14 +1732,14 @@
       </c>
       <c r="C11" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>220</v>
+        <v>668</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>220</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A14</f>
         <v>130152</v>
@@ -1738,14 +1750,14 @@
       </c>
       <c r="C12" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>2663</v>
+        <v>7789</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>2663</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3894.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A15</f>
         <v>130153</v>
@@ -1756,14 +1768,14 @@
       </c>
       <c r="C13" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>1618</v>
+        <v>5027</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1618</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2513.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A16</f>
         <v>130154</v>
@@ -1774,14 +1786,14 @@
       </c>
       <c r="C14" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>1602</v>
+        <v>4808</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1602</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A17</f>
         <v>130155</v>
@@ -1792,14 +1804,14 @@
       </c>
       <c r="C15" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>2030</v>
+        <v>5754</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A18</f>
         <v>130157</v>
@@ -1810,14 +1822,14 @@
       </c>
       <c r="C16" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>552</v>
+        <v>1550</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>552</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A19</f>
         <v>130158</v>
@@ -1828,14 +1840,14 @@
       </c>
       <c r="C17" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>687</v>
+        <v>2100</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>687</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A20</f>
         <v>130159</v>
@@ -1846,14 +1858,14 @@
       </c>
       <c r="C18" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>646</v>
+        <v>2058</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>646</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A21</f>
         <v>130700</v>
@@ -1864,14 +1876,14 @@
       </c>
       <c r="C19" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>151</v>
+        <v>416</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A22</f>
         <v>130701</v>
@@ -1882,14 +1894,14 @@
       </c>
       <c r="C20" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>52</v>
+        <v>198</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A23</f>
         <v>130702</v>
@@ -1900,14 +1912,14 @@
       </c>
       <c r="C21" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>287</v>
+        <v>922</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>287</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A24</f>
         <v>130703</v>
@@ -1918,14 +1930,14 @@
       </c>
       <c r="C22" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>463</v>
+        <v>1592</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>463</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A25</f>
         <v>130707</v>
@@ -1936,14 +1948,14 @@
       </c>
       <c r="C23" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A26</f>
         <v>131150</v>
@@ -1954,14 +1966,14 @@
       </c>
       <c r="C24" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>440</v>
+        <v>1554</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>440</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A27</f>
         <v>131151</v>
@@ -1972,14 +1984,14 @@
       </c>
       <c r="C25" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>954</v>
+        <v>2645</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>954</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1322.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A28</f>
         <v>131152</v>
@@ -1990,14 +2002,14 @@
       </c>
       <c r="C26" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>284</v>
+        <v>1133</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>284</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>566.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A29</f>
         <v>131153</v>
@@ -2008,14 +2020,14 @@
       </c>
       <c r="C27" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>243</v>
+        <v>1026</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>243</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A30</f>
         <v>131154</v>
@@ -2026,14 +2038,14 @@
       </c>
       <c r="C28" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>339</v>
+        <v>790</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>339</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A31</f>
         <v>131155</v>
@@ -2044,14 +2056,14 @@
       </c>
       <c r="C29" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>361</v>
+        <v>1020</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>361</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A32</f>
         <v>131700</v>
@@ -2062,14 +2074,14 @@
       </c>
       <c r="C30" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A33</f>
         <v>131701</v>
@@ -2080,14 +2092,14 @@
       </c>
       <c r="C31" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A34</f>
         <v>132150</v>
@@ -2098,14 +2110,14 @@
       </c>
       <c r="C32" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>561</v>
+        <v>1916</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>561</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A35</f>
         <v>132151</v>
@@ -2116,14 +2128,14 @@
       </c>
       <c r="C33" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>339</v>
+        <v>1310</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>339</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A36</f>
         <v>132152</v>
@@ -2134,14 +2146,14 @@
       </c>
       <c r="C34" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>498</v>
+        <v>1746</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>498</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A37</f>
         <v>132153</v>
@@ -2152,14 +2164,14 @@
       </c>
       <c r="C35" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>351</v>
+        <v>1171</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>351</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>585.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A38</f>
         <v>134000</v>
@@ -2170,14 +2182,14 @@
       </c>
       <c r="C36" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A39</f>
         <v>134001</v>
@@ -2195,7 +2207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A40</f>
         <v>140230</v>
@@ -2206,14 +2218,14 @@
       </c>
       <c r="C38" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A41</f>
         <v>140231</v>
@@ -2224,14 +2236,14 @@
       </c>
       <c r="C39" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>371</v>
+        <v>1237</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>371</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>618.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A42</f>
         <v>140232</v>
@@ -2242,14 +2254,14 @@
       </c>
       <c r="C40" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>342</v>
+        <v>920</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>342</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A43</f>
         <v>150360</v>
@@ -2260,14 +2272,14 @@
       </c>
       <c r="C41" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>202</v>
+        <v>620</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>202</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A44</f>
         <v>150361</v>
@@ -2278,14 +2290,14 @@
       </c>
       <c r="C42" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>330</v>
+        <v>1150</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>330</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A45</f>
         <v>150362</v>
@@ -2296,14 +2308,14 @@
       </c>
       <c r="C43" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>151</v>
+        <v>584</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A46</f>
         <v>150363</v>
@@ -2314,14 +2326,14 @@
       </c>
       <c r="C44" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>216</v>
+        <v>632</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>216</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A47</f>
         <v>151500</v>
@@ -2332,14 +2344,14 @@
       </c>
       <c r="C45" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A48</f>
         <v>151501</v>
@@ -2350,14 +2362,14 @@
       </c>
       <c r="C46" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A49</f>
         <v>151502</v>
@@ -2368,14 +2380,14 @@
       </c>
       <c r="C47" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A50</f>
         <v>151503</v>
@@ -2386,14 +2398,14 @@
       </c>
       <c r="C48" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C49" s="11"/>
     </row>
   </sheetData>
@@ -2404,13 +2416,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC79391-350C-4657-A510-D4378E4F4331}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="1" max="7" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G1</f>
         <v>DASHBOARD</v>
@@ -2422,7 +2434,7 @@
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
     </row>
-    <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G2</f>
         <v>TOTAL UNITS SALES GROSS</v>
@@ -2452,22 +2464,22 @@
         <v>DIF UNITS</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <f>'[2]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>20466</v>
+        <v>64658</v>
       </c>
       <c r="B3" s="3">
         <f>'[2]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>20012</v>
+        <v>63679</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>20466</v>
+        <v>21552.666666666668</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>429786</v>
+        <v>452606</v>
       </c>
       <c r="E3" s="4">
         <f>'[2]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2475,14 +2487,14 @@
       </c>
       <c r="F3" s="6">
         <f>'[2]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>2.9747093023255813E-2</v>
+        <v>9.3979651162790695E-2</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-258214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-235394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="str">
         <f>'[2]VINCULO VTS BY SKU OPEN'!G4</f>
         <v>UNITS RETURN</v>
@@ -2509,10 +2521,10 @@
       </c>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <f>'[2]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>454</v>
+        <v>979</v>
       </c>
       <c r="B5" s="16">
         <f>'[2]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2520,7 +2532,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="D5" s="16">
         <f>'[2]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2528,11 +2540,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B6EC6A-5E6E-4080-867A-CF0C63ED12E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD6C5B2-17D1-4BF2-AAE6-39F17FA245A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -774,6 +774,8 @@
       <sheetName val="INVENTARIO NACIONAL 02-10-26"/>
       <sheetName val="INVENTARIO NACIONAL 05-10-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 07-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 08-10-2 "/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU SEPTIEMBRE"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -786,36 +788,38 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
         <row r="3">
           <cell r="G3">
-            <v>64658</v>
+            <v>175115</v>
           </cell>
           <cell r="H3">
-            <v>63679</v>
+            <v>171557</v>
           </cell>
           <cell r="I3">
-            <v>21552.666666666668</v>
+            <v>29185.833333333332</v>
           </cell>
           <cell r="J3">
-            <v>452606</v>
+            <v>612902.5</v>
           </cell>
           <cell r="K3">
             <v>688000</v>
           </cell>
           <cell r="L3">
-            <v>9.3979651162790695E-2</v>
+            <v>0.25452761627906978</v>
           </cell>
           <cell r="M3">
-            <v>-235394</v>
+            <v>-75097.5</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>2759</v>
+            <v>7023</v>
           </cell>
           <cell r="D4">
-            <v>1379.5</v>
+            <v>1170.5</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -838,180 +842,180 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>3</v>
+            <v>50</v>
           </cell>
           <cell r="D5">
-            <v>1.5</v>
+            <v>8.3333333333333339</v>
           </cell>
           <cell r="G5">
-            <v>979</v>
+            <v>3558</v>
           </cell>
           <cell r="H5">
             <v>46296</v>
           </cell>
           <cell r="I5">
-            <v>46300</v>
+            <v>46304</v>
           </cell>
           <cell r="J5">
             <v>46326</v>
           </cell>
           <cell r="K5">
-            <v>3</v>
+            <v>6</v>
           </cell>
           <cell r="L5">
-            <v>18</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>1244</v>
+            <v>2946</v>
           </cell>
           <cell r="D6">
-            <v>622</v>
+            <v>491</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>173</v>
+            <v>531</v>
           </cell>
           <cell r="D7">
-            <v>86.5</v>
+            <v>88.5</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>17</v>
+            <v>67</v>
           </cell>
           <cell r="D8">
-            <v>8.5</v>
+            <v>11.166666666666666</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>4014</v>
+            <v>9144</v>
           </cell>
           <cell r="D9">
-            <v>2007</v>
+            <v>1524</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>422</v>
+            <v>958</v>
           </cell>
           <cell r="D10">
-            <v>211</v>
+            <v>159.66666666666666</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>891</v>
+            <v>2453</v>
           </cell>
           <cell r="D11">
-            <v>445.5</v>
+            <v>408.83333333333331</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>1649</v>
+            <v>4939</v>
           </cell>
           <cell r="D12">
-            <v>824.5</v>
+            <v>823.16666666666663</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>668</v>
+            <v>2217</v>
           </cell>
           <cell r="D13">
-            <v>334</v>
+            <v>369.5</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>7789</v>
+            <v>21459</v>
           </cell>
           <cell r="D14">
-            <v>3894.5</v>
+            <v>3576.5</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>5027</v>
+            <v>12943</v>
           </cell>
           <cell r="D15">
-            <v>2513.5</v>
+            <v>2157.1666666666665</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>4808</v>
+            <v>12688</v>
           </cell>
           <cell r="D16">
-            <v>2404</v>
+            <v>2114.6666666666665</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>5754</v>
+            <v>16097</v>
           </cell>
           <cell r="D17">
-            <v>2877</v>
+            <v>2682.8333333333335</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>1550</v>
+            <v>4776</v>
           </cell>
           <cell r="D18">
-            <v>775</v>
+            <v>796</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>2100</v>
+            <v>6325</v>
           </cell>
           <cell r="D19">
-            <v>1050</v>
+            <v>1054.1666666666667</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>2058</v>
+            <v>6106</v>
           </cell>
           <cell r="D20">
-            <v>1029</v>
+            <v>1017.6666666666666</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>416</v>
+            <v>1674</v>
           </cell>
           <cell r="D21">
-            <v>208</v>
+            <v>279</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>198</v>
+            <v>814</v>
           </cell>
           <cell r="D22">
-            <v>99</v>
+            <v>135.66666666666666</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>922</v>
+            <v>3061</v>
           </cell>
           <cell r="D23">
-            <v>461</v>
+            <v>510.16666666666669</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>1592</v>
+            <v>5170</v>
           </cell>
           <cell r="D24">
-            <v>796</v>
+            <v>861.66666666666663</v>
           </cell>
         </row>
         <row r="25">
@@ -1019,211 +1023,211 @@
             <v>260</v>
           </cell>
           <cell r="D25">
-            <v>130</v>
+            <v>43.333333333333336</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>1554</v>
+            <v>3741</v>
           </cell>
           <cell r="D26">
-            <v>777</v>
+            <v>623.5</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>2645</v>
+            <v>6195</v>
           </cell>
           <cell r="D27">
-            <v>1322.5</v>
+            <v>1032.5</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>1133</v>
+            <v>3566</v>
           </cell>
           <cell r="D28">
-            <v>566.5</v>
+            <v>594.33333333333337</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>1026</v>
+            <v>2944</v>
           </cell>
           <cell r="D29">
-            <v>513</v>
+            <v>490.66666666666669</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>790</v>
+            <v>1661</v>
           </cell>
           <cell r="D30">
-            <v>395</v>
+            <v>276.83333333333331</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>1020</v>
+            <v>1796</v>
           </cell>
           <cell r="D31">
-            <v>510</v>
+            <v>299.33333333333331</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>154</v>
+            <v>622</v>
           </cell>
           <cell r="D32">
-            <v>77</v>
+            <v>103.66666666666667</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>298</v>
+            <v>749</v>
           </cell>
           <cell r="D33">
-            <v>149</v>
+            <v>124.83333333333333</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>1916</v>
+            <v>5071</v>
           </cell>
           <cell r="D34">
-            <v>958</v>
+            <v>845.16666666666663</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>1310</v>
+            <v>3592</v>
           </cell>
           <cell r="D35">
-            <v>655</v>
+            <v>598.66666666666663</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>1746</v>
+            <v>4718</v>
           </cell>
           <cell r="D36">
-            <v>873</v>
+            <v>786.33333333333337</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>1171</v>
+            <v>3097</v>
           </cell>
           <cell r="D37">
-            <v>585.5</v>
+            <v>516.16666666666663</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>6</v>
+            <v>21</v>
           </cell>
           <cell r="D38">
-            <v>3</v>
+            <v>3.5</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>0</v>
+            <v>8</v>
           </cell>
           <cell r="D39">
-            <v>0</v>
+            <v>1.3333333333333333</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>120</v>
+            <v>224</v>
           </cell>
           <cell r="D40">
-            <v>60</v>
+            <v>37.333333333333336</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>1237</v>
+            <v>3650</v>
           </cell>
           <cell r="D41">
-            <v>618.5</v>
+            <v>608.33333333333337</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>920</v>
+            <v>2645</v>
           </cell>
           <cell r="D42">
-            <v>460</v>
+            <v>440.83333333333331</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>620</v>
+            <v>1659</v>
           </cell>
           <cell r="D43">
-            <v>310</v>
+            <v>276.5</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>1150</v>
+            <v>2900</v>
           </cell>
           <cell r="D44">
-            <v>575</v>
+            <v>483.33333333333331</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>584</v>
+            <v>1552</v>
           </cell>
           <cell r="D45">
-            <v>292</v>
+            <v>258.66666666666669</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>632</v>
+            <v>1620</v>
           </cell>
           <cell r="D46">
-            <v>316</v>
+            <v>270</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>63</v>
+            <v>242</v>
           </cell>
           <cell r="D47">
-            <v>31.5</v>
+            <v>40.333333333333336</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>130</v>
+            <v>507</v>
           </cell>
           <cell r="D48">
-            <v>65</v>
+            <v>84.5</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>51</v>
+            <v>311</v>
           </cell>
           <cell r="D49">
-            <v>25.5</v>
+            <v>51.833333333333336</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>68</v>
+            <v>323</v>
           </cell>
           <cell r="D50">
-            <v>34</v>
+            <v>53.833333333333336</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7"/>
+      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1527,25 +1531,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CD20E1-8530-482E-BAF2-454F195C9DA1}">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="10"/>
-    <col min="2" max="2" width="50.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.5546875" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.109375" customWidth="1"/>
-    <col min="11" max="11" width="24.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="10"/>
+    <col min="2" max="2" width="50.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1559,7 +1563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A4</f>
         <v>110150</v>
@@ -1570,14 +1574,14 @@
       </c>
       <c r="C2" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>2759</v>
+        <v>7023</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1379.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1170.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A5</f>
         <v>110151</v>
@@ -1588,14 +1592,14 @@
       </c>
       <c r="C3" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8.3333333333333339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A6</f>
         <v>110230</v>
@@ -1606,14 +1610,14 @@
       </c>
       <c r="C4" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>1244</v>
+        <v>2946</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>622</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A7</f>
         <v>110400</v>
@@ -1624,14 +1628,14 @@
       </c>
       <c r="C5" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>173</v>
+        <v>531</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>86.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A8</f>
         <v>111000</v>
@@ -1642,14 +1646,14 @@
       </c>
       <c r="C6" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>11.166666666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A9</f>
         <v>120130</v>
@@ -1660,14 +1664,14 @@
       </c>
       <c r="C7" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>4014</v>
+        <v>9144</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A10</f>
         <v>120131</v>
@@ -1678,14 +1682,14 @@
       </c>
       <c r="C8" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>422</v>
+        <v>958</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>211</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>159.66666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A11</f>
         <v>120132</v>
@@ -1696,14 +1700,14 @@
       </c>
       <c r="C9" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>891</v>
+        <v>2453</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>445.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>408.83333333333331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A12</f>
         <v>130150</v>
@@ -1714,14 +1718,14 @@
       </c>
       <c r="C10" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>1649</v>
+        <v>4939</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>824.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>823.16666666666663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A13</f>
         <v>130151</v>
@@ -1732,14 +1736,14 @@
       </c>
       <c r="C11" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>668</v>
+        <v>2217</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>334</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>369.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A14</f>
         <v>130152</v>
@@ -1750,14 +1754,14 @@
       </c>
       <c r="C12" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>7789</v>
+        <v>21459</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3894.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3576.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A15</f>
         <v>130153</v>
@@ -1768,14 +1772,14 @@
       </c>
       <c r="C13" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>5027</v>
+        <v>12943</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2513.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2157.1666666666665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A16</f>
         <v>130154</v>
@@ -1786,14 +1790,14 @@
       </c>
       <c r="C14" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>4808</v>
+        <v>12688</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2404</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2114.6666666666665</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A17</f>
         <v>130155</v>
@@ -1804,14 +1808,14 @@
       </c>
       <c r="C15" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>5754</v>
+        <v>16097</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2877</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2682.8333333333335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A18</f>
         <v>130157</v>
@@ -1822,14 +1826,14 @@
       </c>
       <c r="C16" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>1550</v>
+        <v>4776</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>775</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A19</f>
         <v>130158</v>
@@ -1840,14 +1844,14 @@
       </c>
       <c r="C17" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>2100</v>
+        <v>6325</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1054.1666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A20</f>
         <v>130159</v>
@@ -1858,14 +1862,14 @@
       </c>
       <c r="C18" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>2058</v>
+        <v>6106</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1017.6666666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A21</f>
         <v>130700</v>
@@ -1876,14 +1880,14 @@
       </c>
       <c r="C19" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>416</v>
+        <v>1674</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A22</f>
         <v>130701</v>
@@ -1894,14 +1898,14 @@
       </c>
       <c r="C20" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>198</v>
+        <v>814</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>135.66666666666666</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A23</f>
         <v>130702</v>
@@ -1912,14 +1916,14 @@
       </c>
       <c r="C21" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>922</v>
+        <v>3061</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>461</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>510.16666666666669</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A24</f>
         <v>130703</v>
@@ -1930,14 +1934,14 @@
       </c>
       <c r="C22" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>1592</v>
+        <v>5170</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>796</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>861.66666666666663</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A25</f>
         <v>130707</v>
@@ -1952,10 +1956,10 @@
       </c>
       <c r="D23" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43.333333333333336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A26</f>
         <v>131150</v>
@@ -1966,14 +1970,14 @@
       </c>
       <c r="C24" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>1554</v>
+        <v>3741</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>777</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>623.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A27</f>
         <v>131151</v>
@@ -1984,14 +1988,14 @@
       </c>
       <c r="C25" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>2645</v>
+        <v>6195</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1322.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1032.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A28</f>
         <v>131152</v>
@@ -2002,14 +2006,14 @@
       </c>
       <c r="C26" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>1133</v>
+        <v>3566</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>566.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>594.33333333333337</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A29</f>
         <v>131153</v>
@@ -2020,14 +2024,14 @@
       </c>
       <c r="C27" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>1026</v>
+        <v>2944</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>513</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>490.66666666666669</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A30</f>
         <v>131154</v>
@@ -2038,14 +2042,14 @@
       </c>
       <c r="C28" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>790</v>
+        <v>1661</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>395</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>276.83333333333331</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A31</f>
         <v>131155</v>
@@ -2056,14 +2060,14 @@
       </c>
       <c r="C29" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1020</v>
+        <v>1796</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>510</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>299.33333333333331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A32</f>
         <v>131700</v>
@@ -2074,14 +2078,14 @@
       </c>
       <c r="C30" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>154</v>
+        <v>622</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>103.66666666666667</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A33</f>
         <v>131701</v>
@@ -2092,14 +2096,14 @@
       </c>
       <c r="C31" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>298</v>
+        <v>749</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>149</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>124.83333333333333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A34</f>
         <v>132150</v>
@@ -2110,14 +2114,14 @@
       </c>
       <c r="C32" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>1916</v>
+        <v>5071</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>958</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>845.16666666666663</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A35</f>
         <v>132151</v>
@@ -2128,14 +2132,14 @@
       </c>
       <c r="C33" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>1310</v>
+        <v>3592</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+        <v>598.66666666666663</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A36</f>
         <v>132152</v>
@@ -2146,14 +2150,14 @@
       </c>
       <c r="C34" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>1746</v>
+        <v>4718</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>873</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>786.33333333333337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A37</f>
         <v>132153</v>
@@ -2164,14 +2168,14 @@
       </c>
       <c r="C35" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>1171</v>
+        <v>3097</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>585.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+        <v>516.16666666666663</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A38</f>
         <v>134000</v>
@@ -2182,14 +2186,14 @@
       </c>
       <c r="C36" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A39</f>
         <v>134001</v>
@@ -2200,14 +2204,14 @@
       </c>
       <c r="C37" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A40</f>
         <v>140230</v>
@@ -2218,14 +2222,14 @@
       </c>
       <c r="C38" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>37.333333333333336</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A41</f>
         <v>140231</v>
@@ -2236,14 +2240,14 @@
       </c>
       <c r="C39" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>1237</v>
+        <v>3650</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>618.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>608.33333333333337</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A42</f>
         <v>140232</v>
@@ -2254,14 +2258,14 @@
       </c>
       <c r="C40" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>920</v>
+        <v>2645</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>460</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+        <v>440.83333333333331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A43</f>
         <v>150360</v>
@@ -2272,14 +2276,14 @@
       </c>
       <c r="C41" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>620</v>
+        <v>1659</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>310</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+        <v>276.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A44</f>
         <v>150361</v>
@@ -2290,14 +2294,14 @@
       </c>
       <c r="C42" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>1150</v>
+        <v>2900</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>575</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+        <v>483.33333333333331</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A45</f>
         <v>150362</v>
@@ -2308,14 +2312,14 @@
       </c>
       <c r="C43" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>584</v>
+        <v>1552</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>292</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+        <v>258.66666666666669</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A46</f>
         <v>150363</v>
@@ -2326,14 +2330,14 @@
       </c>
       <c r="C44" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>632</v>
+        <v>1620</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>316</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A47</f>
         <v>151500</v>
@@ -2344,14 +2348,14 @@
       </c>
       <c r="C45" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>63</v>
+        <v>242</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+        <v>40.333333333333336</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A48</f>
         <v>151501</v>
@@ -2362,14 +2366,14 @@
       </c>
       <c r="C46" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>130</v>
+        <v>507</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A49</f>
         <v>151502</v>
@@ -2380,14 +2384,14 @@
       </c>
       <c r="C47" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>51</v>
+        <v>311</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+        <v>51.833333333333336</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!A50</f>
         <v>151503</v>
@@ -2398,14 +2402,14 @@
       </c>
       <c r="C48" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>68</v>
+        <v>323</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+        <v>53.833333333333336</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C49" s="11"/>
     </row>
   </sheetData>
@@ -2416,13 +2420,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC79391-350C-4657-A510-D4378E4F4331}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" customWidth="1"/>
+    <col min="1" max="7" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G1</f>
         <v>DASHBOARD</v>
@@ -2434,7 +2438,7 @@
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
     </row>
-    <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G2</f>
         <v>TOTAL UNITS SALES GROSS</v>
@@ -2464,22 +2468,22 @@
         <v>DIF UNITS</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[2]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>64658</v>
+        <v>175115</v>
       </c>
       <c r="B3" s="3">
         <f>'[2]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>63679</v>
+        <v>171557</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>21552.666666666668</v>
+        <v>29185.833333333332</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>452606</v>
+        <v>612902.5</v>
       </c>
       <c r="E3" s="4">
         <f>'[2]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2487,14 +2491,14 @@
       </c>
       <c r="F3" s="6">
         <f>'[2]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>9.3979651162790695E-2</v>
+        <v>0.25452761627906978</v>
       </c>
       <c r="G3" s="7">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-235394</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>-75097.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="str">
         <f>'[2]VINCULO VTS BY SKU OPEN'!G4</f>
         <v>UNITS RETURN</v>
@@ -2521,10 +2525,10 @@
       </c>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[2]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>979</v>
+        <v>3558</v>
       </c>
       <c r="B5" s="16">
         <f>'[2]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2532,7 +2536,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="D5" s="16">
         <f>'[2]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2540,11 +2544,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD6C5B2-17D1-4BF2-AAE6-39F17FA245A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C0E9F8-1E41-42E2-9AE9-C6C4BAEE1821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -775,51 +775,57 @@
       <sheetName val="INVENTARIO NACIONAL 05-10-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-10-26"/>
       <sheetName val="INVENTARIO NACIONAL 07-10-26"/>
-      <sheetName val="INVENTARIO NACIONAL 08-10-2 "/>
+      <sheetName val="INVENTARIO NACIONAL 08-10-2 (2)"/>
+      <sheetName val="INVENTARIO NACIONAL 09-10-26 "/>
+      <sheetName val="INVENTARIO NACIONAL 13-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 30-10-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU SEPTIEMBRE"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11">
         <row r="3">
           <cell r="G3">
-            <v>175115</v>
+            <v>625691</v>
           </cell>
           <cell r="H3">
-            <v>171557</v>
+            <v>610798</v>
           </cell>
           <cell r="I3">
-            <v>29185.833333333332</v>
+            <v>31284.55</v>
           </cell>
           <cell r="J3">
-            <v>612902.5</v>
+            <v>656975.55000000005</v>
           </cell>
           <cell r="K3">
             <v>688000</v>
           </cell>
           <cell r="L3">
-            <v>0.25452761627906978</v>
+            <v>0.9094345930232558</v>
           </cell>
           <cell r="M3">
-            <v>-75097.5</v>
+            <v>-31024.449999999953</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>7023</v>
+            <v>27365</v>
           </cell>
           <cell r="D4">
-            <v>1170.5</v>
+            <v>1368.25</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -842,392 +848,392 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>50</v>
+            <v>107</v>
           </cell>
           <cell r="D5">
-            <v>8.3333333333333339</v>
+            <v>5.35</v>
           </cell>
           <cell r="G5">
-            <v>3558</v>
+            <v>14893</v>
           </cell>
           <cell r="H5">
             <v>46296</v>
           </cell>
           <cell r="I5">
-            <v>46304</v>
+            <v>46325</v>
           </cell>
           <cell r="J5">
             <v>46326</v>
           </cell>
           <cell r="K5">
-            <v>6</v>
+            <v>20</v>
           </cell>
           <cell r="L5">
-            <v>15</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>2946</v>
+            <v>11066</v>
           </cell>
           <cell r="D6">
-            <v>491</v>
+            <v>553.29999999999995</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>531</v>
+            <v>2242</v>
           </cell>
           <cell r="D7">
-            <v>88.5</v>
+            <v>112.1</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>67</v>
+            <v>326</v>
           </cell>
           <cell r="D8">
-            <v>11.166666666666666</v>
+            <v>16.3</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>9144</v>
+            <v>32718</v>
           </cell>
           <cell r="D9">
-            <v>1524</v>
+            <v>1635.9</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>958</v>
+            <v>2877</v>
           </cell>
           <cell r="D10">
-            <v>159.66666666666666</v>
+            <v>143.85</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>2453</v>
+            <v>8411</v>
           </cell>
           <cell r="D11">
-            <v>408.83333333333331</v>
+            <v>420.55</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>4939</v>
+            <v>17545</v>
           </cell>
           <cell r="D12">
-            <v>823.16666666666663</v>
+            <v>877.25</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>2217</v>
+            <v>7950</v>
           </cell>
           <cell r="D13">
-            <v>369.5</v>
+            <v>397.5</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>21459</v>
+            <v>74433</v>
           </cell>
           <cell r="D14">
-            <v>3576.5</v>
+            <v>3721.65</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>12943</v>
+            <v>45715</v>
           </cell>
           <cell r="D15">
-            <v>2157.1666666666665</v>
+            <v>2285.75</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>12688</v>
+            <v>45631</v>
           </cell>
           <cell r="D16">
-            <v>2114.6666666666665</v>
+            <v>2281.5500000000002</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>16097</v>
+            <v>56896</v>
           </cell>
           <cell r="D17">
-            <v>2682.8333333333335</v>
+            <v>2844.8</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>4776</v>
+            <v>16124</v>
           </cell>
           <cell r="D18">
-            <v>796</v>
+            <v>806.2</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>6325</v>
+            <v>20890</v>
           </cell>
           <cell r="D19">
-            <v>1054.1666666666667</v>
+            <v>1044.5</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>6106</v>
+            <v>20345</v>
           </cell>
           <cell r="D20">
-            <v>1017.6666666666666</v>
+            <v>1017.25</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>1674</v>
+            <v>6236</v>
           </cell>
           <cell r="D21">
-            <v>279</v>
+            <v>311.8</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>814</v>
+            <v>3194</v>
           </cell>
           <cell r="D22">
-            <v>135.66666666666666</v>
+            <v>159.69999999999999</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>3061</v>
+            <v>11208</v>
           </cell>
           <cell r="D23">
-            <v>510.16666666666669</v>
+            <v>560.4</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>5170</v>
+            <v>18579</v>
           </cell>
           <cell r="D24">
-            <v>861.66666666666663</v>
+            <v>928.95</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>260</v>
+            <v>1375</v>
           </cell>
           <cell r="D25">
-            <v>43.333333333333336</v>
+            <v>68.75</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>3741</v>
+            <v>14268</v>
           </cell>
           <cell r="D26">
-            <v>623.5</v>
+            <v>713.4</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>6195</v>
+            <v>23467</v>
           </cell>
           <cell r="D27">
-            <v>1032.5</v>
+            <v>1173.3499999999999</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>3566</v>
+            <v>12967</v>
           </cell>
           <cell r="D28">
-            <v>594.33333333333337</v>
+            <v>648.35</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>2944</v>
+            <v>10438</v>
           </cell>
           <cell r="D29">
-            <v>490.66666666666669</v>
+            <v>521.9</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>1661</v>
+            <v>7267</v>
           </cell>
           <cell r="D30">
-            <v>276.83333333333331</v>
+            <v>363.35</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>1796</v>
+            <v>8185</v>
           </cell>
           <cell r="D31">
-            <v>299.33333333333331</v>
+            <v>409.25</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>622</v>
+            <v>2705</v>
           </cell>
           <cell r="D32">
-            <v>103.66666666666667</v>
+            <v>135.25</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>749</v>
+            <v>3150</v>
           </cell>
           <cell r="D33">
-            <v>124.83333333333333</v>
+            <v>157.5</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>5071</v>
+            <v>16638</v>
           </cell>
           <cell r="D34">
-            <v>845.16666666666663</v>
+            <v>831.9</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>3592</v>
+            <v>12349</v>
           </cell>
           <cell r="D35">
-            <v>598.66666666666663</v>
+            <v>617.45000000000005</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>4718</v>
+            <v>16111</v>
           </cell>
           <cell r="D36">
-            <v>786.33333333333337</v>
+            <v>805.55</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>3097</v>
+            <v>11521</v>
           </cell>
           <cell r="D37">
-            <v>516.16666666666663</v>
+            <v>576.04999999999995</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>21</v>
+            <v>66</v>
           </cell>
           <cell r="D38">
-            <v>3.5</v>
+            <v>3.3</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>8</v>
+            <v>18</v>
           </cell>
           <cell r="D39">
-            <v>1.3333333333333333</v>
+            <v>0.9</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>224</v>
+            <v>2437</v>
           </cell>
           <cell r="D40">
-            <v>37.333333333333336</v>
+            <v>121.85</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>3650</v>
+            <v>8916</v>
           </cell>
           <cell r="D41">
-            <v>608.33333333333337</v>
+            <v>445.8</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>2645</v>
+            <v>7486</v>
           </cell>
           <cell r="D42">
-            <v>440.83333333333331</v>
+            <v>374.3</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>1659</v>
+            <v>6554</v>
           </cell>
           <cell r="D43">
-            <v>276.5</v>
+            <v>327.7</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>2900</v>
+            <v>11903</v>
           </cell>
           <cell r="D44">
-            <v>483.33333333333331</v>
+            <v>595.15</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>1552</v>
+            <v>5679</v>
           </cell>
           <cell r="D45">
-            <v>258.66666666666669</v>
+            <v>283.95</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>1620</v>
+            <v>6319</v>
           </cell>
           <cell r="D46">
-            <v>270</v>
+            <v>315.95</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>242</v>
+            <v>1195</v>
           </cell>
           <cell r="D47">
-            <v>40.333333333333336</v>
+            <v>59.75</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>507</v>
+            <v>1921</v>
           </cell>
           <cell r="D48">
-            <v>84.5</v>
+            <v>96.05</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>311</v>
+            <v>1587</v>
           </cell>
           <cell r="D49">
-            <v>51.833333333333336</v>
+            <v>79.349999999999994</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>323</v>
+            <v>1311</v>
           </cell>
           <cell r="D50">
-            <v>53.833333333333336</v>
+            <v>65.55</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="12" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1574,11 +1580,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>7023</v>
+        <v>27365</v>
       </c>
       <c r="D2" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1170.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D4</f>
+        <v>1368.25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1592,11 +1598,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="D3" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>8.3333333333333339</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D5</f>
+        <v>5.35</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1610,11 +1616,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>2946</v>
+        <v>11066</v>
       </c>
       <c r="D4" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>491</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D6</f>
+        <v>553.29999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1628,11 +1634,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>531</v>
+        <v>2242</v>
       </c>
       <c r="D5" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>88.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D7</f>
+        <v>112.1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1646,11 +1652,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>67</v>
+        <v>326</v>
       </c>
       <c r="D6" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>11.166666666666666</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D8</f>
+        <v>16.3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1664,11 +1670,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>9144</v>
+        <v>32718</v>
       </c>
       <c r="D7" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1524</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D9</f>
+        <v>1635.9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1682,11 +1688,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>958</v>
+        <v>2877</v>
       </c>
       <c r="D8" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>159.66666666666666</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D10</f>
+        <v>143.85</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1700,11 +1706,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>2453</v>
+        <v>8411</v>
       </c>
       <c r="D9" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>408.83333333333331</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D11</f>
+        <v>420.55</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1718,11 +1724,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>4939</v>
+        <v>17545</v>
       </c>
       <c r="D10" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>823.16666666666663</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D12</f>
+        <v>877.25</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1736,11 +1742,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>2217</v>
+        <v>7950</v>
       </c>
       <c r="D11" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>369.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D13</f>
+        <v>397.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1754,11 +1760,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>21459</v>
+        <v>74433</v>
       </c>
       <c r="D12" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3576.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D14</f>
+        <v>3721.65</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1772,11 +1778,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>12943</v>
+        <v>45715</v>
       </c>
       <c r="D13" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2157.1666666666665</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D15</f>
+        <v>2285.75</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1790,11 +1796,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>12688</v>
+        <v>45631</v>
       </c>
       <c r="D14" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2114.6666666666665</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D16</f>
+        <v>2281.5500000000002</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1808,11 +1814,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>16097</v>
+        <v>56896</v>
       </c>
       <c r="D15" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2682.8333333333335</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D17</f>
+        <v>2844.8</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1826,11 +1832,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>4776</v>
+        <v>16124</v>
       </c>
       <c r="D16" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>796</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D18</f>
+        <v>806.2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1844,11 +1850,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>6325</v>
+        <v>20890</v>
       </c>
       <c r="D17" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>1054.1666666666667</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D19</f>
+        <v>1044.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1862,11 +1868,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>6106</v>
+        <v>20345</v>
       </c>
       <c r="D18" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>1017.6666666666666</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D20</f>
+        <v>1017.25</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1880,11 +1886,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>1674</v>
+        <v>6236</v>
       </c>
       <c r="D19" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>279</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D21</f>
+        <v>311.8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1898,11 +1904,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>814</v>
+        <v>3194</v>
       </c>
       <c r="D20" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>135.66666666666666</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D22</f>
+        <v>159.69999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1916,11 +1922,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>3061</v>
+        <v>11208</v>
       </c>
       <c r="D21" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>510.16666666666669</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D23</f>
+        <v>560.4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1934,11 +1940,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>5170</v>
+        <v>18579</v>
       </c>
       <c r="D22" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>861.66666666666663</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D24</f>
+        <v>928.95</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1952,11 +1958,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>260</v>
+        <v>1375</v>
       </c>
       <c r="D23" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>43.333333333333336</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D25</f>
+        <v>68.75</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1970,11 +1976,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>3741</v>
+        <v>14268</v>
       </c>
       <c r="D24" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>623.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D26</f>
+        <v>713.4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1988,11 +1994,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>6195</v>
+        <v>23467</v>
       </c>
       <c r="D25" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>1032.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D27</f>
+        <v>1173.3499999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2006,11 +2012,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>3566</v>
+        <v>12967</v>
       </c>
       <c r="D26" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>594.33333333333337</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D28</f>
+        <v>648.35</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2024,11 +2030,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>2944</v>
+        <v>10438</v>
       </c>
       <c r="D27" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>490.66666666666669</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D29</f>
+        <v>521.9</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2042,11 +2048,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1661</v>
+        <v>7267</v>
       </c>
       <c r="D28" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>276.83333333333331</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D30</f>
+        <v>363.35</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2060,11 +2066,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1796</v>
+        <v>8185</v>
       </c>
       <c r="D29" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>299.33333333333331</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D31</f>
+        <v>409.25</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2078,11 +2084,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>622</v>
+        <v>2705</v>
       </c>
       <c r="D30" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>103.66666666666667</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D32</f>
+        <v>135.25</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2096,11 +2102,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>749</v>
+        <v>3150</v>
       </c>
       <c r="D31" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>124.83333333333333</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D33</f>
+        <v>157.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2114,11 +2120,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>5071</v>
+        <v>16638</v>
       </c>
       <c r="D32" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>845.16666666666663</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D34</f>
+        <v>831.9</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2132,11 +2138,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>3592</v>
+        <v>12349</v>
       </c>
       <c r="D33" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>598.66666666666663</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D35</f>
+        <v>617.45000000000005</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2150,11 +2156,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>4718</v>
+        <v>16111</v>
       </c>
       <c r="D34" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>786.33333333333337</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D36</f>
+        <v>805.55</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2168,11 +2174,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>3097</v>
+        <v>11521</v>
       </c>
       <c r="D35" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>516.16666666666663</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D37</f>
+        <v>576.04999999999995</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2186,11 +2192,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D36" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>3.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D38</f>
+        <v>3.3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2204,11 +2210,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D37" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>1.3333333333333333</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D39</f>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2222,11 +2228,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>224</v>
+        <v>2437</v>
       </c>
       <c r="D38" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>37.333333333333336</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D40</f>
+        <v>121.85</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2240,11 +2246,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>3650</v>
+        <v>8916</v>
       </c>
       <c r="D39" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>608.33333333333337</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D41</f>
+        <v>445.8</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2258,11 +2264,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>2645</v>
+        <v>7486</v>
       </c>
       <c r="D40" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>440.83333333333331</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D42</f>
+        <v>374.3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2276,11 +2282,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1659</v>
+        <v>6554</v>
       </c>
       <c r="D41" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>276.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D43</f>
+        <v>327.7</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2294,11 +2300,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>2900</v>
+        <v>11903</v>
       </c>
       <c r="D42" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>483.33333333333331</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D44</f>
+        <v>595.15</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2312,11 +2318,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>1552</v>
+        <v>5679</v>
       </c>
       <c r="D43" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>258.66666666666669</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D45</f>
+        <v>283.95</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2330,11 +2336,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>1620</v>
+        <v>6319</v>
       </c>
       <c r="D44" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>270</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D46</f>
+        <v>315.95</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2348,11 +2354,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>242</v>
+        <v>1195</v>
       </c>
       <c r="D45" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>40.333333333333336</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D47</f>
+        <v>59.75</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2366,11 +2372,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>507</v>
+        <v>1921</v>
       </c>
       <c r="D46" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>84.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D48</f>
+        <v>96.05</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2384,11 +2390,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>311</v>
+        <v>1587</v>
       </c>
       <c r="D47" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>51.833333333333336</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D49</f>
+        <v>79.349999999999994</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2402,11 +2408,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>323</v>
+        <v>1311</v>
       </c>
       <c r="D48" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>53.833333333333336</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!D50</f>
+        <v>65.55</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2471,19 +2477,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[2]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>175115</v>
+        <v>625691</v>
       </c>
       <c r="B3" s="3">
         <f>'[2]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>171557</v>
+        <v>610798</v>
       </c>
       <c r="C3" s="4">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>29185.833333333332</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!I3</f>
+        <v>31284.55</v>
       </c>
       <c r="D3" s="5">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>612902.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!J3</f>
+        <v>656975.55000000005</v>
       </c>
       <c r="E3" s="4">
         <f>'[2]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2491,11 +2497,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[2]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.25452761627906978</v>
+        <v>0.9094345930232558</v>
       </c>
       <c r="G3" s="7">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-75097.5</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!M3</f>
+        <v>-31024.449999999953</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2528,27 +2534,27 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[2]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>3558</v>
+        <v>14893</v>
       </c>
       <c r="B5" s="16">
         <f>'[2]VINCULO VTS BY SKU OPEN'!H5</f>
         <v>46296</v>
       </c>
       <c r="C5" s="16">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46304</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!I5</f>
+        <v>46325</v>
       </c>
       <c r="D5" s="16">
         <f>'[2]VINCULO VTS BY SKU OPEN'!J5</f>
         <v>46326</v>
       </c>
       <c r="E5" s="19">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>6</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!K5</f>
+        <v>20</v>
       </c>
       <c r="F5" s="17">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>15</v>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!L5</f>
+        <v>1</v>
       </c>
       <c r="G5" s="11"/>
     </row>
